--- a/src/app/modules/dashboard/excel_files/arabic-oil-free-recipes-complete.xlsx
+++ b/src/app/modules/dashboard/excel_files/arabic-oil-free-recipes-complete.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V81"/>
+  <dimension ref="A1:W81"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -446,95 +446,100 @@
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
+          <t>recipe_id</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
           <t>ingredients</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>instructions</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>nutritional</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>serving_size</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>prep_time</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>category</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>oils</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>whole_food_type</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>flavor</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>weight_and_muscle</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>kid_approved</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>no_weekend_prep</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>holiday_recipes</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="R1" s="1" t="inlineStr">
         <is>
           <t>serving_temperature</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="S1" s="1" t="inlineStr">
         <is>
           <t>ratting</t>
         </is>
       </c>
-      <c r="S1" s="1" t="inlineStr">
+      <c r="T1" s="1" t="inlineStr">
         <is>
           <t>recipe_tips</t>
         </is>
       </c>
-      <c r="T1" s="1" t="inlineStr">
+      <c r="U1" s="1" t="inlineStr">
         <is>
           <t>prep</t>
         </is>
       </c>
-      <c r="U1" s="1" t="inlineStr">
+      <c r="V1" s="1" t="inlineStr">
         <is>
           <t>prep_time_note</t>
         </is>
       </c>
-      <c r="V1" s="1" t="inlineStr">
+      <c r="W1" s="1" t="inlineStr">
         <is>
           <t>prep_list</t>
         </is>
@@ -558,10 +563,15 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
+          <t>3312</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
           <t>['1 lb boneless, skin less chicken breast, thinly sliced', '2 tsp ground cumin', '2 tsp ground coriander', '1 tsp smoked paprika', '1/2 tsp ground turmeric', '1/2 tsp ground cinnamon', 'Juice of 1 lemon', '4 garlic cloves, minced', 'Salt and pepper, to taste', '4 whole wheat pita breads (or flatbreads)', '1 cup diced tomatoes', '1 cup thinly sliced red onions', '1 cup chopped lettuce', '1/2 cup fat free plain yogurt (for a cooling sauce)', 'Fresh parsley, chopped (for garnish)']</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
+      <c r="F2" t="inlineStr">
         <is>
           <t>1. In a bowl, combine chicken slices with cumin, coriander, paprika, turmeric, cinnamon, lemon juice, garlic, salt, and pepper. Toss well and let marinate in the refrigerator for at least 30 minutes.
 2. Preheat a grill pan over medium high heat. Grill the chicken for 5–7 minutes until fully cooked and slightly charred.
@@ -571,59 +581,59 @@
 6. Cook time: 10</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr">
+      <c r="G2" t="inlineStr">
         <is>
           <t>{"calories": 420, "protein": "38 g", "carbs": "45 g", "fiber": "5 g", "fat": "6 g"}</t>
         </is>
       </c>
-      <c r="G2" t="n">
+      <c r="H2" t="n">
         <v>4</v>
       </c>
-      <c r="H2" t="n">
+      <c r="I2" t="n">
         <v>20</v>
       </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>['weight-loss', 'plant-based', 'whole-foods', 'oil-free', 'lunches-and-dinners', 'soups', 'salads', 'wraps', 'sandwiches', 'rice', 'stews', 'stir-fry', 'seafood', 'ethnic', 'arabic', 'desserts']</t>
-        </is>
-      </c>
       <c r="J2" t="inlineStr">
         <is>
+          <t>['animal-protein', 'arabic', 'ethnic', 'lunches-and-dinners', 'oil-free', 'weight-loss', 'wraps']</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
           <t>oil_free</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>plant_based</t>
-        </is>
-      </c>
       <c r="L2" t="inlineStr">
         <is>
+          <t>whole_food</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
           <t>Savory</t>
         </is>
       </c>
-      <c r="M2" t="inlineStr">
+      <c r="N2" t="inlineStr">
         <is>
           <t>weight_loss</t>
         </is>
       </c>
-      <c r="N2" t="b">
-        <v>0</v>
-      </c>
       <c r="O2" t="b">
         <v>0</v>
       </c>
-      <c r="P2" t="inlineStr"/>
-      <c r="Q2" t="inlineStr">
+      <c r="P2" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q2" t="inlineStr"/>
+      <c r="R2" t="inlineStr">
         <is>
           <t>hot</t>
         </is>
       </c>
-      <c r="R2" t="n">
-        <v>0</v>
-      </c>
-      <c r="S2" t="inlineStr"/>
-      <c r="T2" t="inlineStr">
+      <c r="S2" t="n">
+        <v>0</v>
+      </c>
+      <c r="T2" t="inlineStr"/>
+      <c r="U2" t="inlineStr">
         <is>
           <t>1. In a bowl, combine chicken slices with cumin, coriander, paprika, turmeric, cinnamon, lemon juice, garlic, salt, and pepper. Toss well and let marinate in the refrigerator for at least 30 minutes.
 2. Preheat a grill pan over medium high heat. Grill the chicken for 5–7 minutes until fully cooked and slightly charred.
@@ -633,8 +643,8 @@
 6. Cook time: 10</t>
         </is>
       </c>
-      <c r="U2" t="inlineStr"/>
-      <c r="V2" t="inlineStr">
+      <c r="V2" t="inlineStr"/>
+      <c r="W2" t="inlineStr">
         <is>
           <t>['In a bowl, combine chicken slices with cumin, coriander, paprika, turmeric, cinnamon, lemon juice, garlic, salt, and pepper. Toss well and let marinate in the refrigerator for at least 30 minutes.', 'Preheat a grill pan over medium high heat. Grill the chicken for 5–7 minutes until fully cooked and slightly charred.', 'Warm the whole wheat pitas on a dry skillet for 1–2 minutes per side.', 'To assemble, layer pita with chopped lettuce, diced tomatoes, red onions, grilled chicken, and a dollop of fat free yogurt.', 'Garnish with fresh parsley, roll up, and serve immediately.', 'Cook time: 10']</t>
         </is>
@@ -653,15 +663,20 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Oil Free Lamb Kofta with Bulgur Pilaf</t>
+          <t>Oil Free Lamb Kofta With Bulgur Pilaf</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
+          <t>3313</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
           <t>['1 lb ground lamb (lean)', '1 small onion, grated', '3 garlic cloves, minced', '1 tsp ground cumin', '1 tsp ground coriander', '1/2 tsp ground allspice', '1/4 tsp cayenne pepper (optional)', 'Salt and pepper, to taste', '1 cup bulgur wheat', '2 cups low sodium vegetable broth', '1/2 cup chopped fresh parsley', 'Juice of 1 lemon']</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr">
+      <c r="F3" t="inlineStr">
         <is>
           <t>1. In a large bowl, combine ground lamb, grated onion, garlic, cumin, coriander, allspice, cayenne, salt, and pepper. Mix gently and form into small, oval-shaped kofta (about 1 inch thick).
 2. Preheat a grill pan or nonstick skillet over medium high heat and grill the kofta for about 4–5 minutes per side until cooked through.
@@ -671,59 +686,59 @@
 6. Cook time: 20</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr">
+      <c r="G3" t="inlineStr">
         <is>
           <t>{"calories": 480, "protein": "30 g", "carbs": "50 g", "fiber": "8 g", "fat": "12 g"}</t>
         </is>
       </c>
-      <c r="G3" t="n">
+      <c r="H3" t="n">
         <v>4</v>
       </c>
-      <c r="H3" t="n">
+      <c r="I3" t="n">
         <v>25</v>
       </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>['weight-loss', 'plant-based', 'whole-foods', 'oil-free', 'lunches-and-dinners', 'soups', 'salads', 'wraps', 'sandwiches', 'rice', 'stews', 'stir-fry', 'seafood', 'ethnic', 'arabic', 'desserts']</t>
-        </is>
-      </c>
       <c r="J3" t="inlineStr">
         <is>
+          <t>['animal-protein', 'arabic', 'ethnic', 'lunches-and-dinners', 'oil-free', 'rice', 'weight-loss']</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
           <t>oil_free</t>
         </is>
       </c>
-      <c r="K3" t="inlineStr">
+      <c r="L3" t="inlineStr">
         <is>
           <t>plant_based</t>
         </is>
       </c>
-      <c r="L3" t="inlineStr">
+      <c r="M3" t="inlineStr">
         <is>
           <t>Savory</t>
         </is>
       </c>
-      <c r="M3" t="inlineStr">
+      <c r="N3" t="inlineStr">
         <is>
           <t>weight_loss</t>
         </is>
       </c>
-      <c r="N3" t="b">
-        <v>0</v>
-      </c>
       <c r="O3" t="b">
         <v>0</v>
       </c>
-      <c r="P3" t="inlineStr"/>
-      <c r="Q3" t="inlineStr">
+      <c r="P3" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q3" t="inlineStr"/>
+      <c r="R3" t="inlineStr">
         <is>
           <t>hot</t>
         </is>
       </c>
-      <c r="R3" t="n">
-        <v>0</v>
-      </c>
-      <c r="S3" t="inlineStr"/>
-      <c r="T3" t="inlineStr">
+      <c r="S3" t="n">
+        <v>0</v>
+      </c>
+      <c r="T3" t="inlineStr"/>
+      <c r="U3" t="inlineStr">
         <is>
           <t>1. In a large bowl, combine ground lamb, grated onion, garlic, cumin, coriander, allspice, cayenne, salt, and pepper. Mix gently and form into small, oval-shaped kofta (about 1 inch thick).
 2. Preheat a grill pan or nonstick skillet over medium high heat and grill the kofta for about 4–5 minutes per side until cooked through.
@@ -733,8 +748,8 @@
 6. Cook time: 20</t>
         </is>
       </c>
-      <c r="U3" t="inlineStr"/>
-      <c r="V3" t="inlineStr">
+      <c r="V3" t="inlineStr"/>
+      <c r="W3" t="inlineStr">
         <is>
           <t>['In a large bowl, combine ground lamb, grated onion, garlic, cumin, coriander, allspice, cayenne, salt, and pepper. Mix gently and form into small, oval-shaped kofta (about 1 inch thick).', 'Preheat a grill pan or nonstick skillet over medium high heat and grill the kofta for about 4–5 minutes per side until cooked through.', 'Meanwhile, bring the vegetable broth to a boil in a saucepan. Stir in bulgur wheat, cover, and reduce heat; simmer for 15 minutes until tender.', 'Fluff the pilaf with a fork and stir in chopped parsley and lemon juice.', 'Serve the lamb kofta on a bed of bulgur pilaf.', 'Cook time: 20']</t>
         </is>
@@ -753,15 +768,20 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Oil Free Grilled Fish with Sumac Rice &amp; Vegetables</t>
+          <t>Oil Free Grilled Fish With Sumac Rice &amp; Vegetables</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
+          <t>3314</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
           <t>['8\u202foz white fish fillet (such as cod or tilapia)', 'Juice of 1 lemon', '1 tsp ground sumac', 'Salt and pepper, to taste', '2 cups cooked basmati rice', '1 cup steamed green beans', '1 cup diced tomatoes', '1/2 cup chopped fresh parsley']</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr">
+      <c r="F4" t="inlineStr">
         <is>
           <t>1. Season the fish fillet with lemon juice, sumac, salt, and pepper.
 2. Preheat a grill pan over medium heat and grill the fish for 4–5 minutes per side until it flakes easily.
@@ -770,59 +790,59 @@
 5. Cook time: 10</t>
         </is>
       </c>
-      <c r="F4" t="inlineStr">
+      <c r="G4" t="inlineStr">
         <is>
           <t>{"calories": 500, "protein": "35 g", "carbs": "60 g", "fiber": "8 g", "fat": "10 g"}</t>
         </is>
       </c>
-      <c r="G4" t="n">
+      <c r="H4" t="n">
         <v>2</v>
       </c>
-      <c r="H4" t="n">
+      <c r="I4" t="n">
         <v>15</v>
       </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>['weight-loss', 'plant-based', 'whole-foods', 'oil-free', 'lunches-and-dinners', 'soups', 'salads', 'wraps', 'sandwiches', 'rice', 'stews', 'stir-fry', 'seafood', 'ethnic', 'arabic', 'desserts']</t>
-        </is>
-      </c>
       <c r="J4" t="inlineStr">
         <is>
+          <t>['animal-protein', 'arabic', 'ethnic', 'lunches-and-dinners', 'oil-free', 'rice', 'seafood', 'weight-loss']</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
           <t>oil_free</t>
         </is>
       </c>
-      <c r="K4" t="inlineStr">
+      <c r="L4" t="inlineStr">
         <is>
           <t>plant_based</t>
         </is>
       </c>
-      <c r="L4" t="inlineStr">
+      <c r="M4" t="inlineStr">
         <is>
           <t>Savory</t>
         </is>
       </c>
-      <c r="M4" t="inlineStr">
+      <c r="N4" t="inlineStr">
         <is>
           <t>weight_loss</t>
         </is>
       </c>
-      <c r="N4" t="b">
-        <v>0</v>
-      </c>
       <c r="O4" t="b">
         <v>0</v>
       </c>
-      <c r="P4" t="inlineStr"/>
-      <c r="Q4" t="inlineStr">
+      <c r="P4" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q4" t="inlineStr"/>
+      <c r="R4" t="inlineStr">
         <is>
           <t>hot</t>
         </is>
       </c>
-      <c r="R4" t="n">
-        <v>0</v>
-      </c>
-      <c r="S4" t="inlineStr"/>
-      <c r="T4" t="inlineStr">
+      <c r="S4" t="n">
+        <v>0</v>
+      </c>
+      <c r="T4" t="inlineStr"/>
+      <c r="U4" t="inlineStr">
         <is>
           <t>1. Season the fish fillet with lemon juice, sumac, salt, and pepper.
 2. Preheat a grill pan over medium heat and grill the fish for 4–5 minutes per side until it flakes easily.
@@ -831,8 +851,8 @@
 5. Cook time: 10</t>
         </is>
       </c>
-      <c r="U4" t="inlineStr"/>
-      <c r="V4" t="inlineStr">
+      <c r="V4" t="inlineStr"/>
+      <c r="W4" t="inlineStr">
         <is>
           <t>['Season the fish fillet with lemon juice, sumac, salt, and pepper.', 'Preheat a grill pan over medium heat and grill the fish for 4–5 minutes per side until it flakes easily.', 'In a bowl, mix the cooked basmati rice with steamed green beans, diced tomatoes, and chopped parsley.', 'Serve the grilled fish over the sumac rice mixture, with an extra squeeze of lemon.', 'Cook time: 10']</t>
         </is>
@@ -851,15 +871,20 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Oil Free Mujadara (Lentils &amp; Rice with Caramelized Onions)</t>
+          <t>Oil Free Mujadara (Lentils &amp; Rice With Caramelized Onions)</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
+          <t>3315</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
           <t>['1 cup brown lentils, rinsed', '1 cup basmati rice, rinsed', '4 cups low sodium vegetable broth', '2 large onions, thinly sliced', '1 tsp ground cumin', '1/2 tsp ground cinnamon', 'Salt and pepper, to taste', 'Juice of 1 lemon', 'Fresh parsley, chopped (for garnish)']</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr">
+      <c r="F5" t="inlineStr">
         <is>
           <t>1. In a pot, combine lentils and vegetable broth; bring to a boil, then reduce heat and simmer for 20 minutes until lentils are nearly tender.
 2. Stir in the basmati rice, cover, and simmer for an additional 15–20 minutes until both lentils and rice are cooked.
@@ -869,59 +894,59 @@
 6. Cook time: 40</t>
         </is>
       </c>
-      <c r="F5" t="inlineStr">
+      <c r="G5" t="inlineStr">
         <is>
           <t>{"calories": 400, "protein": "15 g", "carbs": "70 g", "fiber": "12 g", "fat": "3 g"}</t>
         </is>
       </c>
-      <c r="G5" t="n">
+      <c r="H5" t="n">
         <v>4</v>
       </c>
-      <c r="H5" t="n">
+      <c r="I5" t="n">
         <v>15</v>
       </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>['weight-loss', 'plant-based', 'whole-foods', 'oil-free', 'lunches-and-dinners', 'soups', 'salads', 'wraps', 'sandwiches', 'rice', 'stews', 'stir-fry', 'seafood', 'ethnic', 'arabic', 'desserts']</t>
-        </is>
-      </c>
       <c r="J5" t="inlineStr">
         <is>
+          <t>['arabic', 'ethnic', 'lunches-and-dinners', 'oil-free', 'rice', 'weight-loss']</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
           <t>oil_free</t>
         </is>
       </c>
-      <c r="K5" t="inlineStr">
+      <c r="L5" t="inlineStr">
         <is>
           <t>plant_based</t>
         </is>
       </c>
-      <c r="L5" t="inlineStr">
+      <c r="M5" t="inlineStr">
         <is>
           <t>Savory</t>
         </is>
       </c>
-      <c r="M5" t="inlineStr">
+      <c r="N5" t="inlineStr">
         <is>
           <t>weight_loss</t>
         </is>
       </c>
-      <c r="N5" t="b">
-        <v>0</v>
-      </c>
       <c r="O5" t="b">
         <v>0</v>
       </c>
-      <c r="P5" t="inlineStr"/>
-      <c r="Q5" t="inlineStr">
+      <c r="P5" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q5" t="inlineStr"/>
+      <c r="R5" t="inlineStr">
         <is>
           <t>hot</t>
         </is>
       </c>
-      <c r="R5" t="n">
-        <v>0</v>
-      </c>
-      <c r="S5" t="inlineStr"/>
-      <c r="T5" t="inlineStr">
+      <c r="S5" t="n">
+        <v>0</v>
+      </c>
+      <c r="T5" t="inlineStr"/>
+      <c r="U5" t="inlineStr">
         <is>
           <t>1. In a pot, combine lentils and vegetable broth; bring to a boil, then reduce heat and simmer for 20 minutes until lentils are nearly tender.
 2. Stir in the basmati rice, cover, and simmer for an additional 15–20 minutes until both lentils and rice are cooked.
@@ -931,8 +956,8 @@
 6. Cook time: 40</t>
         </is>
       </c>
-      <c r="U5" t="inlineStr"/>
-      <c r="V5" t="inlineStr">
+      <c r="V5" t="inlineStr"/>
+      <c r="W5" t="inlineStr">
         <is>
           <t>['In a pot, combine lentils and vegetable broth; bring to a boil, then reduce heat and simmer for 20 minutes until lentils are nearly tender.', 'Stir in the basmati rice, cover, and simmer for an additional 15–20 minutes until both lentils and rice are cooked.', 'Meanwhile, in a nonstick pan (using a few tablespoons of water if needed), slowly caramelize the sliced onions over low heat for 15–20 minutes until deeply browned and sweet.', 'Season the lentil and rice mixture with cumin, cinnamon, salt, and pepper; stir in lemon juice.', 'Top with the caramelized onions and garnish with fresh parsley before serving.', 'Cook time: 40']</t>
         </is>
@@ -951,15 +976,20 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Oil Free Baked Falafel Patties with Tahini Sauce</t>
+          <t>Oil Free Baked Falafel Patties With Tahini Sauce</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
+          <t>3316</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
           <t>['1 can (15 oz) chickpeas, drained and rinsed', '1 small onion, roughly chopped', '3 garlic cloves', '1/4 cup fresh parsley', '1/4 cup fresh cilantro', '2 tsp ground cumin', '1 tsp ground coriander', '1/2 tsp baking soda', 'Salt and pepper, to taste', '2 tbsp lemon juice', '2–3 tbsp water (as needed)', 'For Tahini Sauce:', '1/4 cup tahini (no added oil)', 'Juice of 1 lemon', '1 garlic clove, minced', '2–3 tbsp water', 'Salt, to taste']</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr">
+      <c r="F6" t="inlineStr">
         <is>
           <t>1. In a food processor, combine chickpeas, onion, garlic, parsley, cilantro, cumin, coriander, baking soda, salt, pepper, and lemon juice. Process until well blended but still slightly chunky; add water as needed to achieve a pliable mixture.
 2. Form the mixture into small patties.
@@ -969,59 +999,59 @@
 6. Cook time: 25</t>
         </is>
       </c>
-      <c r="F6" t="inlineStr">
+      <c r="G6" t="inlineStr">
         <is>
           <t>{"calories": 420, "protein": "16 g", "carbs": "60 g", "fiber": "12 g", "fat": "10 g"}</t>
         </is>
       </c>
-      <c r="G6" t="n">
+      <c r="H6" t="n">
         <v>4</v>
       </c>
-      <c r="H6" t="n">
+      <c r="I6" t="n">
         <v>20</v>
       </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>['weight-loss', 'plant-based', 'whole-foods', 'oil-free', 'lunches-and-dinners', 'soups', 'salads', 'wraps', 'sandwiches', 'rice', 'stews', 'stir-fry', 'seafood', 'ethnic', 'arabic', 'desserts']</t>
-        </is>
-      </c>
       <c r="J6" t="inlineStr">
         <is>
+          <t>['arabic', 'ethnic', 'lunches-and-dinners', 'oil-free', 'vegetarian', 'weight-loss']</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
           <t>oil_free</t>
         </is>
       </c>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>plant_based</t>
-        </is>
-      </c>
       <c r="L6" t="inlineStr">
         <is>
+          <t>Vegetarian</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
           <t>Savory</t>
         </is>
       </c>
-      <c r="M6" t="inlineStr">
+      <c r="N6" t="inlineStr">
         <is>
           <t>weight_loss</t>
         </is>
       </c>
-      <c r="N6" t="b">
-        <v>0</v>
-      </c>
       <c r="O6" t="b">
         <v>0</v>
       </c>
-      <c r="P6" t="inlineStr"/>
-      <c r="Q6" t="inlineStr">
+      <c r="P6" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q6" t="inlineStr"/>
+      <c r="R6" t="inlineStr">
         <is>
           <t>hot</t>
         </is>
       </c>
-      <c r="R6" t="n">
-        <v>0</v>
-      </c>
-      <c r="S6" t="inlineStr"/>
-      <c r="T6" t="inlineStr">
+      <c r="S6" t="n">
+        <v>0</v>
+      </c>
+      <c r="T6" t="inlineStr"/>
+      <c r="U6" t="inlineStr">
         <is>
           <t>1. In a food processor, combine chickpeas, onion, garlic, parsley, cilantro, cumin, coriander, baking soda, salt, pepper, and lemon juice. Process until well blended but still slightly chunky; add water as needed to achieve a pliable mixture.
 2. Form the mixture into small patties.
@@ -1031,8 +1061,8 @@
 6. Cook time: 25</t>
         </is>
       </c>
-      <c r="U6" t="inlineStr"/>
-      <c r="V6" t="inlineStr">
+      <c r="V6" t="inlineStr"/>
+      <c r="W6" t="inlineStr">
         <is>
           <t>['In a food processor, combine chickpeas, onion, garlic, parsley, cilantro, cumin, coriander, baking soda, salt, pepper, and lemon juice. Process until well blended but still slightly chunky; add water as needed to achieve a pliable mixture.', 'Form the mixture into small patties.', 'Place patties on a parchment lined baking sheet and bake in a preheated 400°F (200°C) oven for 20–25 minutes, flipping halfway through until golden.', 'For the tahini sauce, whisk together tahini, lemon juice, garlic, water, and salt until smooth.', 'Serve the falafel patties with tahini sauce and whole wheat pita if desired.', 'Cook time: 25']</t>
         </is>
@@ -1056,10 +1086,15 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
+          <t>3317</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
           <t>['30 grape leaves, rinsed and patted dry', '1 cup short grain rice, rinsed', '1/2 cup chopped tomatoes', '1/4 cup chopped fresh parsley', '1/4 cup chopped fresh mint', '1 small onion, finely chopped', 'Juice of 1 lemon', '1 tsp ground allspice', 'Salt and pepper, to taste', '1 cup vegetable broth (low sodium)']</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr">
+      <c r="F7" t="inlineStr">
         <is>
           <t>1. In a bowl, mix rice, tomatoes, parsley, mint, onion, lemon juice, allspice, salt, and pepper.
 2. Place a heaping teaspoon of filling onto each grape leaf and roll tightly into a cigar shape.
@@ -1069,59 +1104,59 @@
 6. Cook time: 45</t>
         </is>
       </c>
-      <c r="F7" t="inlineStr">
+      <c r="G7" t="inlineStr">
         <is>
           <t>{"calories": 350, "protein": "8 g", "carbs": "65 g", "fiber": "10 g", "fat": "3 g"}</t>
         </is>
       </c>
-      <c r="G7" t="n">
+      <c r="H7" t="n">
         <v>4</v>
       </c>
-      <c r="H7" t="n">
+      <c r="I7" t="n">
         <v>30</v>
       </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>['weight-loss', 'plant-based', 'whole-foods', 'oil-free', 'lunches-and-dinners', 'soups', 'salads', 'wraps', 'sandwiches', 'rice', 'stews', 'stir-fry', 'seafood', 'ethnic', 'arabic', 'desserts']</t>
-        </is>
-      </c>
       <c r="J7" t="inlineStr">
         <is>
+          <t>['arabic', 'ethnic', 'lunches-and-dinners', 'oil-free', 'vegetarian', 'weight-loss']</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
           <t>oil_free</t>
         </is>
       </c>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>plant_based</t>
-        </is>
-      </c>
       <c r="L7" t="inlineStr">
         <is>
+          <t>Vegetarian</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
           <t>Savory</t>
         </is>
       </c>
-      <c r="M7" t="inlineStr">
+      <c r="N7" t="inlineStr">
         <is>
           <t>weight_loss</t>
         </is>
       </c>
-      <c r="N7" t="b">
-        <v>0</v>
-      </c>
       <c r="O7" t="b">
         <v>0</v>
       </c>
-      <c r="P7" t="inlineStr"/>
-      <c r="Q7" t="inlineStr">
+      <c r="P7" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q7" t="inlineStr"/>
+      <c r="R7" t="inlineStr">
         <is>
           <t>hot</t>
         </is>
       </c>
-      <c r="R7" t="n">
-        <v>0</v>
-      </c>
-      <c r="S7" t="inlineStr"/>
-      <c r="T7" t="inlineStr">
+      <c r="S7" t="n">
+        <v>0</v>
+      </c>
+      <c r="T7" t="inlineStr"/>
+      <c r="U7" t="inlineStr">
         <is>
           <t>1. In a bowl, mix rice, tomatoes, parsley, mint, onion, lemon juice, allspice, salt, and pepper.
 2. Place a heaping teaspoon of filling onto each grape leaf and roll tightly into a cigar shape.
@@ -1131,8 +1166,8 @@
 6. Cook time: 45</t>
         </is>
       </c>
-      <c r="U7" t="inlineStr"/>
-      <c r="V7" t="inlineStr">
+      <c r="V7" t="inlineStr"/>
+      <c r="W7" t="inlineStr">
         <is>
           <t>['In a bowl, mix rice, tomatoes, parsley, mint, onion, lemon juice, allspice, salt, and pepper.', 'Place a heaping teaspoon of filling onto each grape leaf and roll tightly into a cigar shape.', 'Arrange stuffed grape leaves in a pot, seam side down.', 'Pour vegetable broth over the leaves, cover, and simmer on low heat for 45 minutes until rice is tender.', 'Allow to cool slightly before serving.', 'Cook time: 45']</t>
         </is>
@@ -1156,10 +1191,15 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
+          <t>3318</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
           <t>['2 medium eggplants, sliced into 1/2 inch rounds', '1 cup cooked chickpeas, mashed lightly', '1 large tomato, diced', '1 onion, finely chopped', '2 garlic cloves, minced', '1 tsp ground cinnamon', '1/2 tsp ground allspice', '1 cup cooked brown rice', 'Salt and pepper, to taste', '1/4 cup chopped fresh parsley']</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr">
+      <c r="F8" t="inlineStr">
         <is>
           <t>1. Preheat oven to 400°F (200°C).
 2. Arrange eggplant slices on a baking sheet; roast for 20 minutes until soft and lightly browned.
@@ -1169,59 +1209,59 @@
 6. Cook time: 40</t>
         </is>
       </c>
-      <c r="F8" t="inlineStr">
+      <c r="G8" t="inlineStr">
         <is>
           <t>{"calories": 370, "protein": "12 g", "carbs": "65 g", "fiber": "10 g", "fat": "5 g"}</t>
         </is>
       </c>
-      <c r="G8" t="n">
+      <c r="H8" t="n">
         <v>4</v>
       </c>
-      <c r="H8" t="n">
+      <c r="I8" t="n">
         <v>25</v>
       </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>['weight-loss', 'plant-based', 'whole-foods', 'oil-free', 'lunches-and-dinners', 'soups', 'salads', 'wraps', 'sandwiches', 'rice', 'stews', 'stir-fry', 'seafood', 'ethnic', 'arabic', 'desserts']</t>
-        </is>
-      </c>
       <c r="J8" t="inlineStr">
         <is>
+          <t>['arabic', 'ethnic', 'lunches-and-dinners', 'oil-free', 'vegetarian', 'weight-loss']</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
           <t>oil_free</t>
         </is>
       </c>
-      <c r="K8" t="inlineStr">
-        <is>
-          <t>plant_based</t>
-        </is>
-      </c>
       <c r="L8" t="inlineStr">
         <is>
+          <t>Vegetarian</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
           <t>Savory</t>
         </is>
       </c>
-      <c r="M8" t="inlineStr">
+      <c r="N8" t="inlineStr">
         <is>
           <t>weight_loss</t>
         </is>
       </c>
-      <c r="N8" t="b">
-        <v>0</v>
-      </c>
       <c r="O8" t="b">
         <v>0</v>
       </c>
-      <c r="P8" t="inlineStr"/>
-      <c r="Q8" t="inlineStr">
+      <c r="P8" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q8" t="inlineStr"/>
+      <c r="R8" t="inlineStr">
         <is>
           <t>hot</t>
         </is>
       </c>
-      <c r="R8" t="n">
-        <v>0</v>
-      </c>
-      <c r="S8" t="inlineStr"/>
-      <c r="T8" t="inlineStr">
+      <c r="S8" t="n">
+        <v>0</v>
+      </c>
+      <c r="T8" t="inlineStr"/>
+      <c r="U8" t="inlineStr">
         <is>
           <t>1. Preheat oven to 400°F (200°C).
 2. Arrange eggplant slices on a baking sheet; roast for 20 minutes until soft and lightly browned.
@@ -1231,8 +1271,8 @@
 6. Cook time: 40</t>
         </is>
       </c>
-      <c r="U8" t="inlineStr"/>
-      <c r="V8" t="inlineStr">
+      <c r="V8" t="inlineStr"/>
+      <c r="W8" t="inlineStr">
         <is>
           <t>['Preheat oven to 400°F (200°C).', 'Arrange eggplant slices on a baking sheet; roast for 20 minutes until soft and lightly browned.', 'In a skillet, sauté onion and garlic (using a splash of water) until softened; add diced tomato, mashed chickpeas, cinnamon, allspice, salt, and pepper. Cook for 5 minutes until flavors meld.', 'In a baking dish, layer roasted eggplant, brown rice, and the tomato-chickpea mixture. Repeat layers and top with chopped parsley.', 'Bake for 20 minutes; let stand for 5 minutes before serving.', 'Cook time: 40']</t>
         </is>
@@ -1251,15 +1291,20 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Oil Free Chicken Kabsa (Spiced Rice with Chicken)</t>
+          <t>Oil Free Chicken Kabsa (Spiced Rice With Chicken)</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
+          <t>3319</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
           <t>['1 lb chicken thighs, skin less', '2 cups basmati rice, rinsed', '4 cups low sodium chicken broth', '1 large onion, thinly sliced', '3 garlic cloves, minced', '1 tsp ground cumin', '1 tsp ground coriander', '1/2 tsp ground cardamom', '1/2 tsp turmeric', '1/2 tsp cinnamon', 'Salt and pepper, to taste', '1/4 cup raisins', '1/4 cup slivered almonds (optional, toasted without oil)', 'Fresh cilantro, chopped (for garnish)']</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr">
+      <c r="F9" t="inlineStr">
         <is>
           <t>1. In a large pot, sauté onion and garlic (using a splash of water) until soft.
 2. Add spices (cumin, coriander, cardamom, turmeric, cinnamon), salt, and pepper; stir for 1 minute until aromatic.
@@ -1269,59 +1314,59 @@
 6. Cook time: 30</t>
         </is>
       </c>
-      <c r="F9" t="inlineStr">
+      <c r="G9" t="inlineStr">
         <is>
           <t>{"calories": 480, "protein": "32 g", "carbs": "65 g", "fiber": "6 g", "fat": "8 g"}</t>
         </is>
       </c>
-      <c r="G9" t="n">
+      <c r="H9" t="n">
         <v>4</v>
       </c>
-      <c r="H9" t="n">
+      <c r="I9" t="n">
         <v>25</v>
       </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>['weight-loss', 'plant-based', 'whole-foods', 'oil-free', 'lunches-and-dinners', 'soups', 'salads', 'wraps', 'sandwiches', 'rice', 'stews', 'stir-fry', 'seafood', 'ethnic', 'arabic', 'desserts']</t>
-        </is>
-      </c>
       <c r="J9" t="inlineStr">
         <is>
+          <t>['animal-protein', 'arabic', 'ethnic', 'lunches-and-dinners', 'oil-free', 'rice', 'weight-loss']</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
           <t>oil_free</t>
         </is>
       </c>
-      <c r="K9" t="inlineStr">
+      <c r="L9" t="inlineStr">
         <is>
           <t>plant_based</t>
         </is>
       </c>
-      <c r="L9" t="inlineStr">
-        <is>
-          <t>Savory</t>
-        </is>
-      </c>
       <c r="M9" t="inlineStr">
         <is>
+          <t>Spicy</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
           <t>weight_loss</t>
         </is>
       </c>
-      <c r="N9" t="b">
-        <v>0</v>
-      </c>
       <c r="O9" t="b">
         <v>0</v>
       </c>
-      <c r="P9" t="inlineStr"/>
-      <c r="Q9" t="inlineStr">
+      <c r="P9" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q9" t="inlineStr"/>
+      <c r="R9" t="inlineStr">
         <is>
           <t>hot</t>
         </is>
       </c>
-      <c r="R9" t="n">
-        <v>0</v>
-      </c>
-      <c r="S9" t="inlineStr"/>
-      <c r="T9" t="inlineStr">
+      <c r="S9" t="n">
+        <v>0</v>
+      </c>
+      <c r="T9" t="inlineStr"/>
+      <c r="U9" t="inlineStr">
         <is>
           <t>1. In a large pot, sauté onion and garlic (using a splash of water) until soft.
 2. Add spices (cumin, coriander, cardamom, turmeric, cinnamon), salt, and pepper; stir for 1 minute until aromatic.
@@ -1331,8 +1376,8 @@
 6. Cook time: 30</t>
         </is>
       </c>
-      <c r="U9" t="inlineStr"/>
-      <c r="V9" t="inlineStr">
+      <c r="V9" t="inlineStr"/>
+      <c r="W9" t="inlineStr">
         <is>
           <t>['In a large pot, sauté onion and garlic (using a splash of water) until soft.', 'Add spices (cumin, coriander, cardamom, turmeric, cinnamon), salt, and pepper; stir for 1 minute until aromatic.', 'Add chicken thighs and brown lightly on all sides (about 5 minutes).', 'Stir in basmati rice, raisins, and chicken broth. Bring to a boil, then reduce heat, cover, and simmer for 25–30 minutes until rice is tender and chicken is cooked through.', 'Garnish with toasted almonds and chopped cilantro before serving.', 'Cook time: 30']</t>
         </is>
@@ -1351,15 +1396,20 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Oil Free Lamb Tagine with Vegetables</t>
+          <t>Oil Free Lamb Tagine With Vegetables</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
+          <t>3320</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
           <t>['1 lb lean lamb stew meat, cut into 1 inch cubes', '1 large onion, chopped', '2 garlic cloves, minced', '1 tsp ground cumin', '1 tsp ground coriander', '1/2 tsp ground cinnamon', '1/2 tsp paprika', '2 cups chopped tomatoes', '2 cups cubed butternut squash', '1 cup chopped carrots', '1 cup low sodium lamb or vegetable broth', 'Salt and pepper, to taste', '1/4 cup chopped fresh cilantro']</t>
         </is>
       </c>
-      <c r="E10" t="inlineStr">
+      <c r="F10" t="inlineStr">
         <is>
           <t>1. In a heavy pot, combine lamb, onion, garlic, cumin, coriander, cinnamon, paprika, salt, and pepper.
 2. Add chopped tomatoes, butternut squash, carrots, and broth.
@@ -1368,59 +1418,59 @@
 5. Cook time: 1</t>
         </is>
       </c>
-      <c r="F10" t="inlineStr">
+      <c r="G10" t="inlineStr">
         <is>
           <t>{"calories": 500, "protein": "38 g", "carbs": "50 g", "fiber": "8 g", "fat": "12 g"}</t>
         </is>
       </c>
-      <c r="G10" t="n">
+      <c r="H10" t="n">
         <v>4</v>
       </c>
-      <c r="H10" t="n">
+      <c r="I10" t="n">
         <v>20</v>
       </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>['weight-loss', 'plant-based', 'whole-foods', 'oil-free', 'lunches-and-dinners', 'soups', 'salads', 'wraps', 'sandwiches', 'rice', 'stews', 'stir-fry', 'seafood', 'ethnic', 'arabic', 'desserts']</t>
-        </is>
-      </c>
       <c r="J10" t="inlineStr">
         <is>
+          <t>['animal-protein', 'arabic', 'ethnic', 'lunches-and-dinners', 'oil-free', 'weight-loss']</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
           <t>oil_free</t>
         </is>
       </c>
-      <c r="K10" t="inlineStr">
+      <c r="L10" t="inlineStr">
         <is>
           <t>plant_based</t>
         </is>
       </c>
-      <c r="L10" t="inlineStr">
+      <c r="M10" t="inlineStr">
         <is>
           <t>Savory</t>
         </is>
       </c>
-      <c r="M10" t="inlineStr">
+      <c r="N10" t="inlineStr">
         <is>
           <t>weight_loss</t>
         </is>
       </c>
-      <c r="N10" t="b">
-        <v>0</v>
-      </c>
       <c r="O10" t="b">
         <v>0</v>
       </c>
-      <c r="P10" t="inlineStr"/>
-      <c r="Q10" t="inlineStr">
+      <c r="P10" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q10" t="inlineStr"/>
+      <c r="R10" t="inlineStr">
         <is>
           <t>hot</t>
         </is>
       </c>
-      <c r="R10" t="n">
-        <v>0</v>
-      </c>
-      <c r="S10" t="inlineStr"/>
-      <c r="T10" t="inlineStr">
+      <c r="S10" t="n">
+        <v>0</v>
+      </c>
+      <c r="T10" t="inlineStr"/>
+      <c r="U10" t="inlineStr">
         <is>
           <t>1. In a heavy pot, combine lamb, onion, garlic, cumin, coriander, cinnamon, paprika, salt, and pepper.
 2. Add chopped tomatoes, butternut squash, carrots, and broth.
@@ -1429,8 +1479,8 @@
 5. Cook time: 1</t>
         </is>
       </c>
-      <c r="U10" t="inlineStr"/>
-      <c r="V10" t="inlineStr">
+      <c r="V10" t="inlineStr"/>
+      <c r="W10" t="inlineStr">
         <is>
           <t>['In a heavy pot, combine lamb, onion, garlic, cumin, coriander, cinnamon, paprika, salt, and pepper.', 'Add chopped tomatoes, butternut squash, carrots, and broth.', 'Bring to a simmer, then cover and cook on low heat for 1 to 1½ hours until the lamb is tender and vegetables are soft.', 'Stir in chopped cilantro and adjust seasoning before serving.', 'Cook time: 1']</t>
         </is>
@@ -1454,10 +1504,15 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
+          <t>3321</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
           <t>['2 cups whole wheat flour', '1 cup pitted dates, chopped', '1/2 cup walnuts, chopped', '1 tsp baking powder', '1/2 tsp baking soda', '1/2 tsp salt', '1 cup unsweetened applesauce', '1/4 cup honey or maple syrup', '1 tsp cinnamon', '1/2 cup water (adjust as needed)', '1 tsp vanilla extract']</t>
         </is>
       </c>
-      <c r="E11" t="inlineStr">
+      <c r="F11" t="inlineStr">
         <is>
           <t>1. Preheat oven to 350°F (175°C). Grease a loaf pan with a nonstick spray or water brush.
 2. In a large bowl, whisk together whole wheat flour, baking powder, baking soda, salt, and cinnamon.
@@ -1469,59 +1524,59 @@
 8. Cook time: 50</t>
         </is>
       </c>
-      <c r="F11" t="inlineStr">
+      <c r="G11" t="inlineStr">
         <is>
           <t>{"calories": 180, "protein": "5 g", "carbs": "32 g", "fiber": "4 g", "fat": "3 g"}</t>
         </is>
       </c>
-      <c r="G11" t="n">
+      <c r="H11" t="n">
         <v>10</v>
       </c>
-      <c r="H11" t="n">
+      <c r="I11" t="n">
         <v>20</v>
       </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>['weight-loss', 'plant-based', 'whole-foods', 'oil-free', 'lunches-and-dinners', 'soups', 'salads', 'wraps', 'sandwiches', 'rice', 'stews', 'stir-fry', 'seafood', 'ethnic', 'arabic', 'desserts']</t>
-        </is>
-      </c>
       <c r="J11" t="inlineStr">
         <is>
+          <t>['appetizers', 'arabic', 'ethnic', 'oil-free', 'sides', 'vegetarian', 'weight-loss']</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
           <t>oil_free</t>
         </is>
       </c>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t>plant_based</t>
-        </is>
-      </c>
       <c r="L11" t="inlineStr">
         <is>
+          <t>Vegetarian</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
           <t>Savory</t>
         </is>
       </c>
-      <c r="M11" t="inlineStr">
+      <c r="N11" t="inlineStr">
         <is>
           <t>weight_loss</t>
         </is>
       </c>
-      <c r="N11" t="b">
-        <v>0</v>
-      </c>
       <c r="O11" t="b">
         <v>0</v>
       </c>
-      <c r="P11" t="inlineStr"/>
-      <c r="Q11" t="inlineStr">
+      <c r="P11" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q11" t="inlineStr"/>
+      <c r="R11" t="inlineStr">
         <is>
           <t>hot</t>
         </is>
       </c>
-      <c r="R11" t="n">
-        <v>0</v>
-      </c>
-      <c r="S11" t="inlineStr"/>
-      <c r="T11" t="inlineStr">
+      <c r="S11" t="n">
+        <v>0</v>
+      </c>
+      <c r="T11" t="inlineStr"/>
+      <c r="U11" t="inlineStr">
         <is>
           <t>1. Preheat oven to 350°F (175°C). Grease a loaf pan with a nonstick spray or water brush.
 2. In a large bowl, whisk together whole wheat flour, baking powder, baking soda, salt, and cinnamon.
@@ -1533,8 +1588,8 @@
 8. Cook time: 50</t>
         </is>
       </c>
-      <c r="U11" t="inlineStr"/>
-      <c r="V11" t="inlineStr">
+      <c r="V11" t="inlineStr"/>
+      <c r="W11" t="inlineStr">
         <is>
           <t>['Preheat oven to 350°F (175°C). Grease a loaf pan with a nonstick spray or water brush.', 'In a large bowl, whisk together whole wheat flour, baking powder, baking soda, salt, and cinnamon.', 'In another bowl, mix unsweetened applesauce, honey (or maple syrup), vanilla extract, and water.', 'Stir the wet ingredients into the dry until just combined; fold in chopped dates and walnuts.', 'Pour batter into the prepared loaf pan and smooth the top.', 'Bake for 45–50 minutes until a toothpick inserted into the center comes out clean.', 'Let cool in the pan for 10 minutes, then transfer to a wire rack to cool completely before slicing.', 'Cook time: 50']</t>
         </is>
@@ -1558,10 +1613,15 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
+          <t>3322</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
           <t>['1 lb chicken thighs, bone in or boneless (trimmed of excess fat)', '2 cups basmati rice, rinsed', '4 cups low sodium chicken broth', '1 large onion, thinly sliced', '3 garlic cloves, minced', '1 tsp ground cumin', '1 tsp ground coriander', '1/2 tsp ground cinnamon', '1/2 tsp ground turmeric', '1/4 tsp ground cardamom', '1 large tomato, chopped', '1/2 cup raisins', 'Salt and pepper, to taste', 'Juice of 1 lemon', 'Fresh cilantro, chopped (for garnish)']</t>
         </is>
       </c>
-      <c r="E12" t="inlineStr">
+      <c r="F12" t="inlineStr">
         <is>
           <t>1. In a large pot, combine the sliced onion and garlic with chicken broth; bring to a boil.
 2. Add chicken thighs, tomato, raisins, and all spices (cumin, coriander, cinnamon, turmeric, cardamom), then season with salt and pepper.
@@ -1572,59 +1632,59 @@
 7. Cook time: 30</t>
         </is>
       </c>
-      <c r="F12" t="inlineStr">
+      <c r="G12" t="inlineStr">
         <is>
           <t>{"calories": 480, "protein": "32 g", "carbs": "60 g", "fiber": "7 g", "fat": "6 g"}</t>
         </is>
       </c>
-      <c r="G12" t="n">
+      <c r="H12" t="n">
         <v>4</v>
       </c>
-      <c r="H12" t="n">
+      <c r="I12" t="n">
         <v>20</v>
       </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>['weight-loss', 'plant-based', 'whole-foods', 'oil-free', 'lunches-and-dinners', 'soups', 'salads', 'wraps', 'sandwiches', 'rice', 'stews', 'stir-fry', 'seafood', 'ethnic', 'arabic', 'desserts']</t>
-        </is>
-      </c>
       <c r="J12" t="inlineStr">
         <is>
+          <t>['animal-protein', 'arabic', 'ethnic', 'lunches-and-dinners', 'oil-free', 'weight-loss']</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
           <t>oil_free</t>
         </is>
       </c>
-      <c r="K12" t="inlineStr">
+      <c r="L12" t="inlineStr">
         <is>
           <t>plant_based</t>
         </is>
       </c>
-      <c r="L12" t="inlineStr">
+      <c r="M12" t="inlineStr">
         <is>
           <t>Savory</t>
         </is>
       </c>
-      <c r="M12" t="inlineStr">
+      <c r="N12" t="inlineStr">
         <is>
           <t>weight_loss</t>
         </is>
       </c>
-      <c r="N12" t="b">
-        <v>0</v>
-      </c>
       <c r="O12" t="b">
         <v>0</v>
       </c>
-      <c r="P12" t="inlineStr"/>
-      <c r="Q12" t="inlineStr">
+      <c r="P12" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q12" t="inlineStr"/>
+      <c r="R12" t="inlineStr">
         <is>
           <t>hot</t>
         </is>
       </c>
-      <c r="R12" t="n">
-        <v>0</v>
-      </c>
-      <c r="S12" t="inlineStr"/>
-      <c r="T12" t="inlineStr">
+      <c r="S12" t="n">
+        <v>0</v>
+      </c>
+      <c r="T12" t="inlineStr"/>
+      <c r="U12" t="inlineStr">
         <is>
           <t>1. In a large pot, combine the sliced onion and garlic with chicken broth; bring to a boil.
 2. Add chicken thighs, tomato, raisins, and all spices (cumin, coriander, cinnamon, turmeric, cardamom), then season with salt and pepper.
@@ -1635,8 +1695,8 @@
 7. Cook time: 30</t>
         </is>
       </c>
-      <c r="U12" t="inlineStr"/>
-      <c r="V12" t="inlineStr">
+      <c r="V12" t="inlineStr"/>
+      <c r="W12" t="inlineStr">
         <is>
           <t>['In a large pot, combine the sliced onion and garlic with chicken broth; bring to a boil.', 'Add chicken thighs, tomato, raisins, and all spices (cumin, coriander, cinnamon, turmeric, cardamom), then season with salt and pepper.', 'Cover and simmer for 25–30 minutes until the chicken is tender and infused with spices.', 'Remove the chicken; stir in the basmati rice into the broth. Cover and cook on low heat for 15–20 minutes until rice is tender.', 'Shred or chop the chicken and return it to the pot. Stir in lemon juice and adjust seasoning as needed.', 'Garnish with fresh cilantro before serving.', 'Cook time: 30']</t>
         </is>
@@ -1660,10 +1720,15 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
+          <t>3323</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
           <t>['1 lb lean lamb stew meat, cut into 1 inch cubes', '2 cups basmati rice, rinsed', '4 cups low sodium lamb or vegetable broth', '1 large onion, chopped', '3 garlic cloves, minced', '1 tsp ground turmeric', '1 tsp ground cumin', '1/2 tsp ground cinnamon', '1/2 tsp ground coriander', '1 large tomato, diced', '1/2 cup chopped dried apricots', 'Salt and pepper, to taste', 'Juice of 1 lemon', 'Fresh parsley, chopped (for garnish)']</t>
         </is>
       </c>
-      <c r="E13" t="inlineStr">
+      <c r="F13" t="inlineStr">
         <is>
           <t>1. In a heavy pot, combine lamb cubes, chopped onion, garlic, tomato, apricots, and spices.
 2. Pour in broth and bring to a boil; then cover and simmer on low heat for 1–1½ hours until the lamb is tender.
@@ -1672,59 +1737,59 @@
 5. Cook time: 1</t>
         </is>
       </c>
-      <c r="F13" t="inlineStr">
+      <c r="G13" t="inlineStr">
         <is>
           <t>{"calories": 520, "protein": "34 g", "carbs": "60 g", "fiber": "8 g", "fat": "10 g"}</t>
         </is>
       </c>
-      <c r="G13" t="n">
+      <c r="H13" t="n">
         <v>4</v>
       </c>
-      <c r="H13" t="n">
+      <c r="I13" t="n">
         <v>25</v>
       </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>['weight-loss', 'plant-based', 'whole-foods', 'oil-free', 'lunches-and-dinners', 'soups', 'salads', 'wraps', 'sandwiches', 'rice', 'stews', 'stir-fry', 'seafood', 'ethnic', 'arabic', 'desserts']</t>
-        </is>
-      </c>
       <c r="J13" t="inlineStr">
         <is>
+          <t>['animal-protein', 'arabic', 'ethnic', 'lunches-and-dinners', 'oil-free', 'weight-loss']</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
           <t>oil_free</t>
         </is>
       </c>
-      <c r="K13" t="inlineStr">
+      <c r="L13" t="inlineStr">
         <is>
           <t>plant_based</t>
         </is>
       </c>
-      <c r="L13" t="inlineStr">
+      <c r="M13" t="inlineStr">
         <is>
           <t>Savory</t>
         </is>
       </c>
-      <c r="M13" t="inlineStr">
+      <c r="N13" t="inlineStr">
         <is>
           <t>weight_loss</t>
         </is>
       </c>
-      <c r="N13" t="b">
-        <v>0</v>
-      </c>
       <c r="O13" t="b">
         <v>0</v>
       </c>
-      <c r="P13" t="inlineStr"/>
-      <c r="Q13" t="inlineStr">
+      <c r="P13" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q13" t="inlineStr"/>
+      <c r="R13" t="inlineStr">
         <is>
           <t>hot</t>
         </is>
       </c>
-      <c r="R13" t="n">
-        <v>0</v>
-      </c>
-      <c r="S13" t="inlineStr"/>
-      <c r="T13" t="inlineStr">
+      <c r="S13" t="n">
+        <v>0</v>
+      </c>
+      <c r="T13" t="inlineStr"/>
+      <c r="U13" t="inlineStr">
         <is>
           <t>1. In a heavy pot, combine lamb cubes, chopped onion, garlic, tomato, apricots, and spices.
 2. Pour in broth and bring to a boil; then cover and simmer on low heat for 1–1½ hours until the lamb is tender.
@@ -1733,8 +1798,8 @@
 5. Cook time: 1</t>
         </is>
       </c>
-      <c r="U13" t="inlineStr"/>
-      <c r="V13" t="inlineStr">
+      <c r="V13" t="inlineStr"/>
+      <c r="W13" t="inlineStr">
         <is>
           <t>['In a heavy pot, combine lamb cubes, chopped onion, garlic, tomato, apricots, and spices.', 'Pour in broth and bring to a boil; then cover and simmer on low heat for 1–1½ hours until the lamb is tender.', 'Stir in the basmati rice; cover and cook for an additional 20 minutes until rice is fully cooked.', 'Stir in lemon juice, adjust seasoning, and garnish with chopped parsley before serving.', 'Cook time: 1']</t>
         </is>
@@ -1758,10 +1823,15 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
+          <t>3324</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
           <t>['1 lb chicken legs or thighs (skin removed)', '2 cups basmati rice, rinsed', '4 cups low sodium chicken broth', '1 large onion, sliced', '3 garlic cloves, minced', '1 tsp ground cumin', '1 tsp ground coriander', '1/2 tsp ground turmeric', '1/2 tsp ground cinnamon', 'Salt and pepper, to taste', 'Juice of 1 lemon', 'Fresh cilantro, chopped (for garnish)']</t>
         </is>
       </c>
-      <c r="E14" t="inlineStr">
+      <c r="F14" t="inlineStr">
         <is>
           <t>1. Season the chicken with salt, pepper, and half of the spices (cumin, coriander, turmeric, cinnamon).
 2. In a large pot, place the chicken, onion, garlic, and chicken broth; bring to a boil and then simmer for 30 minutes until the chicken is tender.
@@ -1771,59 +1841,59 @@
 6. Cook time: 50</t>
         </is>
       </c>
-      <c r="F14" t="inlineStr">
+      <c r="G14" t="inlineStr">
         <is>
           <t>{"calories": 520, "protein": "36 g", "carbs": "60 g", "fiber": "7 g", "fat": "8 g"}</t>
         </is>
       </c>
-      <c r="G14" t="n">
+      <c r="H14" t="n">
         <v>4</v>
       </c>
-      <c r="H14" t="n">
+      <c r="I14" t="n">
         <v>25</v>
       </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>['weight-loss', 'plant-based', 'whole-foods', 'oil-free', 'lunches-and-dinners', 'soups', 'salads', 'wraps', 'sandwiches', 'rice', 'stews', 'stir-fry', 'seafood', 'ethnic', 'arabic', 'desserts']</t>
-        </is>
-      </c>
       <c r="J14" t="inlineStr">
         <is>
+          <t>['animal-protein', 'arabic', 'ethnic', 'lunches-and-dinners', 'oil-free', 'weight-loss']</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
           <t>oil_free</t>
         </is>
       </c>
-      <c r="K14" t="inlineStr">
+      <c r="L14" t="inlineStr">
         <is>
           <t>plant_based</t>
         </is>
       </c>
-      <c r="L14" t="inlineStr">
+      <c r="M14" t="inlineStr">
         <is>
           <t>Savory</t>
         </is>
       </c>
-      <c r="M14" t="inlineStr">
+      <c r="N14" t="inlineStr">
         <is>
           <t>weight_loss</t>
         </is>
       </c>
-      <c r="N14" t="b">
-        <v>0</v>
-      </c>
       <c r="O14" t="b">
         <v>0</v>
       </c>
-      <c r="P14" t="inlineStr"/>
-      <c r="Q14" t="inlineStr">
+      <c r="P14" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q14" t="inlineStr"/>
+      <c r="R14" t="inlineStr">
         <is>
           <t>hot</t>
         </is>
       </c>
-      <c r="R14" t="n">
-        <v>0</v>
-      </c>
-      <c r="S14" t="inlineStr"/>
-      <c r="T14" t="inlineStr">
+      <c r="S14" t="n">
+        <v>0</v>
+      </c>
+      <c r="T14" t="inlineStr"/>
+      <c r="U14" t="inlineStr">
         <is>
           <t>1. Season the chicken with salt, pepper, and half of the spices (cumin, coriander, turmeric, cinnamon).
 2. In a large pot, place the chicken, onion, garlic, and chicken broth; bring to a boil and then simmer for 30 minutes until the chicken is tender.
@@ -1833,8 +1903,8 @@
 6. Cook time: 50</t>
         </is>
       </c>
-      <c r="U14" t="inlineStr"/>
-      <c r="V14" t="inlineStr">
+      <c r="V14" t="inlineStr"/>
+      <c r="W14" t="inlineStr">
         <is>
           <t>['Season the chicken with salt, pepper, and half of the spices (cumin, coriander, turmeric, cinnamon).', 'In a large pot, place the chicken, onion, garlic, and chicken broth; bring to a boil and then simmer for 30 minutes until the chicken is tender.', 'Remove the chicken; stir basmati rice into the broth along with any remaining spices. Cover and cook on low heat for 20 minutes until rice is tender.', 'Return the chicken to the pot, drizzle with lemon juice, and gently mix to combine.', 'Garnish with fresh cilantro before serving.', 'Cook time: 50']</t>
         </is>
@@ -1853,15 +1923,20 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Oil Free Stuffed Bell Peppers with Spiced Rice &amp; Ground Beef</t>
+          <t>Oil Free Stuffed Bell Peppers With Spiced Rice &amp; Ground Beef</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
+          <t>3325</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
           <t>['4 large bell peppers, tops cut off and seeded', '1 lb lean ground beef', '1 cup basmati rice, rinsed', '1 large tomato, diced', '1 small onion, finely chopped', '2 garlic cloves, minced', '1 tsp ground cumin', '1/2 tsp ground cinnamon', 'Salt and pepper, to taste', '2 cups low sodium beef broth', 'Fresh parsley, chopped (for garnish)']</t>
         </is>
       </c>
-      <c r="E15" t="inlineStr">
+      <c r="F15" t="inlineStr">
         <is>
           <t>1. In a skillet, sauté onion and garlic (using a splash of water) until softened. Add ground beef, cumin, cinnamon, salt, and pepper; cook until beef is browned.
 2. Stir in diced tomato and basmati rice, then add beef broth; bring to a simmer and cook for 10 minutes until rice begins to soften.
@@ -1871,59 +1946,59 @@
 6. Cook time: 35</t>
         </is>
       </c>
-      <c r="F15" t="inlineStr">
+      <c r="G15" t="inlineStr">
         <is>
           <t>{"calories": 540, "protein": "32 g", "carbs": "65 g", "fiber": "8 g", "fat": "10 g"}</t>
         </is>
       </c>
-      <c r="G15" t="n">
+      <c r="H15" t="n">
         <v>4</v>
       </c>
-      <c r="H15" t="n">
+      <c r="I15" t="n">
         <v>30</v>
       </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>['weight-loss', 'plant-based', 'whole-foods', 'oil-free', 'lunches-and-dinners', 'soups', 'salads', 'wraps', 'sandwiches', 'rice', 'stews', 'stir-fry', 'seafood', 'ethnic', 'arabic', 'desserts']</t>
-        </is>
-      </c>
       <c r="J15" t="inlineStr">
         <is>
+          <t>['animal-protein', 'arabic', 'ethnic', 'lunches-and-dinners', 'oil-free', 'rice', 'weight-loss']</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
           <t>oil_free</t>
         </is>
       </c>
-      <c r="K15" t="inlineStr">
+      <c r="L15" t="inlineStr">
         <is>
           <t>plant_based</t>
         </is>
       </c>
-      <c r="L15" t="inlineStr">
-        <is>
-          <t>Savory</t>
-        </is>
-      </c>
       <c r="M15" t="inlineStr">
         <is>
+          <t>Spicy</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr">
+        <is>
           <t>weight_loss</t>
         </is>
       </c>
-      <c r="N15" t="b">
-        <v>0</v>
-      </c>
       <c r="O15" t="b">
         <v>0</v>
       </c>
-      <c r="P15" t="inlineStr"/>
-      <c r="Q15" t="inlineStr">
+      <c r="P15" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q15" t="inlineStr"/>
+      <c r="R15" t="inlineStr">
         <is>
           <t>hot</t>
         </is>
       </c>
-      <c r="R15" t="n">
-        <v>0</v>
-      </c>
-      <c r="S15" t="inlineStr"/>
-      <c r="T15" t="inlineStr">
+      <c r="S15" t="n">
+        <v>0</v>
+      </c>
+      <c r="T15" t="inlineStr"/>
+      <c r="U15" t="inlineStr">
         <is>
           <t>1. In a skillet, sauté onion and garlic (using a splash of water) until softened. Add ground beef, cumin, cinnamon, salt, and pepper; cook until beef is browned.
 2. Stir in diced tomato and basmati rice, then add beef broth; bring to a simmer and cook for 10 minutes until rice begins to soften.
@@ -1933,8 +2008,8 @@
 6. Cook time: 35</t>
         </is>
       </c>
-      <c r="U15" t="inlineStr"/>
-      <c r="V15" t="inlineStr">
+      <c r="V15" t="inlineStr"/>
+      <c r="W15" t="inlineStr">
         <is>
           <t>['In a skillet, sauté onion and garlic (using a splash of water) until softened. Add ground beef, cumin, cinnamon, salt, and pepper; cook until beef is browned.', 'Stir in diced tomato and basmati rice, then add beef broth; bring to a simmer and cook for 10 minutes until rice begins to soften.', 'Stuff each bell pepper with the rice-beef mixture and place in a baking dish.', 'Cover with foil and bake at 375°F (190°C) for 30–35 minutes until peppers are tender.', 'Garnish with fresh parsley before serving.', 'Cook time: 35']</t>
         </is>
@@ -1953,15 +2028,20 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Oil Free Lamb Shawarma with Whole Wheat Flatbread</t>
+          <t>Oil Free Lamb Shawarma With Whole Wheat Flatbread</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
+          <t>3326</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
           <t>['1 lb lamb shoulder, thinly sliced', '2 tsp ground cumin', '2 tsp ground coriander', '1 tsp smoked paprika', '1/2 tsp ground turmeric', '1/2 tsp ground cinnamon', 'Juice of 1 lemon', '4 garlic cloves, minced', 'Salt and pepper, to taste', '4 whole wheat flatbreads', '1 cup diced tomatoes', '1 cup chopped lettuce', '1/2 cup thinly sliced red onions', '1/2 cup fat free plain yogurt (for sauce)', 'Fresh parsley, chopped (for garnish)']</t>
         </is>
       </c>
-      <c r="E16" t="inlineStr">
+      <c r="F16" t="inlineStr">
         <is>
           <t>1. In a bowl, combine lamb slices with cumin, coriander, paprika, turmeric, cinnamon, lemon juice, garlic, salt, and pepper. Marinate for at least 1 hour in the refrigerator.
 2. Grill the marinated lamb over medium-high heat for 5–7 minutes until cooked through.
@@ -1971,59 +2051,59 @@
 6. Cook time: 10</t>
         </is>
       </c>
-      <c r="F16" t="inlineStr">
+      <c r="G16" t="inlineStr">
         <is>
           <t>{"calories": 550, "protein": "38 g", "carbs": "60 g", "fiber": "7 g", "fat": "12 g"}</t>
         </is>
       </c>
-      <c r="G16" t="n">
+      <c r="H16" t="n">
         <v>4</v>
       </c>
-      <c r="H16" t="n">
+      <c r="I16" t="n">
         <v>25</v>
       </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>['weight-loss', 'plant-based', 'whole-foods', 'oil-free', 'lunches-and-dinners', 'soups', 'salads', 'wraps', 'sandwiches', 'rice', 'stews', 'stir-fry', 'seafood', 'ethnic', 'arabic', 'desserts']</t>
-        </is>
-      </c>
       <c r="J16" t="inlineStr">
         <is>
+          <t>['animal-protein', 'arabic', 'ethnic', 'lunches-and-dinners', 'oil-free', 'weight-loss']</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
           <t>oil_free</t>
         </is>
       </c>
-      <c r="K16" t="inlineStr">
+      <c r="L16" t="inlineStr">
         <is>
           <t>plant_based</t>
         </is>
       </c>
-      <c r="L16" t="inlineStr">
+      <c r="M16" t="inlineStr">
         <is>
           <t>Savory</t>
         </is>
       </c>
-      <c r="M16" t="inlineStr">
+      <c r="N16" t="inlineStr">
         <is>
           <t>weight_loss</t>
         </is>
       </c>
-      <c r="N16" t="b">
-        <v>0</v>
-      </c>
       <c r="O16" t="b">
         <v>0</v>
       </c>
-      <c r="P16" t="inlineStr"/>
-      <c r="Q16" t="inlineStr">
+      <c r="P16" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q16" t="inlineStr"/>
+      <c r="R16" t="inlineStr">
         <is>
           <t>hot</t>
         </is>
       </c>
-      <c r="R16" t="n">
-        <v>0</v>
-      </c>
-      <c r="S16" t="inlineStr"/>
-      <c r="T16" t="inlineStr">
+      <c r="S16" t="n">
+        <v>0</v>
+      </c>
+      <c r="T16" t="inlineStr"/>
+      <c r="U16" t="inlineStr">
         <is>
           <t>1. In a bowl, combine lamb slices with cumin, coriander, paprika, turmeric, cinnamon, lemon juice, garlic, salt, and pepper. Marinate for at least 1 hour in the refrigerator.
 2. Grill the marinated lamb over medium-high heat for 5–7 minutes until cooked through.
@@ -2033,8 +2113,8 @@
 6. Cook time: 10</t>
         </is>
       </c>
-      <c r="U16" t="inlineStr"/>
-      <c r="V16" t="inlineStr">
+      <c r="V16" t="inlineStr"/>
+      <c r="W16" t="inlineStr">
         <is>
           <t>['In a bowl, combine lamb slices with cumin, coriander, paprika, turmeric, cinnamon, lemon juice, garlic, salt, and pepper. Marinate for at least 1 hour in the refrigerator.', 'Grill the marinated lamb over medium-high heat for 5–7 minutes until cooked through.', 'Warm the flatbreads on a dry skillet for 1–2 minutes per side.', 'Assemble wraps by layering flatbread with lettuce, tomatoes, onions, and grilled lamb; drizzle with yogurt and garnish with parsley.', 'Roll up tightly and serve.', 'Cook time: 10']</t>
         </is>
@@ -2053,15 +2133,20 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Oil Free Beef  Tagine with Apricots</t>
+          <t>Oil Free Beef  Tagine With Apricots</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
+          <t>3327</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
           <t>['1 lb lean beef stew meat, cut into 1 inch cubes', '1 large onion, chopped', '2 garlic cloves, minced', '1 tsp ground cumin', '1 tsp ground coriander', '1/2 tsp ground cinnamon', '1/2 cup dried apricots, chopped', '1 large tomato, diced', '2 cups low sodium beef broth', 'Salt and pepper, to taste', 'Fresh cilantro, chopped (for garnish)']</t>
         </is>
       </c>
-      <c r="E17" t="inlineStr">
+      <c r="F17" t="inlineStr">
         <is>
           <t>1. In a heavy pot, combine beef, onion, garlic, cumin, coriander, cinnamon, salt, and pepper.
 2. Add chopped tomato, dried apricots, and beef broth.
@@ -2070,59 +2155,59 @@
 5. Cook time: 1</t>
         </is>
       </c>
-      <c r="F17" t="inlineStr">
+      <c r="G17" t="inlineStr">
         <is>
           <t>{"calories": 520, "protein": "38 g", "carbs": "50 g", "fiber": "8 g", "fat": "12 g"}</t>
         </is>
       </c>
-      <c r="G17" t="n">
+      <c r="H17" t="n">
         <v>4</v>
       </c>
-      <c r="H17" t="n">
+      <c r="I17" t="n">
         <v>20</v>
       </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>['weight-loss', 'plant-based', 'whole-foods', 'oil-free', 'lunches-and-dinners', 'soups', 'salads', 'wraps', 'sandwiches', 'rice', 'stews', 'stir-fry', 'seafood', 'ethnic', 'arabic', 'desserts']</t>
-        </is>
-      </c>
       <c r="J17" t="inlineStr">
         <is>
+          <t>['animal-protein', 'arabic', 'ethnic', 'lunches-and-dinners', 'oil-free', 'weight-loss']</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
           <t>oil_free</t>
         </is>
       </c>
-      <c r="K17" t="inlineStr">
+      <c r="L17" t="inlineStr">
         <is>
           <t>plant_based</t>
         </is>
       </c>
-      <c r="L17" t="inlineStr">
+      <c r="M17" t="inlineStr">
         <is>
           <t>Savory</t>
         </is>
       </c>
-      <c r="M17" t="inlineStr">
+      <c r="N17" t="inlineStr">
         <is>
           <t>weight_loss</t>
         </is>
       </c>
-      <c r="N17" t="b">
-        <v>0</v>
-      </c>
       <c r="O17" t="b">
         <v>0</v>
       </c>
-      <c r="P17" t="inlineStr"/>
-      <c r="Q17" t="inlineStr">
+      <c r="P17" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q17" t="inlineStr"/>
+      <c r="R17" t="inlineStr">
         <is>
           <t>hot</t>
         </is>
       </c>
-      <c r="R17" t="n">
-        <v>0</v>
-      </c>
-      <c r="S17" t="inlineStr"/>
-      <c r="T17" t="inlineStr">
+      <c r="S17" t="n">
+        <v>0</v>
+      </c>
+      <c r="T17" t="inlineStr"/>
+      <c r="U17" t="inlineStr">
         <is>
           <t>1. In a heavy pot, combine beef, onion, garlic, cumin, coriander, cinnamon, salt, and pepper.
 2. Add chopped tomato, dried apricots, and beef broth.
@@ -2131,8 +2216,8 @@
 5. Cook time: 1</t>
         </is>
       </c>
-      <c r="U17" t="inlineStr"/>
-      <c r="V17" t="inlineStr">
+      <c r="V17" t="inlineStr"/>
+      <c r="W17" t="inlineStr">
         <is>
           <t>['In a heavy pot, combine beef, onion, garlic, cumin, coriander, cinnamon, salt, and pepper.', 'Add chopped tomato, dried apricots, and beef broth.', 'Bring to a boil, then reduce heat, cover, and simmer for 1–1½ hours until beef is tender and flavors meld.', 'Garnish with fresh cilantro before serving.', 'Cook time: 1']</t>
         </is>
@@ -2156,10 +2241,15 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
+          <t>3328</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
           <t>['1 lb boneless, skin less chicken thighs, cut into chunks', '1 cup jameed or plain unsweetened yogurt (prepared oil free)', '2 cups basmati rice, rinsed', '4 cups low sodium chicken broth', '1 large onion, thinly sliced', '2 garlic cloves, minced', '1 tsp ground cardamom', 'Salt and pepper, to taste', 'Fresh parsley, chopped (for garnish)']</t>
         </is>
       </c>
-      <c r="E18" t="inlineStr">
+      <c r="F18" t="inlineStr">
         <is>
           <t>1. In a pot, combine chicken broth, onion, garlic, cardamom, salt, and pepper; bring to a boil and add chicken chunks. Simmer for 25–30 minutes until chicken is tender.
 2. Meanwhile, cook basmati rice in a separate pot using a portion of the broth until fluffy.
@@ -2168,59 +2258,59 @@
 5. Cook time: 30</t>
         </is>
       </c>
-      <c r="F18" t="inlineStr">
+      <c r="G18" t="inlineStr">
         <is>
           <t>{"calories": 540, "protein": "36 g", "carbs": "60 g", "fiber": "7 g", "fat": "14 g"}</t>
         </is>
       </c>
-      <c r="G18" t="n">
+      <c r="H18" t="n">
         <v>4</v>
       </c>
-      <c r="H18" t="n">
+      <c r="I18" t="n">
         <v>20</v>
       </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>['weight-loss', 'plant-based', 'whole-foods', 'oil-free', 'lunches-and-dinners', 'soups', 'salads', 'wraps', 'sandwiches', 'rice', 'stews', 'stir-fry', 'seafood', 'ethnic', 'arabic', 'desserts']</t>
-        </is>
-      </c>
       <c r="J18" t="inlineStr">
         <is>
+          <t>['animal-protein', 'arabic', 'ethnic', 'lunches-and-dinners', 'oil-free', 'weight-loss']</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
           <t>oil_free</t>
         </is>
       </c>
-      <c r="K18" t="inlineStr">
+      <c r="L18" t="inlineStr">
         <is>
           <t>plant_based</t>
         </is>
       </c>
-      <c r="L18" t="inlineStr">
+      <c r="M18" t="inlineStr">
         <is>
           <t>Savory</t>
         </is>
       </c>
-      <c r="M18" t="inlineStr">
+      <c r="N18" t="inlineStr">
         <is>
           <t>weight_loss</t>
         </is>
       </c>
-      <c r="N18" t="b">
-        <v>0</v>
-      </c>
       <c r="O18" t="b">
         <v>0</v>
       </c>
-      <c r="P18" t="inlineStr"/>
-      <c r="Q18" t="inlineStr">
+      <c r="P18" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q18" t="inlineStr"/>
+      <c r="R18" t="inlineStr">
         <is>
           <t>hot</t>
         </is>
       </c>
-      <c r="R18" t="n">
-        <v>0</v>
-      </c>
-      <c r="S18" t="inlineStr"/>
-      <c r="T18" t="inlineStr">
+      <c r="S18" t="n">
+        <v>0</v>
+      </c>
+      <c r="T18" t="inlineStr"/>
+      <c r="U18" t="inlineStr">
         <is>
           <t>1. In a pot, combine chicken broth, onion, garlic, cardamom, salt, and pepper; bring to a boil and add chicken chunks. Simmer for 25–30 minutes until chicken is tender.
 2. Meanwhile, cook basmati rice in a separate pot using a portion of the broth until fluffy.
@@ -2229,8 +2319,8 @@
 5. Cook time: 30</t>
         </is>
       </c>
-      <c r="U18" t="inlineStr"/>
-      <c r="V18" t="inlineStr">
+      <c r="V18" t="inlineStr"/>
+      <c r="W18" t="inlineStr">
         <is>
           <t>['In a pot, combine chicken broth, onion, garlic, cardamom, salt, and pepper; bring to a boil and add chicken chunks. Simmer for 25–30 minutes until chicken is tender.', 'Meanwhile, cook basmati rice in a separate pot using a portion of the broth until fluffy.', 'Stir the yogurt (or prepared jameed) into the remaining broth off the heat to create a tangy sauce.', 'Serve the chicken over rice and generously spoon the yogurt sauce over the top. Garnish with fresh parsley.', 'Cook time: 30']</t>
         </is>
@@ -2254,10 +2344,15 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
+          <t>3329</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
           <t>['1 cup semolina', '1/2 cup whole wheat flour', '1 tsp baking powder', '1/2 tsp baking soda', '1/4 tsp salt', '1 cup pitted dates, finely chopped', '1/2 cup unsweetened applesauce', '1/2 cup low fat milk (or plant based milk)', '1/4 cup honey or maple syrup', '1 tsp ground cinnamon', '1/2 tsp ground cardamom', '1 tsp vanilla extract', '1/4 cup chopped walnuts (optional, for garnish)']</t>
         </is>
       </c>
-      <c r="E19" t="inlineStr">
+      <c r="F19" t="inlineStr">
         <is>
           <t>1. Preheat oven to 350°F (175°C). Grease a loaf pan lightly with water or nonstick spray.
 2. In a bowl, whisk together semolina, whole wheat flour, baking powder, baking soda, salt, cinnamon, and cardamom.
@@ -2269,59 +2364,59 @@
 8. Cook time: 50</t>
         </is>
       </c>
-      <c r="F19" t="inlineStr">
+      <c r="G19" t="inlineStr">
         <is>
           <t>{"calories": 180, "protein": "5 g", "carbs": "32 g", "fiber": "4 g", "fat": "3 g"}</t>
         </is>
       </c>
-      <c r="G19" t="n">
+      <c r="H19" t="n">
         <v>10</v>
       </c>
-      <c r="H19" t="n">
+      <c r="I19" t="n">
         <v>20</v>
       </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>['weight-loss', 'plant-based', 'whole-foods', 'oil-free', 'lunches-and-dinners', 'soups', 'salads', 'wraps', 'sandwiches', 'rice', 'stews', 'stir-fry', 'seafood', 'ethnic', 'arabic', 'desserts']</t>
-        </is>
-      </c>
       <c r="J19" t="inlineStr">
         <is>
+          <t>['arabic', 'desserts', 'ethnic', 'oil-free', 'vegetarian', 'weight-loss']</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
           <t>oil_free</t>
         </is>
       </c>
-      <c r="K19" t="inlineStr">
-        <is>
-          <t>plant_based</t>
-        </is>
-      </c>
       <c r="L19" t="inlineStr">
         <is>
+          <t>Vegetarian</t>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr">
+        <is>
           <t>Savory</t>
         </is>
       </c>
-      <c r="M19" t="inlineStr">
+      <c r="N19" t="inlineStr">
         <is>
           <t>weight_loss</t>
         </is>
       </c>
-      <c r="N19" t="b">
-        <v>0</v>
-      </c>
       <c r="O19" t="b">
         <v>0</v>
       </c>
-      <c r="P19" t="inlineStr"/>
-      <c r="Q19" t="inlineStr">
+      <c r="P19" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q19" t="inlineStr"/>
+      <c r="R19" t="inlineStr">
         <is>
           <t>hot</t>
         </is>
       </c>
-      <c r="R19" t="n">
-        <v>0</v>
-      </c>
-      <c r="S19" t="inlineStr"/>
-      <c r="T19" t="inlineStr">
+      <c r="S19" t="n">
+        <v>0</v>
+      </c>
+      <c r="T19" t="inlineStr"/>
+      <c r="U19" t="inlineStr">
         <is>
           <t>1. Preheat oven to 350°F (175°C). Grease a loaf pan lightly with water or nonstick spray.
 2. In a bowl, whisk together semolina, whole wheat flour, baking powder, baking soda, salt, cinnamon, and cardamom.
@@ -2333,8 +2428,8 @@
 8. Cook time: 50</t>
         </is>
       </c>
-      <c r="U19" t="inlineStr"/>
-      <c r="V19" t="inlineStr">
+      <c r="V19" t="inlineStr"/>
+      <c r="W19" t="inlineStr">
         <is>
           <t>['Preheat oven to 350°F (175°C). Grease a loaf pan lightly with water or nonstick spray.', 'In a bowl, whisk together semolina, whole wheat flour, baking powder, baking soda, salt, cinnamon, and cardamom.', 'In another bowl, mix applesauce, milk, honey (or maple syrup), and vanilla extract until well combined.', 'Stir the wet ingredients into the dry; fold in chopped dates.', 'Pour the batter into the prepared pan and smooth the top.', 'Bake for 45–50 minutes until a toothpick inserted into the center comes out clean.', 'Let cool in the pan for 10 minutes, then transfer to a wire rack. Garnish with walnuts if desired, and slice to serve.', 'Cook time: 50']</t>
         </is>
@@ -2358,10 +2453,15 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
+          <t>3330</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
           <t>['1 lb boneless, skin less chicken breast, cut into 1 inch cubes', '2 tsp ground cumin', '2 tsp ground coriander', '1 tsp smoked paprika', 'Juice of 1 lemon', '4 garlic cloves, minced', 'Salt and pepper, to taste', '1 large tomato, cut into wedges', '1 red onion, cut into wedges', '1/2 cup chopped fresh parsley (for garnish)', 'Lemon wedges, for serving']</t>
         </is>
       </c>
-      <c r="E20" t="inlineStr">
+      <c r="F20" t="inlineStr">
         <is>
           <t>1. In a bowl, combine chicken cubes with minced garlic, lemon juice, cumin, coriander, paprika, salt, and pepper. Toss to coat well.
 2. Thread the marinated chicken onto skewers.
@@ -2371,59 +2471,59 @@
 6. Cook time: 10</t>
         </is>
       </c>
-      <c r="F20" t="inlineStr">
+      <c r="G20" t="inlineStr">
         <is>
           <t>{"calories": 430, "protein": "38 g", "carbs": "35 g", "fiber": "5 g", "fat": "6 g"}</t>
         </is>
       </c>
-      <c r="G20" t="n">
+      <c r="H20" t="n">
         <v>4</v>
       </c>
-      <c r="H20" t="n">
+      <c r="I20" t="n">
         <v>20</v>
       </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>['weight-loss', 'plant-based', 'whole-foods', 'oil-free', 'lunches-and-dinners', 'soups', 'salads', 'wraps', 'sandwiches', 'rice', 'stews', 'stir-fry', 'seafood', 'ethnic', 'arabic', 'desserts']</t>
-        </is>
-      </c>
       <c r="J20" t="inlineStr">
         <is>
+          <t>['animal-protein', 'arabic', 'ethnic', 'lunches-and-dinners', 'oil-free', 'weight-loss']</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
           <t>oil_free</t>
         </is>
       </c>
-      <c r="K20" t="inlineStr">
+      <c r="L20" t="inlineStr">
         <is>
           <t>plant_based</t>
         </is>
       </c>
-      <c r="L20" t="inlineStr">
+      <c r="M20" t="inlineStr">
         <is>
           <t>Savory</t>
         </is>
       </c>
-      <c r="M20" t="inlineStr">
+      <c r="N20" t="inlineStr">
         <is>
           <t>weight_loss</t>
         </is>
       </c>
-      <c r="N20" t="b">
-        <v>0</v>
-      </c>
       <c r="O20" t="b">
         <v>0</v>
       </c>
-      <c r="P20" t="inlineStr"/>
-      <c r="Q20" t="inlineStr">
+      <c r="P20" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q20" t="inlineStr"/>
+      <c r="R20" t="inlineStr">
         <is>
           <t>hot</t>
         </is>
       </c>
-      <c r="R20" t="n">
-        <v>0</v>
-      </c>
-      <c r="S20" t="inlineStr"/>
-      <c r="T20" t="inlineStr">
+      <c r="S20" t="n">
+        <v>0</v>
+      </c>
+      <c r="T20" t="inlineStr"/>
+      <c r="U20" t="inlineStr">
         <is>
           <t>1. In a bowl, combine chicken cubes with minced garlic, lemon juice, cumin, coriander, paprika, salt, and pepper. Toss to coat well.
 2. Thread the marinated chicken onto skewers.
@@ -2433,8 +2533,8 @@
 6. Cook time: 10</t>
         </is>
       </c>
-      <c r="U20" t="inlineStr"/>
-      <c r="V20" t="inlineStr">
+      <c r="V20" t="inlineStr"/>
+      <c r="W20" t="inlineStr">
         <is>
           <t>['In a bowl, combine chicken cubes with minced garlic, lemon juice, cumin, coriander, paprika, salt, and pepper. Toss to coat well.', 'Thread the marinated chicken onto skewers.', 'Preheat a grill or grill pan over medium high heat; grill the skewers for about 8–10 minutes, turning occasionally, until the chicken is cooked through and lightly charred.', 'Arrange the chicken skewers on a plate alongside tomato and onion wedges.', 'Garnish with chopped parsley and serve with additional lemon wedges.', 'Cook time: 10']</t>
         </is>
@@ -2453,15 +2553,20 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Oil Free Lamb Kebabs with Quinoa Pilaf</t>
+          <t>Oil Free Lamb Kebabs With Quinoa Pilaf</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
+          <t>3331</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
           <t>['1 lb lean lamb stew meat, cut into 1 inch cubes', '1 tsp ground cumin', '1 tsp ground coriander', '1/2 tsp ground allspice', '1/4 tsp cayenne pepper (optional)', 'Salt and pepper, to taste', '1 cup quinoa, rinsed', '2 cups low sodium vegetable broth', '1/2 cup chopped fresh parsley', 'Juice of 1 lemon']</t>
         </is>
       </c>
-      <c r="E21" t="inlineStr">
+      <c r="F21" t="inlineStr">
         <is>
           <t>1. In a bowl, toss lamb cubes with cumin, coriander, allspice, cayenne (if using), salt, and pepper.
 2. Thread the lamb onto skewers. Preheat a grill or grill pan over medium high heat and grill for 8–10 minutes, turning to ensure even cooking.
@@ -2470,59 +2575,59 @@
 5. Cook time: 20</t>
         </is>
       </c>
-      <c r="F21" t="inlineStr">
+      <c r="G21" t="inlineStr">
         <is>
           <t>{"calories": 500, "protein": "35 g", "carbs": "55 g", "fiber": "8 g", "fat": "10 g"}</t>
         </is>
       </c>
-      <c r="G21" t="n">
+      <c r="H21" t="n">
         <v>4</v>
       </c>
-      <c r="H21" t="n">
+      <c r="I21" t="n">
         <v>25</v>
       </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>['weight-loss', 'plant-based', 'whole-foods', 'oil-free', 'lunches-and-dinners', 'soups', 'salads', 'wraps', 'sandwiches', 'rice', 'stews', 'stir-fry', 'seafood', 'ethnic', 'arabic', 'desserts']</t>
-        </is>
-      </c>
       <c r="J21" t="inlineStr">
         <is>
+          <t>['animal-protein', 'arabic', 'ethnic', 'lunches-and-dinners', 'oil-free', 'rice', 'weight-loss']</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
           <t>oil_free</t>
         </is>
       </c>
-      <c r="K21" t="inlineStr">
+      <c r="L21" t="inlineStr">
         <is>
           <t>plant_based</t>
         </is>
       </c>
-      <c r="L21" t="inlineStr">
+      <c r="M21" t="inlineStr">
         <is>
           <t>Savory</t>
         </is>
       </c>
-      <c r="M21" t="inlineStr">
+      <c r="N21" t="inlineStr">
         <is>
           <t>weight_loss</t>
         </is>
       </c>
-      <c r="N21" t="b">
-        <v>0</v>
-      </c>
       <c r="O21" t="b">
         <v>0</v>
       </c>
-      <c r="P21" t="inlineStr"/>
-      <c r="Q21" t="inlineStr">
+      <c r="P21" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q21" t="inlineStr"/>
+      <c r="R21" t="inlineStr">
         <is>
           <t>hot</t>
         </is>
       </c>
-      <c r="R21" t="n">
-        <v>0</v>
-      </c>
-      <c r="S21" t="inlineStr"/>
-      <c r="T21" t="inlineStr">
+      <c r="S21" t="n">
+        <v>0</v>
+      </c>
+      <c r="T21" t="inlineStr"/>
+      <c r="U21" t="inlineStr">
         <is>
           <t>1. In a bowl, toss lamb cubes with cumin, coriander, allspice, cayenne (if using), salt, and pepper.
 2. Thread the lamb onto skewers. Preheat a grill or grill pan over medium high heat and grill for 8–10 minutes, turning to ensure even cooking.
@@ -2531,8 +2636,8 @@
 5. Cook time: 20</t>
         </is>
       </c>
-      <c r="U21" t="inlineStr"/>
-      <c r="V21" t="inlineStr">
+      <c r="V21" t="inlineStr"/>
+      <c r="W21" t="inlineStr">
         <is>
           <t>['In a bowl, toss lamb cubes with cumin, coriander, allspice, cayenne (if using), salt, and pepper.', 'Thread the lamb onto skewers. Preheat a grill or grill pan over medium high heat and grill for 8–10 minutes, turning to ensure even cooking.', 'Meanwhile, bring the vegetable broth to a boil; add quinoa, cover, and simmer for 15 minutes until tender. Fluff with a fork, then stir in chopped parsley and lemon juice.', 'Serve the grilled lamb kebabs over a bed of quinoa pilaf.', 'Cook time: 20']</t>
         </is>
@@ -2556,10 +2661,15 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
+          <t>3332</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
           <t>['1 lb chicken thighs (bone in, skin removed)', '1 large onion, thinly sliced', '2 tsp sumac', '1 tsp ground allspice', 'Juice of 1 lemon', 'Salt and pepper, to taste', '4 whole wheat flatbreads', '1/2 cup chopped fresh parsley']</t>
         </is>
       </c>
-      <c r="E22" t="inlineStr">
+      <c r="F22" t="inlineStr">
         <is>
           <t>1. Season chicken thighs with salt, pepper, sumac, allspice, and lemon juice.
 2. Place chicken and sliced onions in a baking dish; cover and bake at 375°F (190°C) for 35–40 minutes until chicken is tender and onions are caramelized.
@@ -2569,59 +2679,59 @@
 6. Cook time: 40</t>
         </is>
       </c>
-      <c r="F22" t="inlineStr">
+      <c r="G22" t="inlineStr">
         <is>
           <t>{"calories": 480, "protein": "32 g", "carbs": "55 g", "fiber": "6 g", "fat": "8 g"}</t>
         </is>
       </c>
-      <c r="G22" t="n">
+      <c r="H22" t="n">
         <v>4</v>
       </c>
-      <c r="H22" t="n">
+      <c r="I22" t="n">
         <v>20</v>
       </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>['weight-loss', 'plant-based', 'whole-foods', 'oil-free', 'lunches-and-dinners', 'soups', 'salads', 'wraps', 'sandwiches', 'rice', 'stews', 'stir-fry', 'seafood', 'ethnic', 'arabic', 'desserts']</t>
-        </is>
-      </c>
       <c r="J22" t="inlineStr">
         <is>
+          <t>['animal-protein', 'arabic', 'ethnic', 'lunches-and-dinners', 'oil-free', 'weight-loss']</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
           <t>oil_free</t>
         </is>
       </c>
-      <c r="K22" t="inlineStr">
+      <c r="L22" t="inlineStr">
         <is>
           <t>plant_based</t>
         </is>
       </c>
-      <c r="L22" t="inlineStr">
+      <c r="M22" t="inlineStr">
         <is>
           <t>Savory</t>
         </is>
       </c>
-      <c r="M22" t="inlineStr">
+      <c r="N22" t="inlineStr">
         <is>
           <t>weight_loss</t>
         </is>
       </c>
-      <c r="N22" t="b">
-        <v>0</v>
-      </c>
       <c r="O22" t="b">
         <v>0</v>
       </c>
-      <c r="P22" t="inlineStr"/>
-      <c r="Q22" t="inlineStr">
+      <c r="P22" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q22" t="inlineStr"/>
+      <c r="R22" t="inlineStr">
         <is>
           <t>hot</t>
         </is>
       </c>
-      <c r="R22" t="n">
-        <v>0</v>
-      </c>
-      <c r="S22" t="inlineStr"/>
-      <c r="T22" t="inlineStr">
+      <c r="S22" t="n">
+        <v>0</v>
+      </c>
+      <c r="T22" t="inlineStr"/>
+      <c r="U22" t="inlineStr">
         <is>
           <t>1. Season chicken thighs with salt, pepper, sumac, allspice, and lemon juice.
 2. Place chicken and sliced onions in a baking dish; cover and bake at 375°F (190°C) for 35–40 minutes until chicken is tender and onions are caramelized.
@@ -2631,8 +2741,8 @@
 6. Cook time: 40</t>
         </is>
       </c>
-      <c r="U22" t="inlineStr"/>
-      <c r="V22" t="inlineStr">
+      <c r="V22" t="inlineStr"/>
+      <c r="W22" t="inlineStr">
         <is>
           <t>['Season chicken thighs with salt, pepper, sumac, allspice, and lemon juice.', 'Place chicken and sliced onions in a baking dish; cover and bake at 375°F (190°C) for 35–40 minutes until chicken is tender and onions are caramelized.', 'Warm the flatbreads in a dry skillet.', 'To serve, place a flatbread on a plate, layer with shredded chicken and onions, and sprinkle with fresh parsley.', 'Roll or fold and serve immediately.', 'Cook time: 40']</t>
         </is>
@@ -2651,15 +2761,20 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Oil Free Stuffed Eggplant with Ground Beef &amp; Rice</t>
+          <t>Oil Free Stuffed Eggplant With Ground Beef &amp; Rice</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
+          <t>3333</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
           <t>['2 medium eggplants, halved lengthwise', '1 lb lean ground beef', '1 cup cooked basmati rice', '1 large tomato, diced', '1 small onion, finely chopped', '2 garlic cloves, minced', '1 tsp ground cumin', '1/2 tsp ground cinnamon', 'Salt and pepper, to taste', '1/4 cup chopped fresh parsley']</t>
         </is>
       </c>
-      <c r="E23" t="inlineStr">
+      <c r="F23" t="inlineStr">
         <is>
           <t>1. Preheat oven to 400°F (200°C).
 2. Scoop out some flesh from the eggplant halves, leaving a 1/2 inch border. Chop the removed flesh and set aside.
@@ -2670,59 +2785,59 @@
 7. Cook time: 35</t>
         </is>
       </c>
-      <c r="F23" t="inlineStr">
+      <c r="G23" t="inlineStr">
         <is>
           <t>{"calories": 510, "protein": "35 g", "carbs": "60 g", "fiber": "8 g", "fat": "10 g"}</t>
         </is>
       </c>
-      <c r="G23" t="n">
+      <c r="H23" t="n">
         <v>4</v>
       </c>
-      <c r="H23" t="n">
+      <c r="I23" t="n">
         <v>30</v>
       </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>['weight-loss', 'plant-based', 'whole-foods', 'oil-free', 'lunches-and-dinners', 'soups', 'salads', 'wraps', 'sandwiches', 'rice', 'stews', 'stir-fry', 'seafood', 'ethnic', 'arabic', 'desserts']</t>
-        </is>
-      </c>
       <c r="J23" t="inlineStr">
         <is>
+          <t>['animal-protein', 'arabic', 'ethnic', 'lunches-and-dinners', 'oil-free', 'rice', 'weight-loss']</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
           <t>oil_free</t>
         </is>
       </c>
-      <c r="K23" t="inlineStr">
+      <c r="L23" t="inlineStr">
         <is>
           <t>plant_based</t>
         </is>
       </c>
-      <c r="L23" t="inlineStr">
+      <c r="M23" t="inlineStr">
         <is>
           <t>Savory</t>
         </is>
       </c>
-      <c r="M23" t="inlineStr">
+      <c r="N23" t="inlineStr">
         <is>
           <t>weight_loss</t>
         </is>
       </c>
-      <c r="N23" t="b">
-        <v>0</v>
-      </c>
       <c r="O23" t="b">
         <v>0</v>
       </c>
-      <c r="P23" t="inlineStr"/>
-      <c r="Q23" t="inlineStr">
+      <c r="P23" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q23" t="inlineStr"/>
+      <c r="R23" t="inlineStr">
         <is>
           <t>hot</t>
         </is>
       </c>
-      <c r="R23" t="n">
-        <v>0</v>
-      </c>
-      <c r="S23" t="inlineStr"/>
-      <c r="T23" t="inlineStr">
+      <c r="S23" t="n">
+        <v>0</v>
+      </c>
+      <c r="T23" t="inlineStr"/>
+      <c r="U23" t="inlineStr">
         <is>
           <t>1. Preheat oven to 400°F (200°C).
 2. Scoop out some flesh from the eggplant halves, leaving a 1/2 inch border. Chop the removed flesh and set aside.
@@ -2733,8 +2848,8 @@
 7. Cook time: 35</t>
         </is>
       </c>
-      <c r="U23" t="inlineStr"/>
-      <c r="V23" t="inlineStr">
+      <c r="V23" t="inlineStr"/>
+      <c r="W23" t="inlineStr">
         <is>
           <t>['Preheat oven to 400°F (200°C).', 'Scoop out some flesh from the eggplant halves, leaving a 1/2 inch border. Chop the removed flesh and set aside.', 'In a skillet (using water if needed), sauté onion, garlic, and the chopped eggplant flesh until softened. Add ground beef, cumin, cinnamon, salt, and pepper; cook until beef is browned.', 'Stir in the cooked rice and diced tomato; mix well.', 'Spoon the mixture back into the eggplant halves, place in a baking dish, cover with foil, and bake for 35 minutes until eggplant is tender.', 'Garnish with fresh parsley before serving.', 'Cook time: 35']</t>
         </is>
@@ -2753,15 +2868,20 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Oil Free Baked Falafel Wrap with Grilled Chicken</t>
+          <t>Oil Free Baked Falafel Wrap With Grilled Chicken</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
+          <t>3334</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
           <t>['1 can (15 oz) chickpeas, drained and rinsed', '1 small onion, roughly chopped', '3 garlic cloves', '1/4 cup fresh parsley', '1/4 cup fresh cilantro', '2 tsp ground cumin', '1 tsp ground coriander', '1/2 tsp baking soda', 'Salt and pepper, to taste', '2 tbsp lemon juice', '2–3 tbsp water, as needed', '1 lb boneless, skin less chicken breast, grilled and sliced', '4 whole wheat pita breads', '1 cup chopped lettuce', '1/2 cup diced tomatoes', '1/2 cup fat free plain yogurt (for sauce)']</t>
         </is>
       </c>
-      <c r="E24" t="inlineStr">
+      <c r="F24" t="inlineStr">
         <is>
           <t>1. In a food processor, combine chickpeas, onion, garlic, parsley, cilantro, cumin, coriander, baking soda, lemon juice, salt, and pepper. Process until well blended but still slightly chunky; add water if needed.
 2. Form the mixture into small patties and bake on a parchment lined sheet at 400°F (200°C) for 20–25 minutes until golden.
@@ -2770,59 +2890,59 @@
 5. Cook time: 25</t>
         </is>
       </c>
-      <c r="F24" t="inlineStr">
+      <c r="G24" t="inlineStr">
         <is>
           <t>{"calories": 520, "protein": "32 g", "carbs": "60 g", "fiber": "12 g", "fat": "10 g"}</t>
         </is>
       </c>
-      <c r="G24" t="n">
+      <c r="H24" t="n">
         <v>4</v>
       </c>
-      <c r="H24" t="n">
+      <c r="I24" t="n">
         <v>30</v>
       </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>['weight-loss', 'plant-based', 'whole-foods', 'oil-free', 'lunches-and-dinners', 'soups', 'salads', 'wraps', 'sandwiches', 'rice', 'stews', 'stir-fry', 'seafood', 'ethnic', 'arabic', 'desserts']</t>
-        </is>
-      </c>
       <c r="J24" t="inlineStr">
         <is>
+          <t>['animal-protein', 'arabic', 'ethnic', 'lunches-and-dinners', 'oil-free', 'weight-loss', 'wraps']</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
           <t>oil_free</t>
         </is>
       </c>
-      <c r="K24" t="inlineStr">
+      <c r="L24" t="inlineStr">
         <is>
           <t>plant_based</t>
         </is>
       </c>
-      <c r="L24" t="inlineStr">
+      <c r="M24" t="inlineStr">
         <is>
           <t>Savory</t>
         </is>
       </c>
-      <c r="M24" t="inlineStr">
+      <c r="N24" t="inlineStr">
         <is>
           <t>weight_loss</t>
         </is>
       </c>
-      <c r="N24" t="b">
-        <v>0</v>
-      </c>
       <c r="O24" t="b">
         <v>0</v>
       </c>
-      <c r="P24" t="inlineStr"/>
-      <c r="Q24" t="inlineStr">
+      <c r="P24" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q24" t="inlineStr"/>
+      <c r="R24" t="inlineStr">
         <is>
           <t>hot</t>
         </is>
       </c>
-      <c r="R24" t="n">
-        <v>0</v>
-      </c>
-      <c r="S24" t="inlineStr"/>
-      <c r="T24" t="inlineStr">
+      <c r="S24" t="n">
+        <v>0</v>
+      </c>
+      <c r="T24" t="inlineStr"/>
+      <c r="U24" t="inlineStr">
         <is>
           <t>1. In a food processor, combine chickpeas, onion, garlic, parsley, cilantro, cumin, coriander, baking soda, lemon juice, salt, and pepper. Process until well blended but still slightly chunky; add water if needed.
 2. Form the mixture into small patties and bake on a parchment lined sheet at 400°F (200°C) for 20–25 minutes until golden.
@@ -2831,8 +2951,8 @@
 5. Cook time: 25</t>
         </is>
       </c>
-      <c r="U24" t="inlineStr"/>
-      <c r="V24" t="inlineStr">
+      <c r="V24" t="inlineStr"/>
+      <c r="W24" t="inlineStr">
         <is>
           <t>['In a food processor, combine chickpeas, onion, garlic, parsley, cilantro, cumin, coriander, baking soda, lemon juice, salt, and pepper. Process until well blended but still slightly chunky; add water if needed.', 'Form the mixture into small patties and bake on a parchment lined sheet at 400°F (200°C) for 20–25 minutes until golden.', 'To assemble, warm pitas and layer with lettuce, tomatoes, grilled chicken slices, and a falafel patty.', 'Top with a dollop of fat free yogurt and serve.', 'Cook time: 25']</t>
         </is>
@@ -2851,15 +2971,20 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Oil Free Fatteh with Chicken, Chickpeas &amp; Rice</t>
+          <t>Oil Free Fatteh With Chicken, Chickpeas &amp; Rice</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
+          <t>3335</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
           <t>['1 lb chicken breast, boiled and shredded', '2 cups cooked basmati rice', '1 can (15 oz) chickpeas, drained and rinsed', '4 cups low sodium chicken broth (reserved from boiling chicken)', '1 large flatbread, toasted until crisp', '2 garlic cloves, minced', 'Juice of 1 lemon', 'Salt and pepper, to taste', '1/4 cup chopped fresh parsley', '1/2 tsp ground sumac']</t>
         </is>
       </c>
-      <c r="E25" t="inlineStr">
+      <c r="F25" t="inlineStr">
         <is>
           <t>1. Preheat oven to 375°F (190°C). Break the toasted flatbread into bite sized pieces and spread them in a serving dish.
 2. Layer the cooked rice over the bread, then top with shredded chicken and chickpeas.
@@ -2869,59 +2994,59 @@
 6. Cook time: 10</t>
         </is>
       </c>
-      <c r="F25" t="inlineStr">
+      <c r="G25" t="inlineStr">
         <is>
           <t>{"calories": 540, "protein": "36 g", "carbs": "65 g", "fiber": "7 g", "fat": "8 g"}</t>
         </is>
       </c>
-      <c r="G25" t="n">
+      <c r="H25" t="n">
         <v>4</v>
       </c>
-      <c r="H25" t="n">
+      <c r="I25" t="n">
         <v>25</v>
       </c>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>['weight-loss', 'plant-based', 'whole-foods', 'oil-free', 'lunches-and-dinners', 'soups', 'salads', 'wraps', 'sandwiches', 'rice', 'stews', 'stir-fry', 'seafood', 'ethnic', 'arabic', 'desserts']</t>
-        </is>
-      </c>
       <c r="J25" t="inlineStr">
         <is>
+          <t>['animal-protein', 'arabic', 'ethnic', 'lunches-and-dinners', 'oil-free', 'rice', 'weight-loss']</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
           <t>oil_free</t>
         </is>
       </c>
-      <c r="K25" t="inlineStr">
+      <c r="L25" t="inlineStr">
         <is>
           <t>plant_based</t>
         </is>
       </c>
-      <c r="L25" t="inlineStr">
+      <c r="M25" t="inlineStr">
         <is>
           <t>Savory</t>
         </is>
       </c>
-      <c r="M25" t="inlineStr">
+      <c r="N25" t="inlineStr">
         <is>
           <t>weight_loss</t>
         </is>
       </c>
-      <c r="N25" t="b">
-        <v>0</v>
-      </c>
       <c r="O25" t="b">
         <v>0</v>
       </c>
-      <c r="P25" t="inlineStr"/>
-      <c r="Q25" t="inlineStr">
+      <c r="P25" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q25" t="inlineStr"/>
+      <c r="R25" t="inlineStr">
         <is>
           <t>hot</t>
         </is>
       </c>
-      <c r="R25" t="n">
-        <v>0</v>
-      </c>
-      <c r="S25" t="inlineStr"/>
-      <c r="T25" t="inlineStr">
+      <c r="S25" t="n">
+        <v>0</v>
+      </c>
+      <c r="T25" t="inlineStr"/>
+      <c r="U25" t="inlineStr">
         <is>
           <t>1. Preheat oven to 375°F (190°C). Break the toasted flatbread into bite sized pieces and spread them in a serving dish.
 2. Layer the cooked rice over the bread, then top with shredded chicken and chickpeas.
@@ -2931,8 +3056,8 @@
 6. Cook time: 10</t>
         </is>
       </c>
-      <c r="U25" t="inlineStr"/>
-      <c r="V25" t="inlineStr">
+      <c r="V25" t="inlineStr"/>
+      <c r="W25" t="inlineStr">
         <is>
           <t>['Preheat oven to 375°F (190°C). Break the toasted flatbread into bite sized pieces and spread them in a serving dish.', 'Layer the cooked rice over the bread, then top with shredded chicken and chickpeas.', 'In a small saucepan, gently heat the reserved chicken broth with minced garlic, lemon juice, salt, pepper, and sumac.', 'Pour the spiced broth evenly over the layered dish.', 'Garnish with chopped parsley and serve warm.', 'Cook time: 10']</t>
         </is>
@@ -2951,15 +3076,20 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Oil Free Beef  Kofta with Lentil Pilaf</t>
+          <t>Oil Free Beef  Kofta With Lentil Pilaf</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
+          <t>3336</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
           <t>['1 lb lean ground beef', '1 small onion, grated', '2 garlic cloves, minced', '1 tsp ground cumin', '1 tsp ground coriander', '1/2 tsp ground allspice', 'Salt and pepper, to taste', '1 cup brown lentils, rinsed', '2 cups low sodium vegetable broth', '1 cup basmati rice, rinsed', '1/4 cup chopped fresh mint', 'Juice of 1 lemon']</t>
         </is>
       </c>
-      <c r="E26" t="inlineStr">
+      <c r="F26" t="inlineStr">
         <is>
           <t>1. In a bowl, mix ground beef with grated onion, garlic, cumin, coriander, allspice, salt, and pepper. Form into small oval-shaped kofta.
 2. Preheat a grill pan over medium high heat and grill the kofta for about 5–7 minutes until cooked through.
@@ -2969,59 +3099,59 @@
 6. Cook time: 30</t>
         </is>
       </c>
-      <c r="F26" t="inlineStr">
+      <c r="G26" t="inlineStr">
         <is>
           <t>{"calories": 520, "protein": "35 g", "carbs": "60 g", "fiber": "10 g", "fat": "10 g"}</t>
         </is>
       </c>
-      <c r="G26" t="n">
+      <c r="H26" t="n">
         <v>4</v>
       </c>
-      <c r="H26" t="n">
+      <c r="I26" t="n">
         <v>30</v>
       </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>['weight-loss', 'plant-based', 'whole-foods', 'oil-free', 'lunches-and-dinners', 'soups', 'salads', 'wraps', 'sandwiches', 'rice', 'stews', 'stir-fry', 'seafood', 'ethnic', 'arabic', 'desserts']</t>
-        </is>
-      </c>
       <c r="J26" t="inlineStr">
         <is>
+          <t>['animal-protein', 'arabic', 'ethnic', 'lunches-and-dinners', 'oil-free', 'rice', 'weight-loss']</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
           <t>oil_free</t>
         </is>
       </c>
-      <c r="K26" t="inlineStr">
+      <c r="L26" t="inlineStr">
         <is>
           <t>plant_based</t>
         </is>
       </c>
-      <c r="L26" t="inlineStr">
+      <c r="M26" t="inlineStr">
         <is>
           <t>Savory</t>
         </is>
       </c>
-      <c r="M26" t="inlineStr">
+      <c r="N26" t="inlineStr">
         <is>
           <t>weight_loss</t>
         </is>
       </c>
-      <c r="N26" t="b">
-        <v>0</v>
-      </c>
       <c r="O26" t="b">
         <v>0</v>
       </c>
-      <c r="P26" t="inlineStr"/>
-      <c r="Q26" t="inlineStr">
+      <c r="P26" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q26" t="inlineStr"/>
+      <c r="R26" t="inlineStr">
         <is>
           <t>hot</t>
         </is>
       </c>
-      <c r="R26" t="n">
-        <v>0</v>
-      </c>
-      <c r="S26" t="inlineStr"/>
-      <c r="T26" t="inlineStr">
+      <c r="S26" t="n">
+        <v>0</v>
+      </c>
+      <c r="T26" t="inlineStr"/>
+      <c r="U26" t="inlineStr">
         <is>
           <t>1. In a bowl, mix ground beef with grated onion, garlic, cumin, coriander, allspice, salt, and pepper. Form into small oval-shaped kofta.
 2. Preheat a grill pan over medium high heat and grill the kofta for about 5–7 minutes until cooked through.
@@ -3031,8 +3161,8 @@
 6. Cook time: 30</t>
         </is>
       </c>
-      <c r="U26" t="inlineStr"/>
-      <c r="V26" t="inlineStr">
+      <c r="V26" t="inlineStr"/>
+      <c r="W26" t="inlineStr">
         <is>
           <t>['In a bowl, mix ground beef with grated onion, garlic, cumin, coriander, allspice, salt, and pepper. Form into small oval-shaped kofta.', 'Preheat a grill pan over medium high heat and grill the kofta for about 5–7 minutes until cooked through.', 'In a pot, combine brown lentils, basmati rice, and vegetable broth; bring to a boil, then cover and simmer for 25 minutes until both lentils and rice are tender.', 'Stir in chopped mint and lemon juice; adjust seasoning as needed.', 'Serve the grilled kofta over a bed of lentil pilaf.', 'Cook time: 30']</t>
         </is>
@@ -3051,15 +3181,20 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Oil Free Baked Zaatar Chicken with Bulgur</t>
+          <t>Oil Free Baked Zaatar Chicken With Bulgur</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
+          <t>3337</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
           <t>['1 lb chicken breast, thinly sliced', '2 tsp zaatar spice blend', 'Juice of 1 lemon', 'Salt and pepper, to taste', '2 cups bulgur wheat, rinsed', '2 cups low sodium chicken broth', '1/2 cup chopped fresh parsley', '1/4 cup pomegranate seeds (optional, for garnish)']</t>
         </is>
       </c>
-      <c r="E27" t="inlineStr">
+      <c r="F27" t="inlineStr">
         <is>
           <t>1. Preheat oven to 400°F (200°C).
 2. In a bowl, combine chicken slices with zaatar, lemon juice, salt, and pepper. Arrange on a baking sheet and bake for 15–20 minutes until cooked through.
@@ -3068,59 +3203,59 @@
 5. Cook time: 20</t>
         </is>
       </c>
-      <c r="F27" t="inlineStr">
+      <c r="G27" t="inlineStr">
         <is>
           <t>{"calories": 510, "protein": "38 g", "carbs": "60 g", "fiber": "9 g", "fat": "8 g"}</t>
         </is>
       </c>
-      <c r="G27" t="n">
+      <c r="H27" t="n">
         <v>4</v>
       </c>
-      <c r="H27" t="n">
+      <c r="I27" t="n">
         <v>20</v>
       </c>
-      <c r="I27" t="inlineStr">
-        <is>
-          <t>['weight-loss', 'plant-based', 'whole-foods', 'oil-free', 'lunches-and-dinners', 'soups', 'salads', 'wraps', 'sandwiches', 'rice', 'stews', 'stir-fry', 'seafood', 'ethnic', 'arabic', 'desserts']</t>
-        </is>
-      </c>
       <c r="J27" t="inlineStr">
         <is>
+          <t>['animal-protein', 'arabic', 'ethnic', 'lunches-and-dinners', 'oil-free', 'weight-loss']</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
           <t>oil_free</t>
         </is>
       </c>
-      <c r="K27" t="inlineStr">
+      <c r="L27" t="inlineStr">
         <is>
           <t>plant_based</t>
         </is>
       </c>
-      <c r="L27" t="inlineStr">
+      <c r="M27" t="inlineStr">
         <is>
           <t>Savory</t>
         </is>
       </c>
-      <c r="M27" t="inlineStr">
+      <c r="N27" t="inlineStr">
         <is>
           <t>weight_loss</t>
         </is>
       </c>
-      <c r="N27" t="b">
-        <v>0</v>
-      </c>
       <c r="O27" t="b">
         <v>0</v>
       </c>
-      <c r="P27" t="inlineStr"/>
-      <c r="Q27" t="inlineStr">
+      <c r="P27" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q27" t="inlineStr"/>
+      <c r="R27" t="inlineStr">
         <is>
           <t>hot</t>
         </is>
       </c>
-      <c r="R27" t="n">
-        <v>0</v>
-      </c>
-      <c r="S27" t="inlineStr"/>
-      <c r="T27" t="inlineStr">
+      <c r="S27" t="n">
+        <v>0</v>
+      </c>
+      <c r="T27" t="inlineStr"/>
+      <c r="U27" t="inlineStr">
         <is>
           <t>1. Preheat oven to 400°F (200°C).
 2. In a bowl, combine chicken slices with zaatar, lemon juice, salt, and pepper. Arrange on a baking sheet and bake for 15–20 minutes until cooked through.
@@ -3129,8 +3264,8 @@
 5. Cook time: 20</t>
         </is>
       </c>
-      <c r="U27" t="inlineStr"/>
-      <c r="V27" t="inlineStr">
+      <c r="V27" t="inlineStr"/>
+      <c r="W27" t="inlineStr">
         <is>
           <t>['Preheat oven to 400°F (200°C).', 'In a bowl, combine chicken slices with zaatar, lemon juice, salt, and pepper. Arrange on a baking sheet and bake for 15–20 minutes until cooked through.', 'Meanwhile, bring chicken broth to a boil; add bulgur wheat, cover, and simmer for 15 minutes until tender. Stir in chopped parsley.', 'Serve the baked zaatar chicken over the bulgur pilaf and garnish with pomegranate seeds if desired.', 'Cook time: 20']</t>
         </is>
@@ -3149,15 +3284,20 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Oil Free Lamb Rice with Dried Fruits</t>
+          <t>Oil Free Lamb Rice With Dried Fruits</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
+          <t>3338</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
           <t>['1 lb lean lamb stew meat, cut into 1 inch cubes', '2 cups basmati rice, rinsed', '4 cups low sodium lamb broth (or vegetable broth)', '1 large onion, chopped', '2 garlic cloves, minced', '1 tsp ground cumin', '1 tsp ground cinnamon', '1/2 cup dried apricots, chopped', '1/2 cup raisins', 'Salt and pepper, to taste', 'Fresh cilantro, chopped (for garnish)']</t>
         </is>
       </c>
-      <c r="E28" t="inlineStr">
+      <c r="F28" t="inlineStr">
         <is>
           <t>1. In a heavy pot, combine lamb cubes, chopped onion, garlic, cumin, cinnamon, salt, and pepper. Sauté using a splash of water until onions soften.
 2. Add dried apricots, raisins, and broth; bring to a boil, then reduce heat, cover, and simmer for 1–1½ hours until lamb is tender.
@@ -3166,59 +3306,59 @@
 5. Cook time: 1</t>
         </is>
       </c>
-      <c r="F28" t="inlineStr">
+      <c r="G28" t="inlineStr">
         <is>
           <t>{"calories": 520, "protein": "38 g", "carbs": "60 g", "fiber": "8 g", "fat": "10 g"}</t>
         </is>
       </c>
-      <c r="G28" t="n">
+      <c r="H28" t="n">
         <v>4</v>
       </c>
-      <c r="H28" t="n">
+      <c r="I28" t="n">
         <v>25</v>
       </c>
-      <c r="I28" t="inlineStr">
-        <is>
-          <t>['weight-loss', 'plant-based', 'whole-foods', 'oil-free', 'lunches-and-dinners', 'soups', 'salads', 'wraps', 'sandwiches', 'rice', 'stews', 'stir-fry', 'seafood', 'ethnic', 'arabic', 'desserts']</t>
-        </is>
-      </c>
       <c r="J28" t="inlineStr">
         <is>
+          <t>['animal-protein', 'arabic', 'ethnic', 'lunches-and-dinners', 'oil-free', 'rice', 'weight-loss']</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
           <t>oil_free</t>
         </is>
       </c>
-      <c r="K28" t="inlineStr">
+      <c r="L28" t="inlineStr">
         <is>
           <t>plant_based</t>
         </is>
       </c>
-      <c r="L28" t="inlineStr">
+      <c r="M28" t="inlineStr">
         <is>
           <t>Savory</t>
         </is>
       </c>
-      <c r="M28" t="inlineStr">
+      <c r="N28" t="inlineStr">
         <is>
           <t>weight_loss</t>
         </is>
       </c>
-      <c r="N28" t="b">
-        <v>0</v>
-      </c>
       <c r="O28" t="b">
         <v>0</v>
       </c>
-      <c r="P28" t="inlineStr"/>
-      <c r="Q28" t="inlineStr">
+      <c r="P28" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q28" t="inlineStr"/>
+      <c r="R28" t="inlineStr">
         <is>
           <t>hot</t>
         </is>
       </c>
-      <c r="R28" t="n">
-        <v>0</v>
-      </c>
-      <c r="S28" t="inlineStr"/>
-      <c r="T28" t="inlineStr">
+      <c r="S28" t="n">
+        <v>0</v>
+      </c>
+      <c r="T28" t="inlineStr"/>
+      <c r="U28" t="inlineStr">
         <is>
           <t>1. In a heavy pot, combine lamb cubes, chopped onion, garlic, cumin, cinnamon, salt, and pepper. Sauté using a splash of water until onions soften.
 2. Add dried apricots, raisins, and broth; bring to a boil, then reduce heat, cover, and simmer for 1–1½ hours until lamb is tender.
@@ -3227,8 +3367,8 @@
 5. Cook time: 1</t>
         </is>
       </c>
-      <c r="U28" t="inlineStr"/>
-      <c r="V28" t="inlineStr">
+      <c r="V28" t="inlineStr"/>
+      <c r="W28" t="inlineStr">
         <is>
           <t>['In a heavy pot, combine lamb cubes, chopped onion, garlic, cumin, cinnamon, salt, and pepper. Sauté using a splash of water until onions soften.', 'Add dried apricots, raisins, and broth; bring to a boil, then reduce heat, cover, and simmer for 1–1½ hours until lamb is tender.', 'Stir in basmati rice and continue to simmer for 20 minutes until rice is cooked and has absorbed the flavors.', 'Garnish with fresh cilantro before serving.', 'Cook time: 1']</t>
         </is>
@@ -3252,10 +3392,15 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
+          <t>3339</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
           <t>['8 oz white fish fillet (such as cod), cut into chunks', '1/2 lb shrimp, peeled and deveined', '2 cups basmati rice, rinsed', '4 cups low sodium fish or chicken broth', '1 large onion, thinly sliced', '2 garlic cloves, minced', '1 tsp ground cumin', '1/2 tsp ground coriander', 'Salt and pepper, to taste', 'Juice of 1 lemon', 'Fresh parsley, chopped (for garnish)']</t>
         </is>
       </c>
-      <c r="E29" t="inlineStr">
+      <c r="F29" t="inlineStr">
         <is>
           <t>1. In a large pot, sauté sliced onion and garlic (using a few tablespoons of water) until translucent.
 2. Add ground cumin, coriander, salt, and pepper; stir for 1 minute.
@@ -3265,59 +3410,59 @@
 6. Cook time: 25</t>
         </is>
       </c>
-      <c r="F29" t="inlineStr">
+      <c r="G29" t="inlineStr">
         <is>
           <t>{"calories": 540, "protein": "38 g", "carbs": "60 g", "fiber": "7 g", "fat": "8 g"}</t>
         </is>
       </c>
-      <c r="G29" t="n">
+      <c r="H29" t="n">
         <v>4</v>
       </c>
-      <c r="H29" t="n">
+      <c r="I29" t="n">
         <v>20</v>
       </c>
-      <c r="I29" t="inlineStr">
-        <is>
-          <t>['weight-loss', 'plant-based', 'whole-foods', 'oil-free', 'lunches-and-dinners', 'soups', 'salads', 'wraps', 'sandwiches', 'rice', 'stews', 'stir-fry', 'seafood', 'ethnic', 'arabic', 'desserts']</t>
-        </is>
-      </c>
       <c r="J29" t="inlineStr">
         <is>
+          <t>['animal-protein', 'arabic', 'ethnic', 'lunches-and-dinners', 'oil-free', 'seafood', 'weight-loss']</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr">
+        <is>
           <t>oil_free</t>
         </is>
       </c>
-      <c r="K29" t="inlineStr">
+      <c r="L29" t="inlineStr">
         <is>
           <t>plant_based</t>
         </is>
       </c>
-      <c r="L29" t="inlineStr">
+      <c r="M29" t="inlineStr">
         <is>
           <t>Savory</t>
         </is>
       </c>
-      <c r="M29" t="inlineStr">
+      <c r="N29" t="inlineStr">
         <is>
           <t>weight_loss</t>
         </is>
       </c>
-      <c r="N29" t="b">
-        <v>0</v>
-      </c>
       <c r="O29" t="b">
         <v>0</v>
       </c>
-      <c r="P29" t="inlineStr"/>
-      <c r="Q29" t="inlineStr">
+      <c r="P29" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q29" t="inlineStr"/>
+      <c r="R29" t="inlineStr">
         <is>
           <t>hot</t>
         </is>
       </c>
-      <c r="R29" t="n">
-        <v>0</v>
-      </c>
-      <c r="S29" t="inlineStr"/>
-      <c r="T29" t="inlineStr">
+      <c r="S29" t="n">
+        <v>0</v>
+      </c>
+      <c r="T29" t="inlineStr"/>
+      <c r="U29" t="inlineStr">
         <is>
           <t>1. In a large pot, sauté sliced onion and garlic (using a few tablespoons of water) until translucent.
 2. Add ground cumin, coriander, salt, and pepper; stir for 1 minute.
@@ -3327,8 +3472,8 @@
 6. Cook time: 25</t>
         </is>
       </c>
-      <c r="U29" t="inlineStr"/>
-      <c r="V29" t="inlineStr">
+      <c r="V29" t="inlineStr"/>
+      <c r="W29" t="inlineStr">
         <is>
           <t>['In a large pot, sauté sliced onion and garlic (using a few tablespoons of water) until translucent.', 'Add ground cumin, coriander, salt, and pepper; stir for 1 minute.', 'Pour in the broth and bring to a boil. Add basmati rice and simmer for 15 minutes.', 'Gently add fish chunks and shrimp; continue simmering for another 8–10 minutes until the fish is flaky and shrimp are cooked.', 'Stir in lemon juice, adjust seasoning if needed, and garnish with chopped parsley before serving.', 'Cook time: 25']</t>
         </is>
@@ -3352,10 +3497,15 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
+          <t>3340</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
           <t>['1 lb chicken thighs (boneless, skinless), cut into 1 inch cubes', '2 cups fresh okra, trimmed and cut into 1 inch pieces', '1 large tomato, diced', '1 medium onion, chopped', '3 garlic cloves, minced', '1 tsp ground coriander', '1 tsp ground cumin', '½ tsp ground turmeric', '½ tsp ground cinnamon', '4 cups low sodium chicken broth', 'Salt and pepper, to taste', 'Juice of 1 lemon', '¼ cup chopped fresh cilantro (for garnish)']</t>
         </is>
       </c>
-      <c r="E30" t="inlineStr">
+      <c r="F30" t="inlineStr">
         <is>
           <t>1. In a large pot, combine chopped onion and garlic with a splash of water; sauté until soft.
 2. Add the chicken cubes and sauté for about 5 minutes until lightly browned.
@@ -3365,59 +3515,59 @@
 6. Cook time: 40</t>
         </is>
       </c>
-      <c r="F30" t="inlineStr">
+      <c r="G30" t="inlineStr">
         <is>
           <t>{"calories": 420, "protein": "30 g", "carbs": "40 g", "fiber": "7 g", "fat": "10 g"}</t>
         </is>
       </c>
-      <c r="G30" t="n">
+      <c r="H30" t="n">
         <v>4</v>
       </c>
-      <c r="H30" t="n">
+      <c r="I30" t="n">
         <v>20</v>
       </c>
-      <c r="I30" t="inlineStr">
-        <is>
-          <t>['weight-loss', 'plant-based', 'whole-foods', 'oil-free', 'lunches-and-dinners', 'soups', 'salads', 'wraps', 'sandwiches', 'rice', 'stews', 'stir-fry', 'seafood', 'ethnic', 'arabic', 'desserts']</t>
-        </is>
-      </c>
       <c r="J30" t="inlineStr">
         <is>
+          <t>['animal-protein', 'arabic', 'ethnic', 'lunches-and-dinners', 'oil-free', 'stews', 'weight-loss']</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr">
+        <is>
           <t>oil_free</t>
         </is>
       </c>
-      <c r="K30" t="inlineStr">
+      <c r="L30" t="inlineStr">
         <is>
           <t>plant_based</t>
         </is>
       </c>
-      <c r="L30" t="inlineStr">
+      <c r="M30" t="inlineStr">
         <is>
           <t>Savory</t>
         </is>
       </c>
-      <c r="M30" t="inlineStr">
+      <c r="N30" t="inlineStr">
         <is>
           <t>weight_loss</t>
         </is>
       </c>
-      <c r="N30" t="b">
-        <v>0</v>
-      </c>
       <c r="O30" t="b">
         <v>0</v>
       </c>
-      <c r="P30" t="inlineStr"/>
-      <c r="Q30" t="inlineStr">
+      <c r="P30" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q30" t="inlineStr"/>
+      <c r="R30" t="inlineStr">
         <is>
           <t>hot</t>
         </is>
       </c>
-      <c r="R30" t="n">
-        <v>0</v>
-      </c>
-      <c r="S30" t="inlineStr"/>
-      <c r="T30" t="inlineStr">
+      <c r="S30" t="n">
+        <v>0</v>
+      </c>
+      <c r="T30" t="inlineStr"/>
+      <c r="U30" t="inlineStr">
         <is>
           <t>1. In a large pot, combine chopped onion and garlic with a splash of water; sauté until soft.
 2. Add the chicken cubes and sauté for about 5 minutes until lightly browned.
@@ -3427,8 +3577,8 @@
 6. Cook time: 40</t>
         </is>
       </c>
-      <c r="U30" t="inlineStr"/>
-      <c r="V30" t="inlineStr">
+      <c r="V30" t="inlineStr"/>
+      <c r="W30" t="inlineStr">
         <is>
           <t>['In a large pot, combine chopped onion and garlic with a splash of water; sauté until soft.', 'Add the chicken cubes and sauté for about 5 minutes until lightly browned.', 'Stir in the diced tomato, okra, and spices (coriander, cumin, turmeric, cinnamon). Season with salt and pepper.', 'Pour in the chicken broth and bring to a boil. Reduce heat and simmer for 35–40 minutes until the chicken is tender and the okra is cooked.', 'Stir in lemon juice, adjust seasonings, and garnish with chopped cilantro before serving.', 'Cook time: 40']</t>
         </is>
@@ -3447,15 +3597,20 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Oil Free Quinoa Stuffed Tomatoes with Spiced Chickpeas</t>
+          <t>Oil Free Quinoa Stuffed Tomatoes With Spiced Chickpeas</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
+          <t>3341</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
           <t>['4 large tomatoes (tops cut off and insides scooped out)', '1 cup quinoa, rinsed', '1½ cups low sodium vegetable broth', '1 can (15 oz) chickpeas, drained and rinsed', '1 small onion, finely chopped', '2 garlic cloves, minced', '1 tsp ground cumin', '½ tsp ground coriander', 'Salt and pepper, to taste', '¼ cup chopped fresh parsley', 'Juice of 1 lemon']</t>
         </is>
       </c>
-      <c r="E31" t="inlineStr">
+      <c r="F31" t="inlineStr">
         <is>
           <t>1. In a saucepan, bring vegetable broth to a boil and add quinoa; cover and simmer for 15 minutes until tender.
 2. Meanwhile, sauté onion and garlic (using a splash of water) in a nonstick pan until softened. Add chickpeas, cumin, coriander, salt, and pepper; cook for 5 minutes.
@@ -3466,59 +3621,59 @@
 7. Cook time: 25</t>
         </is>
       </c>
-      <c r="F31" t="inlineStr">
+      <c r="G31" t="inlineStr">
         <is>
           <t>{"calories": 350, "protein": "15 g", "carbs": "60 g", "fiber": "10 g", "fat": "5 g"}</t>
         </is>
       </c>
-      <c r="G31" t="n">
+      <c r="H31" t="n">
         <v>4</v>
       </c>
-      <c r="H31" t="n">
+      <c r="I31" t="n">
         <v>25</v>
       </c>
-      <c r="I31" t="inlineStr">
-        <is>
-          <t>['weight-loss', 'plant-based', 'whole-foods', 'oil-free', 'lunches-and-dinners', 'soups', 'salads', 'wraps', 'sandwiches', 'rice', 'stews', 'stir-fry', 'seafood', 'ethnic', 'arabic', 'desserts']</t>
-        </is>
-      </c>
       <c r="J31" t="inlineStr">
         <is>
+          <t>['arabic', 'ethnic', 'lunches-and-dinners', 'oil-free', 'vegetarian', 'weight-loss']</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr">
+        <is>
           <t>oil_free</t>
         </is>
       </c>
-      <c r="K31" t="inlineStr">
-        <is>
-          <t>plant_based</t>
-        </is>
-      </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>Savory</t>
+          <t>Vegetarian</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
         <is>
+          <t>Spicy</t>
+        </is>
+      </c>
+      <c r="N31" t="inlineStr">
+        <is>
           <t>weight_loss</t>
         </is>
       </c>
-      <c r="N31" t="b">
-        <v>0</v>
-      </c>
       <c r="O31" t="b">
         <v>0</v>
       </c>
-      <c r="P31" t="inlineStr"/>
-      <c r="Q31" t="inlineStr">
+      <c r="P31" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q31" t="inlineStr"/>
+      <c r="R31" t="inlineStr">
         <is>
           <t>hot</t>
         </is>
       </c>
-      <c r="R31" t="n">
-        <v>0</v>
-      </c>
-      <c r="S31" t="inlineStr"/>
-      <c r="T31" t="inlineStr">
+      <c r="S31" t="n">
+        <v>0</v>
+      </c>
+      <c r="T31" t="inlineStr"/>
+      <c r="U31" t="inlineStr">
         <is>
           <t>1. In a saucepan, bring vegetable broth to a boil and add quinoa; cover and simmer for 15 minutes until tender.
 2. Meanwhile, sauté onion and garlic (using a splash of water) in a nonstick pan until softened. Add chickpeas, cumin, coriander, salt, and pepper; cook for 5 minutes.
@@ -3529,8 +3684,8 @@
 7. Cook time: 25</t>
         </is>
       </c>
-      <c r="U31" t="inlineStr"/>
-      <c r="V31" t="inlineStr">
+      <c r="V31" t="inlineStr"/>
+      <c r="W31" t="inlineStr">
         <is>
           <t>['In a saucepan, bring vegetable broth to a boil and add quinoa; cover and simmer for 15 minutes until tender.', 'Meanwhile, sauté onion and garlic (using a splash of water) in a nonstick pan until softened. Add chickpeas, cumin, coriander, salt, and pepper; cook for 5 minutes.', 'Stir the cooked quinoa into the chickpea mixture and fold in chopped parsley and lemon juice.', 'Stuff each tomato with the quinoa-chickpea filling.', 'Place stuffed tomatoes in a baking dish, cover with foil, and bake at 375°F (190°C) for 25 minutes.', 'Serve warm.', 'Cook time: 25']</t>
         </is>
@@ -3554,10 +3709,15 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
+          <t>3342</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
           <t>['1 lb lean lamb stew meat, cooked until tender and shredded', '1 small onion, finely chopped', '1 tsp ground cumin', '1 tsp ground coriander', '½ tsp ground cinnamon', 'Salt and pepper, to taste', '6 sheets phyllo dough (prepared oil free or brushed lightly with water)', '½ cup chopped almonds (optional)', '¼ cup chopped fresh mint', 'Juice of 1 lemon']</t>
         </is>
       </c>
-      <c r="E32" t="inlineStr">
+      <c r="F32" t="inlineStr">
         <is>
           <t>1. In a bowl, mix shredded lamb with chopped onion, cumin, coriander, cinnamon, salt, pepper, mint, and lemon juice. Stir in almonds if using.
 2. Place a sheet of phyllo dough on a clean surface; lay about 2 3 tablespoons of the lamb mixture along one edge.
@@ -3567,59 +3727,59 @@
 6. Cook time: 20</t>
         </is>
       </c>
-      <c r="F32" t="inlineStr">
+      <c r="G32" t="inlineStr">
         <is>
           <t>{"calories": 450, "protein": "35 g", "carbs": "40 g", "fiber": "6 g", "fat": "8 g"}</t>
         </is>
       </c>
-      <c r="G32" t="n">
+      <c r="H32" t="n">
         <v>4</v>
       </c>
-      <c r="H32" t="n">
+      <c r="I32" t="n">
         <v>30</v>
       </c>
-      <c r="I32" t="inlineStr">
-        <is>
-          <t>['weight-loss', 'plant-based', 'whole-foods', 'oil-free', 'lunches-and-dinners', 'soups', 'salads', 'wraps', 'sandwiches', 'rice', 'stews', 'stir-fry', 'seafood', 'ethnic', 'arabic', 'desserts']</t>
-        </is>
-      </c>
       <c r="J32" t="inlineStr">
         <is>
+          <t>['animal-protein', 'arabic', 'ethnic', 'lunches-and-dinners', 'oil-free', 'weight-loss', 'wraps']</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr">
+        <is>
           <t>oil_free</t>
         </is>
       </c>
-      <c r="K32" t="inlineStr">
+      <c r="L32" t="inlineStr">
         <is>
           <t>plant_based</t>
         </is>
       </c>
-      <c r="L32" t="inlineStr">
+      <c r="M32" t="inlineStr">
         <is>
           <t>Savory</t>
         </is>
       </c>
-      <c r="M32" t="inlineStr">
+      <c r="N32" t="inlineStr">
         <is>
           <t>weight_loss</t>
         </is>
       </c>
-      <c r="N32" t="b">
-        <v>0</v>
-      </c>
       <c r="O32" t="b">
         <v>0</v>
       </c>
-      <c r="P32" t="inlineStr"/>
-      <c r="Q32" t="inlineStr">
+      <c r="P32" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q32" t="inlineStr"/>
+      <c r="R32" t="inlineStr">
         <is>
           <t>hot</t>
         </is>
       </c>
-      <c r="R32" t="n">
-        <v>0</v>
-      </c>
-      <c r="S32" t="inlineStr"/>
-      <c r="T32" t="inlineStr">
+      <c r="S32" t="n">
+        <v>0</v>
+      </c>
+      <c r="T32" t="inlineStr"/>
+      <c r="U32" t="inlineStr">
         <is>
           <t>1. In a bowl, mix shredded lamb with chopped onion, cumin, coriander, cinnamon, salt, pepper, mint, and lemon juice. Stir in almonds if using.
 2. Place a sheet of phyllo dough on a clean surface; lay about 2 3 tablespoons of the lamb mixture along one edge.
@@ -3629,8 +3789,8 @@
 6. Cook time: 20</t>
         </is>
       </c>
-      <c r="U32" t="inlineStr"/>
-      <c r="V32" t="inlineStr">
+      <c r="V32" t="inlineStr"/>
+      <c r="W32" t="inlineStr">
         <is>
           <t>['In a bowl, mix shredded lamb with chopped onion, cumin, coriander, cinnamon, salt, pepper, mint, and lemon juice. Stir in almonds if using.', 'Place a sheet of phyllo dough on a clean surface; lay about 2 3 tablespoons of the lamb mixture along one edge.', 'Roll the phyllo tightly around the filling, then roll again to form a compact wrap.', 'Preheat the oven to 375°F (190°C), arrange the wraps on a parchment lined baking sheet, and bake for 20 minutes until the phyllo is crisp.', 'Serve warm.', 'Cook time: 20']</t>
         </is>
@@ -3649,15 +3809,20 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Oil Free Chicken Kabab with Freekeh Pilaf</t>
+          <t>Oil Free Chicken Kabab With Freekeh Pilaf</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
+          <t>3343</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
           <t>['1 lb chicken breast, cut into 1 inch cubes', '1 tsp ground sumac', '1 tsp ground cumin', 'Juice of 1 lemon', 'Salt and pepper, to taste', '1 cup freekeh, rinsed', '2 cups low sodium chicken broth', '¼ cup chopped fresh parsley']</t>
         </is>
       </c>
-      <c r="E33" t="inlineStr">
+      <c r="F33" t="inlineStr">
         <is>
           <t>1. In a bowl, marinate chicken cubes with lemon juice, sumac, cumin, salt, and pepper for 20 minutes.
 2. Thread the marinated chicken onto skewers. Preheat a grill pan over medium-high heat and grill for 8–10 minutes, turning to ensure even cooking.
@@ -3666,59 +3831,59 @@
 5. Cook time: 25</t>
         </is>
       </c>
-      <c r="F33" t="inlineStr">
+      <c r="G33" t="inlineStr">
         <is>
           <t>{"calories": 480, "protein": "38 g", "carbs": "55 g", "fiber": "7 g", "fat": "8 g"}</t>
         </is>
       </c>
-      <c r="G33" t="n">
+      <c r="H33" t="n">
         <v>4</v>
       </c>
-      <c r="H33" t="n">
+      <c r="I33" t="n">
         <v>20</v>
       </c>
-      <c r="I33" t="inlineStr">
-        <is>
-          <t>['weight-loss', 'plant-based', 'whole-foods', 'oil-free', 'lunches-and-dinners', 'soups', 'salads', 'wraps', 'sandwiches', 'rice', 'stews', 'stir-fry', 'seafood', 'ethnic', 'arabic', 'desserts']</t>
-        </is>
-      </c>
       <c r="J33" t="inlineStr">
         <is>
+          <t>['animal-protein', 'arabic', 'ethnic', 'lunches-and-dinners', 'oil-free', 'rice', 'weight-loss']</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr">
+        <is>
           <t>oil_free</t>
         </is>
       </c>
-      <c r="K33" t="inlineStr">
+      <c r="L33" t="inlineStr">
         <is>
           <t>plant_based</t>
         </is>
       </c>
-      <c r="L33" t="inlineStr">
+      <c r="M33" t="inlineStr">
         <is>
           <t>Savory</t>
         </is>
       </c>
-      <c r="M33" t="inlineStr">
+      <c r="N33" t="inlineStr">
         <is>
           <t>weight_loss</t>
         </is>
       </c>
-      <c r="N33" t="b">
-        <v>0</v>
-      </c>
       <c r="O33" t="b">
         <v>0</v>
       </c>
-      <c r="P33" t="inlineStr"/>
-      <c r="Q33" t="inlineStr">
+      <c r="P33" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q33" t="inlineStr"/>
+      <c r="R33" t="inlineStr">
         <is>
           <t>hot</t>
         </is>
       </c>
-      <c r="R33" t="n">
-        <v>0</v>
-      </c>
-      <c r="S33" t="inlineStr"/>
-      <c r="T33" t="inlineStr">
+      <c r="S33" t="n">
+        <v>0</v>
+      </c>
+      <c r="T33" t="inlineStr"/>
+      <c r="U33" t="inlineStr">
         <is>
           <t>1. In a bowl, marinate chicken cubes with lemon juice, sumac, cumin, salt, and pepper for 20 minutes.
 2. Thread the marinated chicken onto skewers. Preheat a grill pan over medium-high heat and grill for 8–10 minutes, turning to ensure even cooking.
@@ -3727,8 +3892,8 @@
 5. Cook time: 25</t>
         </is>
       </c>
-      <c r="U33" t="inlineStr"/>
-      <c r="V33" t="inlineStr">
+      <c r="V33" t="inlineStr"/>
+      <c r="W33" t="inlineStr">
         <is>
           <t>['In a bowl, marinate chicken cubes with lemon juice, sumac, cumin, salt, and pepper for 20 minutes.', 'Thread the marinated chicken onto skewers. Preheat a grill pan over medium-high heat and grill for 8–10 minutes, turning to ensure even cooking.', 'Meanwhile, bring chicken broth to a boil in a saucepan; add freekeh, cover, and simmer for 15 minutes until tender. Stir in chopped parsley.', 'Serve the grilled chicken over a bed of freekeh pilaf.', 'Cook time: 25']</t>
         </is>
@@ -3752,10 +3917,15 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
+          <t>3344</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
           <t>['1 lb chicken thighs, cut into pieces', '2 cups basmati rice, rinsed', '4 cups low sodium chicken broth', '1 large onion, sliced', '3 garlic cloves, minced', '1 tsp ground cumin', '1 tsp ground coriander', '½ tsp turmeric', '½ tsp cinnamon', '¼ tsp ground cardamom', 'Salt and pepper, to taste', 'Fresh cilantro, chopped (for garnish)']</t>
         </is>
       </c>
-      <c r="E34" t="inlineStr">
+      <c r="F34" t="inlineStr">
         <is>
           <t>1. In a large pot, sauté onion and garlic (using a splash of water) until soft.
 2. Add chicken pieces along with cumin, coriander, turmeric, cinnamon, cardamom, salt, and pepper; cook for 5 minutes until chicken begins to brown.
@@ -3764,59 +3934,59 @@
 5. Cook time: 30</t>
         </is>
       </c>
-      <c r="F34" t="inlineStr">
+      <c r="G34" t="inlineStr">
         <is>
           <t>{"calories": 550, "protein": "36 g", "carbs": "65 g", "fiber": "7 g", "fat": "10 g"}</t>
         </is>
       </c>
-      <c r="G34" t="n">
+      <c r="H34" t="n">
         <v>4</v>
       </c>
-      <c r="H34" t="n">
+      <c r="I34" t="n">
         <v>25</v>
       </c>
-      <c r="I34" t="inlineStr">
-        <is>
-          <t>['weight-loss', 'plant-based', 'whole-foods', 'oil-free', 'lunches-and-dinners', 'soups', 'salads', 'wraps', 'sandwiches', 'rice', 'stews', 'stir-fry', 'seafood', 'ethnic', 'arabic', 'desserts']</t>
-        </is>
-      </c>
       <c r="J34" t="inlineStr">
         <is>
+          <t>['animal-protein', 'arabic', 'ethnic', 'lunches-and-dinners', 'oil-free', 'weight-loss']</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr">
+        <is>
           <t>oil_free</t>
         </is>
       </c>
-      <c r="K34" t="inlineStr">
+      <c r="L34" t="inlineStr">
         <is>
           <t>plant_based</t>
         </is>
       </c>
-      <c r="L34" t="inlineStr">
+      <c r="M34" t="inlineStr">
         <is>
           <t>Savory</t>
         </is>
       </c>
-      <c r="M34" t="inlineStr">
+      <c r="N34" t="inlineStr">
         <is>
           <t>weight_loss</t>
         </is>
       </c>
-      <c r="N34" t="b">
-        <v>0</v>
-      </c>
       <c r="O34" t="b">
         <v>0</v>
       </c>
-      <c r="P34" t="inlineStr"/>
-      <c r="Q34" t="inlineStr">
+      <c r="P34" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q34" t="inlineStr"/>
+      <c r="R34" t="inlineStr">
         <is>
           <t>hot</t>
         </is>
       </c>
-      <c r="R34" t="n">
-        <v>0</v>
-      </c>
-      <c r="S34" t="inlineStr"/>
-      <c r="T34" t="inlineStr">
+      <c r="S34" t="n">
+        <v>0</v>
+      </c>
+      <c r="T34" t="inlineStr"/>
+      <c r="U34" t="inlineStr">
         <is>
           <t>1. In a large pot, sauté onion and garlic (using a splash of water) until soft.
 2. Add chicken pieces along with cumin, coriander, turmeric, cinnamon, cardamom, salt, and pepper; cook for 5 minutes until chicken begins to brown.
@@ -3825,8 +3995,8 @@
 5. Cook time: 30</t>
         </is>
       </c>
-      <c r="U34" t="inlineStr"/>
-      <c r="V34" t="inlineStr">
+      <c r="V34" t="inlineStr"/>
+      <c r="W34" t="inlineStr">
         <is>
           <t>['In a large pot, sauté onion and garlic (using a splash of water) until soft.', 'Add chicken pieces along with cumin, coriander, turmeric, cinnamon, cardamom, salt, and pepper; cook for 5 minutes until chicken begins to brown.', 'Add basmati rice and chicken broth; bring to a boil, then reduce heat, cover, and simmer for 25–30 minutes until rice is tender and chicken is cooked through.', 'Garnish with fresh cilantro before serving.', 'Cook time: 30']</t>
         </is>
@@ -3845,15 +4015,20 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Oil Free Lamb Kofta with Couscous</t>
+          <t>Oil Free Lamb Kofta With Couscous</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
+          <t>3345</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
           <t>['1 lb lean ground lamb', '1 small onion, grated', '2 garlic cloves, minced', '1 tsp ground cumin', '1 tsp ground coriander', 'Salt and pepper, to taste', '1 cup couscous', '1 cup low sodium vegetable broth', '¼ cup chopped fresh mint', 'Juice of 1 lemon']</t>
         </is>
       </c>
-      <c r="E35" t="inlineStr">
+      <c r="F35" t="inlineStr">
         <is>
           <t>1. In a bowl, mix ground lamb with grated onion, garlic, cumin, coriander, salt, and pepper. Form into small oval- shaped kofta patties.
 2. Preheat a grill pan over medium-high heat and grill the kofta for about 5–7 minutes until cooked through.
@@ -3863,59 +4038,59 @@
 6. Cook time: 15</t>
         </is>
       </c>
-      <c r="F35" t="inlineStr">
+      <c r="G35" t="inlineStr">
         <is>
           <t>{"calories": 520, "protein": "35 g", "carbs": "60 g", "fiber": "10 g", "fat": "10 g"}</t>
         </is>
       </c>
-      <c r="G35" t="n">
+      <c r="H35" t="n">
         <v>4</v>
       </c>
-      <c r="H35" t="n">
+      <c r="I35" t="n">
         <v>25</v>
       </c>
-      <c r="I35" t="inlineStr">
-        <is>
-          <t>['weight-loss', 'plant-based', 'whole-foods', 'oil-free', 'lunches-and-dinners', 'soups', 'salads', 'wraps', 'sandwiches', 'rice', 'stews', 'stir-fry', 'seafood', 'ethnic', 'arabic', 'desserts']</t>
-        </is>
-      </c>
       <c r="J35" t="inlineStr">
         <is>
+          <t>['animal-protein', 'arabic', 'ethnic', 'lunches-and-dinners', 'oil-free', 'weight-loss']</t>
+        </is>
+      </c>
+      <c r="K35" t="inlineStr">
+        <is>
           <t>oil_free</t>
         </is>
       </c>
-      <c r="K35" t="inlineStr">
+      <c r="L35" t="inlineStr">
         <is>
           <t>plant_based</t>
         </is>
       </c>
-      <c r="L35" t="inlineStr">
+      <c r="M35" t="inlineStr">
         <is>
           <t>Savory</t>
         </is>
       </c>
-      <c r="M35" t="inlineStr">
+      <c r="N35" t="inlineStr">
         <is>
           <t>weight_loss</t>
         </is>
       </c>
-      <c r="N35" t="b">
-        <v>0</v>
-      </c>
       <c r="O35" t="b">
         <v>0</v>
       </c>
-      <c r="P35" t="inlineStr"/>
-      <c r="Q35" t="inlineStr">
+      <c r="P35" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q35" t="inlineStr"/>
+      <c r="R35" t="inlineStr">
         <is>
           <t>hot</t>
         </is>
       </c>
-      <c r="R35" t="n">
-        <v>0</v>
-      </c>
-      <c r="S35" t="inlineStr"/>
-      <c r="T35" t="inlineStr">
+      <c r="S35" t="n">
+        <v>0</v>
+      </c>
+      <c r="T35" t="inlineStr"/>
+      <c r="U35" t="inlineStr">
         <is>
           <t>1. In a bowl, mix ground lamb with grated onion, garlic, cumin, coriander, salt, and pepper. Form into small oval- shaped kofta patties.
 2. Preheat a grill pan over medium-high heat and grill the kofta for about 5–7 minutes until cooked through.
@@ -3925,8 +4100,8 @@
 6. Cook time: 15</t>
         </is>
       </c>
-      <c r="U35" t="inlineStr"/>
-      <c r="V35" t="inlineStr">
+      <c r="V35" t="inlineStr"/>
+      <c r="W35" t="inlineStr">
         <is>
           <t>['In a bowl, mix ground lamb with grated onion, garlic, cumin, coriander, salt, and pepper. Form into small oval- shaped kofta patties.', 'Preheat a grill pan over medium-high heat and grill the kofta for about 5–7 minutes until cooked through.', 'Meanwhile, bring vegetable broth to a boil; stir in couscous, cover, and let sit for 5 minutes, then fluff with a fork.', 'Stir in chopped mint and lemon juice into the couscous.', 'Serve the grilled lamb kofta over the couscous.', 'Cook time: 15']</t>
         </is>
@@ -3945,15 +4120,20 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Oil Free Grilled Fish with Sumac Rice Pilaf</t>
+          <t>Oil Free Grilled Fish With Sumac Rice Pilaf</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
+          <t>3346</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
           <t>['8 oz white fish fillet (cod or tilapia)', 'Juice of 1 lemon', '1 tsp ground sumac', 'Salt and pepper, to taste', '2 cups cooked basmati rice', '1 cup diced tomatoes', '½ cup diced cucumbers', '¼ cup chopped fresh parsley', 'Extra lemon wedges, for serving']</t>
         </is>
       </c>
-      <c r="E36" t="inlineStr">
+      <c r="F36" t="inlineStr">
         <is>
           <t>1. Season the fish fillet with lemon juice, sumac, salt, and pepper.
 2. Preheat a grill or grill pan over medium heat and grill the fish for 4–5 minutes per side until it flakes easily.
@@ -3962,59 +4142,59 @@
 5. Cook time: 10</t>
         </is>
       </c>
-      <c r="F36" t="inlineStr">
+      <c r="G36" t="inlineStr">
         <is>
           <t>{"calories": 500, "protein": "35 g", "carbs": "60 g", "fiber": "8 g", "fat": "8 g"}</t>
         </is>
       </c>
-      <c r="G36" t="n">
+      <c r="H36" t="n">
         <v>2</v>
       </c>
-      <c r="H36" t="n">
+      <c r="I36" t="n">
         <v>15</v>
       </c>
-      <c r="I36" t="inlineStr">
-        <is>
-          <t>['weight-loss', 'plant-based', 'whole-foods', 'oil-free', 'lunches-and-dinners', 'soups', 'salads', 'wraps', 'sandwiches', 'rice', 'stews', 'stir-fry', 'seafood', 'ethnic', 'arabic', 'desserts']</t>
-        </is>
-      </c>
       <c r="J36" t="inlineStr">
         <is>
+          <t>['animal-protein', 'arabic', 'ethnic', 'lunches-and-dinners', 'oil-free', 'rice', 'seafood', 'weight-loss']</t>
+        </is>
+      </c>
+      <c r="K36" t="inlineStr">
+        <is>
           <t>oil_free</t>
         </is>
       </c>
-      <c r="K36" t="inlineStr">
+      <c r="L36" t="inlineStr">
         <is>
           <t>plant_based</t>
         </is>
       </c>
-      <c r="L36" t="inlineStr">
+      <c r="M36" t="inlineStr">
         <is>
           <t>Savory</t>
         </is>
       </c>
-      <c r="M36" t="inlineStr">
+      <c r="N36" t="inlineStr">
         <is>
           <t>weight_loss</t>
         </is>
       </c>
-      <c r="N36" t="b">
-        <v>0</v>
-      </c>
       <c r="O36" t="b">
         <v>0</v>
       </c>
-      <c r="P36" t="inlineStr"/>
-      <c r="Q36" t="inlineStr">
+      <c r="P36" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q36" t="inlineStr"/>
+      <c r="R36" t="inlineStr">
         <is>
           <t>hot</t>
         </is>
       </c>
-      <c r="R36" t="n">
-        <v>0</v>
-      </c>
-      <c r="S36" t="inlineStr"/>
-      <c r="T36" t="inlineStr">
+      <c r="S36" t="n">
+        <v>0</v>
+      </c>
+      <c r="T36" t="inlineStr"/>
+      <c r="U36" t="inlineStr">
         <is>
           <t>1. Season the fish fillet with lemon juice, sumac, salt, and pepper.
 2. Preheat a grill or grill pan over medium heat and grill the fish for 4–5 minutes per side until it flakes easily.
@@ -4023,8 +4203,8 @@
 5. Cook time: 10</t>
         </is>
       </c>
-      <c r="U36" t="inlineStr"/>
-      <c r="V36" t="inlineStr">
+      <c r="V36" t="inlineStr"/>
+      <c r="W36" t="inlineStr">
         <is>
           <t>['Season the fish fillet with lemon juice, sumac, salt, and pepper.', 'Preheat a grill or grill pan over medium heat and grill the fish for 4–5 minutes per side until it flakes easily.', 'In a bowl, combine cooked basmati rice with diced tomatoes, cucumbers, and chopped parsley.', 'Serve the grilled fish over the rice pilaf with an extra squeeze of lemon.', 'Cook time: 10']</t>
         </is>
@@ -4043,15 +4223,20 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Oil Free Stuffed Zucchini with Ground Turkey</t>
+          <t>Oil Free Stuffed Zucchini With Ground Turkey</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
+          <t>3347</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
           <t>['4 medium zucchinis, halved lengthwise and seeded', '1 lb lean ground turkey', '1 small onion, finely chopped', '2 garlic cloves, minced', '1 large tomato, diced', '1 tsp ground cumin', '½ tsp ground cinnamon', 'Salt and pepper, to taste', '¼ cup chopped fresh parsley', 'Juice of 1 lemon']</t>
         </is>
       </c>
-      <c r="E37" t="inlineStr">
+      <c r="F37" t="inlineStr">
         <is>
           <t>1. Preheat oven to 375°F (190°C).
 2. In a pan, sauté onion and garlic (using a splash of water) until softened. Add ground turkey, tomato, cumin, cinnamon, salt, and pepper; cook until turkey is done.
@@ -4061,59 +4246,59 @@
 6. Cook time: 25</t>
         </is>
       </c>
-      <c r="F37" t="inlineStr">
+      <c r="G37" t="inlineStr">
         <is>
           <t>{"calories": 480, "protein": "35 g", "carbs": "50 g", "fiber": "7 g", "fat": "8 g"}</t>
         </is>
       </c>
-      <c r="G37" t="n">
+      <c r="H37" t="n">
         <v>4</v>
       </c>
-      <c r="H37" t="n">
+      <c r="I37" t="n">
         <v>25</v>
       </c>
-      <c r="I37" t="inlineStr">
-        <is>
-          <t>['weight-loss', 'plant-based', 'whole-foods', 'oil-free', 'lunches-and-dinners', 'soups', 'salads', 'wraps', 'sandwiches', 'rice', 'stews', 'stir-fry', 'seafood', 'ethnic', 'arabic', 'desserts']</t>
-        </is>
-      </c>
       <c r="J37" t="inlineStr">
         <is>
+          <t>['animal-protein', 'arabic', 'ethnic', 'lunches-and-dinners', 'oil-free', 'weight-loss']</t>
+        </is>
+      </c>
+      <c r="K37" t="inlineStr">
+        <is>
           <t>oil_free</t>
         </is>
       </c>
-      <c r="K37" t="inlineStr">
+      <c r="L37" t="inlineStr">
         <is>
           <t>plant_based</t>
         </is>
       </c>
-      <c r="L37" t="inlineStr">
+      <c r="M37" t="inlineStr">
         <is>
           <t>Savory</t>
         </is>
       </c>
-      <c r="M37" t="inlineStr">
+      <c r="N37" t="inlineStr">
         <is>
           <t>weight_loss</t>
         </is>
       </c>
-      <c r="N37" t="b">
-        <v>0</v>
-      </c>
       <c r="O37" t="b">
         <v>0</v>
       </c>
-      <c r="P37" t="inlineStr"/>
-      <c r="Q37" t="inlineStr">
+      <c r="P37" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q37" t="inlineStr"/>
+      <c r="R37" t="inlineStr">
         <is>
           <t>hot</t>
         </is>
       </c>
-      <c r="R37" t="n">
-        <v>0</v>
-      </c>
-      <c r="S37" t="inlineStr"/>
-      <c r="T37" t="inlineStr">
+      <c r="S37" t="n">
+        <v>0</v>
+      </c>
+      <c r="T37" t="inlineStr"/>
+      <c r="U37" t="inlineStr">
         <is>
           <t>1. Preheat oven to 375°F (190°C).
 2. In a pan, sauté onion and garlic (using a splash of water) until softened. Add ground turkey, tomato, cumin, cinnamon, salt, and pepper; cook until turkey is done.
@@ -4123,8 +4308,8 @@
 6. Cook time: 25</t>
         </is>
       </c>
-      <c r="U37" t="inlineStr"/>
-      <c r="V37" t="inlineStr">
+      <c r="V37" t="inlineStr"/>
+      <c r="W37" t="inlineStr">
         <is>
           <t>['Preheat oven to 375°F (190°C).', 'In a pan, sauté onion and garlic (using a splash of water) until softened. Add ground turkey, tomato, cumin, cinnamon, salt, and pepper; cook until turkey is done.', 'Stir in chopped parsley and lemon juice.', 'Scoop out the centers of each zucchini half and fill with the turkey mixture.', 'Place stuffed zucchinis in a baking dish, cover with foil, and bake for 25 minutes until zucchini is tender.', 'Cook time: 25']</t>
         </is>
@@ -4143,15 +4328,20 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Oil Free Arabic Date and Walnut Biscotti</t>
+          <t>Oil Free Arabic Date And Walnut Biscotti</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
+          <t>3348</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
           <t>['1 ½ cups whole wheat flour', '½ cup semolina', '1 tsp baking powder', '¼ tsp salt', '½ cup unsweetened applesauce', '⅓ cup honey or maple syrup', '1 tsp ground cinnamon', '½ cup chopped dates', '½ cup chopped walnuts', '1 tsp vanilla extract']</t>
         </is>
       </c>
-      <c r="E38" t="inlineStr">
+      <c r="F38" t="inlineStr">
         <is>
           <t>1. Preheat oven to 350°F (175°C).
 2. In a large bowl, whisk together whole wheat flour, semolina, baking powder, salt, and cinnamon.
@@ -4162,59 +4352,59 @@
 7. Cook time: 40</t>
         </is>
       </c>
-      <c r="F38" t="inlineStr">
+      <c r="G38" t="inlineStr">
         <is>
           <t>{"calories": 180, "protein": "5 g", "carbs": "32 g", "fiber": "4 g", "fat": "3 g"}</t>
         </is>
       </c>
-      <c r="G38" t="n">
+      <c r="H38" t="n">
         <v>10</v>
       </c>
-      <c r="H38" t="n">
+      <c r="I38" t="n">
         <v>20</v>
       </c>
-      <c r="I38" t="inlineStr">
-        <is>
-          <t>['weight-loss', 'plant-based', 'whole-foods', 'oil-free', 'lunches-and-dinners', 'soups', 'salads', 'wraps', 'sandwiches', 'rice', 'stews', 'stir-fry', 'seafood', 'ethnic', 'arabic', 'desserts']</t>
-        </is>
-      </c>
       <c r="J38" t="inlineStr">
         <is>
+          <t>['arabic', 'desserts', 'ethnic', 'oil-free', 'vegetarian', 'weight-loss']</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr">
+        <is>
           <t>oil_free</t>
         </is>
       </c>
-      <c r="K38" t="inlineStr">
-        <is>
-          <t>plant_based</t>
-        </is>
-      </c>
       <c r="L38" t="inlineStr">
         <is>
+          <t>Vegetarian</t>
+        </is>
+      </c>
+      <c r="M38" t="inlineStr">
+        <is>
           <t>Savory</t>
         </is>
       </c>
-      <c r="M38" t="inlineStr">
+      <c r="N38" t="inlineStr">
         <is>
           <t>weight_loss</t>
         </is>
       </c>
-      <c r="N38" t="b">
-        <v>0</v>
-      </c>
       <c r="O38" t="b">
         <v>0</v>
       </c>
-      <c r="P38" t="inlineStr"/>
-      <c r="Q38" t="inlineStr">
+      <c r="P38" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q38" t="inlineStr"/>
+      <c r="R38" t="inlineStr">
         <is>
           <t>hot</t>
         </is>
       </c>
-      <c r="R38" t="n">
-        <v>0</v>
-      </c>
-      <c r="S38" t="inlineStr"/>
-      <c r="T38" t="inlineStr">
+      <c r="S38" t="n">
+        <v>0</v>
+      </c>
+      <c r="T38" t="inlineStr"/>
+      <c r="U38" t="inlineStr">
         <is>
           <t>1. Preheat oven to 350°F (175°C).
 2. In a large bowl, whisk together whole wheat flour, semolina, baking powder, salt, and cinnamon.
@@ -4225,8 +4415,8 @@
 7. Cook time: 40</t>
         </is>
       </c>
-      <c r="U38" t="inlineStr"/>
-      <c r="V38" t="inlineStr">
+      <c r="V38" t="inlineStr"/>
+      <c r="W38" t="inlineStr">
         <is>
           <t>['Preheat oven to 350°F (175°C).', 'In a large bowl, whisk together whole wheat flour, semolina, baking powder, salt, and cinnamon.', 'In another bowl, mix unsweetened applesauce, honey, vanilla extract until smooth.', 'Combine the wet and dry ingredients; fold in chopped dates and walnuts.', 'Shape the dough into a log and place on a parchment lined baking sheet. Bake for 25 minutes.', 'Remove from oven, let cool for 10 minutes, then slice into biscotti and return to the oven for 15 minutes to crisp.', 'Cook time: 40']</t>
         </is>
@@ -4245,15 +4435,20 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Oil Free Baked Kofta with Tomato Sauce</t>
+          <t>Oil Free Baked Kofta With Tomato Sauce</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
+          <t>3349</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
           <t>['1 lb lean ground beef or lamb', '1 small onion, grated', '2 garlic cloves, minced', '1 tsp ground cumin', '1 tsp ground coriander', '1/2 tsp ground allspice', 'Salt and pepper, to taste', '2 cups crushed tomatoes (no oil added)', '1 tsp dried oregano', '1/2 tsp sugar (optional)', '1/4 cup water', 'Fresh parsley, chopped (for garnish)']</t>
         </is>
       </c>
-      <c r="E39" t="inlineStr">
+      <c r="F39" t="inlineStr">
         <is>
           <t>1. In a bowl, mix the ground meat with grated onion, garlic, cumin, coriander, allspice, salt, and pepper. Form into small oval patties (kofta).
 2. Place the kofta in a baking dish.
@@ -4263,59 +4458,59 @@
 6. Cook time: 30</t>
         </is>
       </c>
-      <c r="F39" t="inlineStr">
+      <c r="G39" t="inlineStr">
         <is>
           <t>{"calories": 480, "protein": "30 g", "carbs": "50 g", "fiber": "7 g", "fat": "8 g"}</t>
         </is>
       </c>
-      <c r="G39" t="n">
+      <c r="H39" t="n">
         <v>4</v>
       </c>
-      <c r="H39" t="n">
+      <c r="I39" t="n">
         <v>25</v>
       </c>
-      <c r="I39" t="inlineStr">
-        <is>
-          <t>['weight-loss', 'plant-based', 'whole-foods', 'oil-free', 'lunches-and-dinners', 'soups', 'salads', 'wraps', 'sandwiches', 'rice', 'stews', 'stir-fry', 'seafood', 'ethnic', 'arabic', 'desserts']</t>
-        </is>
-      </c>
       <c r="J39" t="inlineStr">
         <is>
+          <t>['animal-protein', 'arabic', 'ethnic', 'lunches-and-dinners', 'oil-free', 'weight-loss']</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr">
+        <is>
           <t>oil_free</t>
         </is>
       </c>
-      <c r="K39" t="inlineStr">
+      <c r="L39" t="inlineStr">
         <is>
           <t>plant_based</t>
         </is>
       </c>
-      <c r="L39" t="inlineStr">
+      <c r="M39" t="inlineStr">
         <is>
           <t>Savory</t>
         </is>
       </c>
-      <c r="M39" t="inlineStr">
+      <c r="N39" t="inlineStr">
         <is>
           <t>weight_loss</t>
         </is>
       </c>
-      <c r="N39" t="b">
-        <v>0</v>
-      </c>
       <c r="O39" t="b">
         <v>0</v>
       </c>
-      <c r="P39" t="inlineStr"/>
-      <c r="Q39" t="inlineStr">
+      <c r="P39" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q39" t="inlineStr"/>
+      <c r="R39" t="inlineStr">
         <is>
           <t>hot</t>
         </is>
       </c>
-      <c r="R39" t="n">
-        <v>0</v>
-      </c>
-      <c r="S39" t="inlineStr"/>
-      <c r="T39" t="inlineStr">
+      <c r="S39" t="n">
+        <v>0</v>
+      </c>
+      <c r="T39" t="inlineStr"/>
+      <c r="U39" t="inlineStr">
         <is>
           <t>1. In a bowl, mix the ground meat with grated onion, garlic, cumin, coriander, allspice, salt, and pepper. Form into small oval patties (kofta).
 2. Place the kofta in a baking dish.
@@ -4325,8 +4520,8 @@
 6. Cook time: 30</t>
         </is>
       </c>
-      <c r="U39" t="inlineStr"/>
-      <c r="V39" t="inlineStr">
+      <c r="V39" t="inlineStr"/>
+      <c r="W39" t="inlineStr">
         <is>
           <t>['In a bowl, mix the ground meat with grated onion, garlic, cumin, coriander, allspice, salt, and pepper. Form into small oval patties (kofta).', 'Place the kofta in a baking dish.', 'In a separate bowl, combine crushed tomatoes, oregano, sugar, and water. Pour over the kofta.', 'Cover and bake in a preheated 375°F (190°C) oven for 30 minutes until the meat is cooked through.', 'Garnish with fresh parsley and serve with a side of whole wheat flatbread.', 'Cook time: 30']</t>
         </is>
@@ -4350,10 +4545,15 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
+          <t>3350</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
           <t>['1 lb chicken breast, boiled and shredded', '2 cups cooked basmati rice', '1 piece whole wheat pita, baked until crisp and broken into pieces', '1 cup low fat plain yogurt (or fat free if preferred)', '2 garlic cloves, minced', 'Juice of 1 lemon', 'Salt and pepper, to taste', '1/4 cup chopped fresh parsley', '1/2 tsp ground sumac']</t>
         </is>
       </c>
-      <c r="E40" t="inlineStr">
+      <c r="F40" t="inlineStr">
         <is>
           <t>1. In a bowl, combine yogurt with minced garlic, lemon juice, salt, pepper, and ground sumac to make a tangy sauce.
 2. In a serving dish, layer the crispy pita pieces, followed by basmati rice, and then the shredded chicken.
@@ -4362,59 +4562,59 @@
 5. Cook time: 00</t>
         </is>
       </c>
-      <c r="F40" t="inlineStr">
+      <c r="G40" t="inlineStr">
         <is>
           <t>{"calories": 520, "protein": "36 g", "carbs": "65 g", "fiber": "7 g", "fat": "8 g"}</t>
         </is>
       </c>
-      <c r="G40" t="n">
+      <c r="H40" t="n">
         <v>4</v>
       </c>
-      <c r="H40" t="n">
+      <c r="I40" t="n">
         <v>20</v>
       </c>
-      <c r="I40" t="inlineStr">
-        <is>
-          <t>['weight-loss', 'plant-based', 'whole-foods', 'oil-free', 'lunches-and-dinners', 'soups', 'salads', 'wraps', 'sandwiches', 'rice', 'stews', 'stir-fry', 'seafood', 'ethnic', 'arabic', 'desserts']</t>
-        </is>
-      </c>
       <c r="J40" t="inlineStr">
         <is>
+          <t>['animal-protein', 'arabic', 'ethnic', 'lunches-and-dinners', 'oil-free', 'weight-loss']</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr">
+        <is>
           <t>oil_free</t>
         </is>
       </c>
-      <c r="K40" t="inlineStr">
+      <c r="L40" t="inlineStr">
         <is>
           <t>plant_based</t>
         </is>
       </c>
-      <c r="L40" t="inlineStr">
+      <c r="M40" t="inlineStr">
         <is>
           <t>Savory</t>
         </is>
       </c>
-      <c r="M40" t="inlineStr">
+      <c r="N40" t="inlineStr">
         <is>
           <t>weight_loss</t>
         </is>
       </c>
-      <c r="N40" t="b">
-        <v>0</v>
-      </c>
       <c r="O40" t="b">
         <v>0</v>
       </c>
-      <c r="P40" t="inlineStr"/>
-      <c r="Q40" t="inlineStr">
+      <c r="P40" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q40" t="inlineStr"/>
+      <c r="R40" t="inlineStr">
         <is>
           <t>hot</t>
         </is>
       </c>
-      <c r="R40" t="n">
-        <v>0</v>
-      </c>
-      <c r="S40" t="inlineStr"/>
-      <c r="T40" t="inlineStr">
+      <c r="S40" t="n">
+        <v>0</v>
+      </c>
+      <c r="T40" t="inlineStr"/>
+      <c r="U40" t="inlineStr">
         <is>
           <t>1. In a bowl, combine yogurt with minced garlic, lemon juice, salt, pepper, and ground sumac to make a tangy sauce.
 2. In a serving dish, layer the crispy pita pieces, followed by basmati rice, and then the shredded chicken.
@@ -4423,8 +4623,8 @@
 5. Cook time: 00</t>
         </is>
       </c>
-      <c r="U40" t="inlineStr"/>
-      <c r="V40" t="inlineStr">
+      <c r="V40" t="inlineStr"/>
+      <c r="W40" t="inlineStr">
         <is>
           <t>['In a bowl, combine yogurt with minced garlic, lemon juice, salt, pepper, and ground sumac to make a tangy sauce.', 'In a serving dish, layer the crispy pita pieces, followed by basmati rice, and then the shredded chicken.', 'Generously spoon the garlic-yogurt sauce over the top.', 'Garnish with chopped parsley and serve immediately.', 'Cook time: 00']</t>
         </is>
@@ -4448,10 +4648,15 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
+          <t>3351</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
           <t>['For the Dough:', '2 cups whole wheat flour', '1 tsp instant yeast', '1/2 tsp salt', '3/4 cup warm water (adjust as needed)', '1 tsp lemon juice', 'For the Filling:', '1 lb lean ground beef', '1 small onion, finely chopped', '2 garlic cloves, minced', '1 tsp ground allspice', '1/2 tsp ground cinnamon', '1 large tomato, diced', 'Salt and pepper, to taste', '1/4 cup chopped fresh parsley']</t>
         </is>
       </c>
-      <c r="E41" t="inlineStr">
+      <c r="F41" t="inlineStr">
         <is>
           <t>1. In a bowl, combine flour, yeast, salt, warm water, and lemon juice to form a smooth dough; let rise for 1 hour until doubled.
 2. Meanwhile, prepare the filling by sautéing onion and garlic (using a splash of water) in a nonstick pan until softened. Add ground beef, tomato, allspice, cinnamon, salt, and pepper; cook until beef is browned and the flavors meld. Stir in parsley.
@@ -4461,59 +4666,59 @@
 6. Cook time: 25</t>
         </is>
       </c>
-      <c r="F41" t="inlineStr">
+      <c r="G41" t="inlineStr">
         <is>
           <t>{"calories": 540, "protein": "32 g", "carbs": "65 g", "fiber": "8 g", "fat": "10 g"}</t>
         </is>
       </c>
-      <c r="G41" t="n">
+      <c r="H41" t="n">
         <v>4</v>
       </c>
-      <c r="H41" t="n">
+      <c r="I41" t="n">
         <v>30</v>
       </c>
-      <c r="I41" t="inlineStr">
-        <is>
-          <t>['weight-loss', 'plant-based', 'whole-foods', 'oil-free', 'lunches-and-dinners', 'soups', 'salads', 'wraps', 'sandwiches', 'rice', 'stews', 'stir-fry', 'seafood', 'ethnic', 'arabic', 'desserts']</t>
-        </is>
-      </c>
       <c r="J41" t="inlineStr">
         <is>
+          <t>['animal-protein', 'arabic', 'ethnic', 'lunches-and-dinners', 'oil-free', 'weight-loss']</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr">
+        <is>
           <t>oil_free</t>
         </is>
       </c>
-      <c r="K41" t="inlineStr">
+      <c r="L41" t="inlineStr">
         <is>
           <t>plant_based</t>
         </is>
       </c>
-      <c r="L41" t="inlineStr">
+      <c r="M41" t="inlineStr">
         <is>
           <t>Savory</t>
         </is>
       </c>
-      <c r="M41" t="inlineStr">
+      <c r="N41" t="inlineStr">
         <is>
           <t>weight_loss</t>
         </is>
       </c>
-      <c r="N41" t="b">
-        <v>0</v>
-      </c>
       <c r="O41" t="b">
         <v>0</v>
       </c>
-      <c r="P41" t="inlineStr"/>
-      <c r="Q41" t="inlineStr">
+      <c r="P41" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q41" t="inlineStr"/>
+      <c r="R41" t="inlineStr">
         <is>
           <t>hot</t>
         </is>
       </c>
-      <c r="R41" t="n">
-        <v>0</v>
-      </c>
-      <c r="S41" t="inlineStr"/>
-      <c r="T41" t="inlineStr">
+      <c r="S41" t="n">
+        <v>0</v>
+      </c>
+      <c r="T41" t="inlineStr"/>
+      <c r="U41" t="inlineStr">
         <is>
           <t>1. In a bowl, combine flour, yeast, salt, warm water, and lemon juice to form a smooth dough; let rise for 1 hour until doubled.
 2. Meanwhile, prepare the filling by sautéing onion and garlic (using a splash of water) in a nonstick pan until softened. Add ground beef, tomato, allspice, cinnamon, salt, and pepper; cook until beef is browned and the flavors meld. Stir in parsley.
@@ -4523,8 +4728,8 @@
 6. Cook time: 25</t>
         </is>
       </c>
-      <c r="U41" t="inlineStr"/>
-      <c r="V41" t="inlineStr">
+      <c r="V41" t="inlineStr"/>
+      <c r="W41" t="inlineStr">
         <is>
           <t>['In a bowl, combine flour, yeast, salt, warm water, and lemon juice to form a smooth dough; let rise for 1 hour until doubled.', 'Meanwhile, prepare the filling by sautéing onion and garlic (using a splash of water) in a nonstick pan until softened. Add ground beef, tomato, allspice, cinnamon, salt, and pepper; cook until beef is browned and the flavors meld. Stir in parsley.', 'Preheat oven to 375°F (190°C). Divide the dough into 10 equal balls; roll each into a thin circle.', 'Place 2–3 tablespoons of filling in the center of each circle, fold up the edges, and shape into an open-faced pie.', 'Place on a parchment lined baking sheet and bake for 20– 25 minutes until the dough is cooked through.', 'Cook time: 25']</t>
         </is>
@@ -4543,15 +4748,20 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Oil Free Arabic Lamb Stew with Barley</t>
+          <t>Oil Free Arabic Lamb Stew With Barley</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
+          <t>3352</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
           <t>['1 lb lean lamb stew meat, cut into 1 inch cubes', '1 cup pearl barley, rinsed', '1 large onion, chopped', '2 garlic cloves, minced', '1 tsp ground cumin', '1 tsp ground coriander', '1 large tomato, diced', '4 cups low sodium lamb or vegetable broth', 'Salt and pepper, to taste', 'Fresh cilantro, chopped (for garnish)']</t>
         </is>
       </c>
-      <c r="E42" t="inlineStr">
+      <c r="F42" t="inlineStr">
         <is>
           <t>1. In a heavy pot, combine lamb, onion, garlic, cumin, and coriander. Sauté using a splash of water until the onion softens.
 2. Add diced tomato and broth; bring to a boil, then reduce heat and simmer for 1–1½ hours until the lamb is tender.
@@ -4560,59 +4770,59 @@
 5. Cook time: 1</t>
         </is>
       </c>
-      <c r="F42" t="inlineStr">
+      <c r="G42" t="inlineStr">
         <is>
           <t>{"calories": 520, "protein": "38 g", "carbs": "60 g", "fiber": "8 g", "fat": "10 g"}</t>
         </is>
       </c>
-      <c r="G42" t="n">
+      <c r="H42" t="n">
         <v>4</v>
       </c>
-      <c r="H42" t="n">
+      <c r="I42" t="n">
         <v>25</v>
       </c>
-      <c r="I42" t="inlineStr">
-        <is>
-          <t>['weight-loss', 'plant-based', 'whole-foods', 'oil-free', 'lunches-and-dinners', 'soups', 'salads', 'wraps', 'sandwiches', 'rice', 'stews', 'stir-fry', 'seafood', 'ethnic', 'arabic', 'desserts']</t>
-        </is>
-      </c>
       <c r="J42" t="inlineStr">
         <is>
+          <t>['animal-protein', 'arabic', 'ethnic', 'lunches-and-dinners', 'oil-free', 'stews', 'weight-loss']</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr">
+        <is>
           <t>oil_free</t>
         </is>
       </c>
-      <c r="K42" t="inlineStr">
+      <c r="L42" t="inlineStr">
         <is>
           <t>plant_based</t>
         </is>
       </c>
-      <c r="L42" t="inlineStr">
+      <c r="M42" t="inlineStr">
         <is>
           <t>Savory</t>
         </is>
       </c>
-      <c r="M42" t="inlineStr">
+      <c r="N42" t="inlineStr">
         <is>
           <t>weight_loss</t>
         </is>
       </c>
-      <c r="N42" t="b">
-        <v>0</v>
-      </c>
       <c r="O42" t="b">
         <v>0</v>
       </c>
-      <c r="P42" t="inlineStr"/>
-      <c r="Q42" t="inlineStr">
+      <c r="P42" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q42" t="inlineStr"/>
+      <c r="R42" t="inlineStr">
         <is>
           <t>hot</t>
         </is>
       </c>
-      <c r="R42" t="n">
-        <v>0</v>
-      </c>
-      <c r="S42" t="inlineStr"/>
-      <c r="T42" t="inlineStr">
+      <c r="S42" t="n">
+        <v>0</v>
+      </c>
+      <c r="T42" t="inlineStr"/>
+      <c r="U42" t="inlineStr">
         <is>
           <t>1. In a heavy pot, combine lamb, onion, garlic, cumin, and coriander. Sauté using a splash of water until the onion softens.
 2. Add diced tomato and broth; bring to a boil, then reduce heat and simmer for 1–1½ hours until the lamb is tender.
@@ -4621,8 +4831,8 @@
 5. Cook time: 1</t>
         </is>
       </c>
-      <c r="U42" t="inlineStr"/>
-      <c r="V42" t="inlineStr">
+      <c r="V42" t="inlineStr"/>
+      <c r="W42" t="inlineStr">
         <is>
           <t>['In a heavy pot, combine lamb, onion, garlic, cumin, and coriander. Sauté using a splash of water until the onion softens.', 'Add diced tomato and broth; bring to a boil, then reduce heat and simmer for 1–1½ hours until the lamb is tender.', 'Stir in pearl barley and continue simmering for another 30 minutes until barley is cooked and the stew has thickened.', 'Adjust seasonings with salt and pepper, garnish with fresh cilantro, and serve warm.', 'Cook time: 1']</t>
         </is>
@@ -4641,15 +4851,20 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Oil Free Lamb Moussaka with Zucchini</t>
+          <t>Oil Free Lamb Moussaka With Zucchini</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
+          <t>3353</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
           <t>['1 lb lean lamb stew meat, cut into 1 inch cubes', '2 medium zucchinis, sliced into ½ inch rounds', '1 large eggplant, sliced into ½ inch rounds', '1 large tomato, diced', '1 small onion, finely chopped', '2 garlic cloves, minced', '1 tsp ground cinnamon', '½ tsp ground allspice', 'Salt and pepper, to taste', '1 cup cooked brown rice', 'Fresh parsley, chopped (for garnish)']</t>
         </is>
       </c>
-      <c r="E43" t="inlineStr">
+      <c r="F43" t="inlineStr">
         <is>
           <t>1. Preheat oven to 375°F (190°C).
 2. Arrange zucchini and eggplant slices on a baking sheet; roast in the oven for 20 minutes until tender and lightly browned.
@@ -4661,59 +4876,59 @@
 8. Cook time: 45</t>
         </is>
       </c>
-      <c r="F43" t="inlineStr">
+      <c r="G43" t="inlineStr">
         <is>
           <t>{"calories": 540, "protein": "35 g", "carbs": "65 g", "fiber": "8 g", "fat": "10 g"}</t>
         </is>
       </c>
-      <c r="G43" t="n">
+      <c r="H43" t="n">
         <v>4</v>
       </c>
-      <c r="H43" t="n">
+      <c r="I43" t="n">
         <v>30</v>
       </c>
-      <c r="I43" t="inlineStr">
-        <is>
-          <t>['weight-loss', 'plant-based', 'whole-foods', 'oil-free', 'lunches-and-dinners', 'soups', 'salads', 'wraps', 'sandwiches', 'rice', 'stews', 'stir-fry', 'seafood', 'ethnic', 'arabic', 'desserts']</t>
-        </is>
-      </c>
       <c r="J43" t="inlineStr">
         <is>
+          <t>['animal-protein', 'arabic', 'ethnic', 'lunches-and-dinners', 'oil-free', 'weight-loss']</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr">
+        <is>
           <t>oil_free</t>
         </is>
       </c>
-      <c r="K43" t="inlineStr">
+      <c r="L43" t="inlineStr">
         <is>
           <t>plant_based</t>
         </is>
       </c>
-      <c r="L43" t="inlineStr">
+      <c r="M43" t="inlineStr">
         <is>
           <t>Savory</t>
         </is>
       </c>
-      <c r="M43" t="inlineStr">
+      <c r="N43" t="inlineStr">
         <is>
           <t>weight_loss</t>
         </is>
       </c>
-      <c r="N43" t="b">
-        <v>0</v>
-      </c>
       <c r="O43" t="b">
         <v>0</v>
       </c>
-      <c r="P43" t="inlineStr"/>
-      <c r="Q43" t="inlineStr">
+      <c r="P43" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q43" t="inlineStr"/>
+      <c r="R43" t="inlineStr">
         <is>
           <t>hot</t>
         </is>
       </c>
-      <c r="R43" t="n">
-        <v>0</v>
-      </c>
-      <c r="S43" t="inlineStr"/>
-      <c r="T43" t="inlineStr">
+      <c r="S43" t="n">
+        <v>0</v>
+      </c>
+      <c r="T43" t="inlineStr"/>
+      <c r="U43" t="inlineStr">
         <is>
           <t>1. Preheat oven to 375°F (190°C).
 2. Arrange zucchini and eggplant slices on a baking sheet; roast in the oven for 20 minutes until tender and lightly browned.
@@ -4725,8 +4940,8 @@
 8. Cook time: 45</t>
         </is>
       </c>
-      <c r="U43" t="inlineStr"/>
-      <c r="V43" t="inlineStr">
+      <c r="V43" t="inlineStr"/>
+      <c r="W43" t="inlineStr">
         <is>
           <t>['Preheat oven to 375°F (190°C).', 'Arrange zucchini and eggplant slices on a baking sheet; roast in the oven for 20 minutes until tender and lightly browned.', 'In a nonstick pan (using a splash of water), sauté onion and garlic until soft. Add lamb cubes, diced tomato, cinnamon, allspice, salt, and pepper; cook until lamb is browned and nearly tender (about 10 minutes).', 'Stir in cooked brown rice and mix well.', 'In a baking dish, layer the roasted zucchini and eggplant, then spoon the lamb and rice mixture over the top.', 'Bake for an additional 25 minutes until heated through.', 'Garnish with fresh parsley before serving.', 'Cook time: 45']</t>
         </is>
@@ -4745,15 +4960,20 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Oil Free Stuffed Vegetables (Mahshi) with Rice &amp; Beef</t>
+          <t>Oil Free Stuffed Vegetables (Mahshi) With Rice &amp; Beef</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
+          <t>3354</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
           <t>['4 medium bell peppers or zucchinis, tops removed and hollowed', '1 lb lean ground beef', '1 cup short grain rice, rinsed', '1 small onion, finely chopped', '2 garlic cloves, minced', '1 large tomato, diced', '1 tsp ground allspice', '½ tsp ground cinnamon', 'Salt and pepper, to taste', '2 cups low sodium vegetable broth', 'Fresh mint or parsley, chopped (for garnish)']</t>
         </is>
       </c>
-      <c r="E44" t="inlineStr">
+      <c r="F44" t="inlineStr">
         <is>
           <t>1. In a bowl, combine ground beef, rice, onion, garlic, tomato, allspice, cinnamon, salt, and pepper.
 2. Stuff each hollowed vegetable with the beef-rice mixture.
@@ -4763,59 +4983,59 @@
 6. Cook time: 40</t>
         </is>
       </c>
-      <c r="F44" t="inlineStr">
+      <c r="G44" t="inlineStr">
         <is>
           <t>{"calories": 530, "protein": "32 g", "carbs": "60 g", "fiber": "7 g", "fat": "8 g"}</t>
         </is>
       </c>
-      <c r="G44" t="n">
+      <c r="H44" t="n">
         <v>4</v>
       </c>
-      <c r="H44" t="n">
+      <c r="I44" t="n">
         <v>30</v>
       </c>
-      <c r="I44" t="inlineStr">
-        <is>
-          <t>['weight-loss', 'plant-based', 'whole-foods', 'oil-free', 'lunches-and-dinners', 'soups', 'salads', 'wraps', 'sandwiches', 'rice', 'stews', 'stir-fry', 'seafood', 'ethnic', 'arabic', 'desserts']</t>
-        </is>
-      </c>
       <c r="J44" t="inlineStr">
         <is>
+          <t>['animal-protein', 'arabic', 'ethnic', 'lunches-and-dinners', 'oil-free', 'rice', 'weight-loss']</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr">
+        <is>
           <t>oil_free</t>
         </is>
       </c>
-      <c r="K44" t="inlineStr">
+      <c r="L44" t="inlineStr">
         <is>
           <t>plant_based</t>
         </is>
       </c>
-      <c r="L44" t="inlineStr">
+      <c r="M44" t="inlineStr">
         <is>
           <t>Savory</t>
         </is>
       </c>
-      <c r="M44" t="inlineStr">
+      <c r="N44" t="inlineStr">
         <is>
           <t>weight_loss</t>
         </is>
       </c>
-      <c r="N44" t="b">
-        <v>0</v>
-      </c>
       <c r="O44" t="b">
         <v>0</v>
       </c>
-      <c r="P44" t="inlineStr"/>
-      <c r="Q44" t="inlineStr">
+      <c r="P44" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q44" t="inlineStr"/>
+      <c r="R44" t="inlineStr">
         <is>
           <t>hot</t>
         </is>
       </c>
-      <c r="R44" t="n">
-        <v>0</v>
-      </c>
-      <c r="S44" t="inlineStr"/>
-      <c r="T44" t="inlineStr">
+      <c r="S44" t="n">
+        <v>0</v>
+      </c>
+      <c r="T44" t="inlineStr"/>
+      <c r="U44" t="inlineStr">
         <is>
           <t>1. In a bowl, combine ground beef, rice, onion, garlic, tomato, allspice, cinnamon, salt, and pepper.
 2. Stuff each hollowed vegetable with the beef-rice mixture.
@@ -4825,8 +5045,8 @@
 6. Cook time: 40</t>
         </is>
       </c>
-      <c r="U44" t="inlineStr"/>
-      <c r="V44" t="inlineStr">
+      <c r="V44" t="inlineStr"/>
+      <c r="W44" t="inlineStr">
         <is>
           <t>['In a bowl, combine ground beef, rice, onion, garlic, tomato, allspice, cinnamon, salt, and pepper.', 'Stuff each hollowed vegetable with the beef-rice mixture.', 'Arrange the stuffed vegetables in a deep baking dish; pour vegetable broth over them.', 'Cover with foil and bake at 375°F (190°C) for 35–40 minutes until the vegetables are tender and the filling is cooked.', 'Garnish with fresh mint or parsley before serving.', 'Cook time: 40']</t>
         </is>
@@ -4845,15 +5065,20 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Oil Free Grilled Fish with Baharat Rice</t>
+          <t>Oil Free Grilled Fish With Baharat Rice</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
+          <t>3355</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
           <t>['8 oz white fish fillet (such as cod or tilapia)', 'Juice of 1 lemon', '1 tsp ground baharat spice blend', 'Salt and pepper, to taste', '2 cups cooked basmati rice', '1 cup diced tomatoes', '½ cup diced cucumbers', '¼ cup chopped fresh parsley', 'Lemon wedges, for serving']</t>
         </is>
       </c>
-      <c r="E45" t="inlineStr">
+      <c r="F45" t="inlineStr">
         <is>
           <t>1. Preparation Steps:
 2. Season the fish fillet with lemon juice, baharat, salt, and pepper.
@@ -4863,59 +5088,59 @@
 6. Cook time: 10</t>
         </is>
       </c>
-      <c r="F45" t="inlineStr">
+      <c r="G45" t="inlineStr">
         <is>
           <t>{"calories": 500, "protein": "35 g", "carbs": "60 g", "fiber": "8 g", "fat": "8 g"}</t>
         </is>
       </c>
-      <c r="G45" t="n">
+      <c r="H45" t="n">
         <v>2</v>
       </c>
-      <c r="H45" t="n">
+      <c r="I45" t="n">
         <v>15</v>
       </c>
-      <c r="I45" t="inlineStr">
-        <is>
-          <t>['weight-loss', 'plant-based', 'whole-foods', 'oil-free', 'lunches-and-dinners', 'soups', 'salads', 'wraps', 'sandwiches', 'rice', 'stews', 'stir-fry', 'seafood', 'ethnic', 'arabic', 'desserts']</t>
-        </is>
-      </c>
       <c r="J45" t="inlineStr">
         <is>
+          <t>['animal-protein', 'arabic', 'ethnic', 'lunches-and-dinners', 'oil-free', 'rice', 'seafood', 'weight-loss']</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr">
+        <is>
           <t>oil_free</t>
         </is>
       </c>
-      <c r="K45" t="inlineStr">
+      <c r="L45" t="inlineStr">
         <is>
           <t>plant_based</t>
         </is>
       </c>
-      <c r="L45" t="inlineStr">
+      <c r="M45" t="inlineStr">
         <is>
           <t>Savory</t>
         </is>
       </c>
-      <c r="M45" t="inlineStr">
+      <c r="N45" t="inlineStr">
         <is>
           <t>weight_loss</t>
         </is>
       </c>
-      <c r="N45" t="b">
-        <v>0</v>
-      </c>
       <c r="O45" t="b">
         <v>0</v>
       </c>
-      <c r="P45" t="inlineStr"/>
-      <c r="Q45" t="inlineStr">
+      <c r="P45" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q45" t="inlineStr"/>
+      <c r="R45" t="inlineStr">
         <is>
           <t>hot</t>
         </is>
       </c>
-      <c r="R45" t="n">
-        <v>0</v>
-      </c>
-      <c r="S45" t="inlineStr"/>
-      <c r="T45" t="inlineStr">
+      <c r="S45" t="n">
+        <v>0</v>
+      </c>
+      <c r="T45" t="inlineStr"/>
+      <c r="U45" t="inlineStr">
         <is>
           <t>1. Preparation Steps:
 2. Season the fish fillet with lemon juice, baharat, salt, and pepper.
@@ -4925,8 +5150,8 @@
 6. Cook time: 10</t>
         </is>
       </c>
-      <c r="U45" t="inlineStr"/>
-      <c r="V45" t="inlineStr">
+      <c r="V45" t="inlineStr"/>
+      <c r="W45" t="inlineStr">
         <is>
           <t>['Preparation Steps:', 'Season the fish fillet with lemon juice, baharat, salt, and pepper.', 'Preheat a grill or grill pan over medium heat; grill the fish for 4–5 minutes per side until it flakes easily.', 'In a bowl, mix basmati rice with diced tomatoes, cucumbers, and chopped parsley.', 'Serve the grilled fish over the rice mixture and garnish with extra lemon wedges.', 'Cook time: 10']</t>
         </is>
@@ -4945,15 +5170,20 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Oil Free Chicken Kabsa with Barley</t>
+          <t>Oil Free Chicken Kabsa With Barley</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
+          <t>3356</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
           <t>['1 lb chicken thighs, skin less and cut into pieces', '2 cups barley, rinsed', '4 cups low sodium chicken broth', '1 large onion, sliced', '3 garlic cloves, minced', '1 tsp ground cumin', '1 tsp ground coriander', '½ tsp ground turmeric', '½ tsp ground cinnamon', 'Salt and pepper, to taste', 'Juice of 1 lemon', 'Fresh cilantro, chopped (for garnish)']</t>
         </is>
       </c>
-      <c r="E46" t="inlineStr">
+      <c r="F46" t="inlineStr">
         <is>
           <t>1. In a large pot, combine chicken, sliced onion, garlic, chicken broth, and spices. Bring to a boil; reduce heat and simmer for 30 minutes until chicken is tender.
 2. Remove the chicken; stir in barley and cook, covered, for an additional 20 minutes until barley is tender.
@@ -4962,59 +5192,59 @@
 5. Cook time: 50</t>
         </is>
       </c>
-      <c r="F46" t="inlineStr">
+      <c r="G46" t="inlineStr">
         <is>
           <t>{"calories": 520, "protein": "36 g", "carbs": "60 g", "fiber": "7 g", "fat": "8 g"}</t>
         </is>
       </c>
-      <c r="G46" t="n">
+      <c r="H46" t="n">
         <v>4</v>
       </c>
-      <c r="H46" t="n">
+      <c r="I46" t="n">
         <v>25</v>
       </c>
-      <c r="I46" t="inlineStr">
-        <is>
-          <t>['weight-loss', 'plant-based', 'whole-foods', 'oil-free', 'lunches-and-dinners', 'soups', 'salads', 'wraps', 'sandwiches', 'rice', 'stews', 'stir-fry', 'seafood', 'ethnic', 'arabic', 'desserts']</t>
-        </is>
-      </c>
       <c r="J46" t="inlineStr">
         <is>
+          <t>['animal-protein', 'arabic', 'ethnic', 'lunches-and-dinners', 'oil-free', 'weight-loss']</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr">
+        <is>
           <t>oil_free</t>
         </is>
       </c>
-      <c r="K46" t="inlineStr">
+      <c r="L46" t="inlineStr">
         <is>
           <t>plant_based</t>
         </is>
       </c>
-      <c r="L46" t="inlineStr">
+      <c r="M46" t="inlineStr">
         <is>
           <t>Savory</t>
         </is>
       </c>
-      <c r="M46" t="inlineStr">
+      <c r="N46" t="inlineStr">
         <is>
           <t>weight_loss</t>
         </is>
       </c>
-      <c r="N46" t="b">
-        <v>0</v>
-      </c>
       <c r="O46" t="b">
         <v>0</v>
       </c>
-      <c r="P46" t="inlineStr"/>
-      <c r="Q46" t="inlineStr">
+      <c r="P46" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q46" t="inlineStr"/>
+      <c r="R46" t="inlineStr">
         <is>
           <t>hot</t>
         </is>
       </c>
-      <c r="R46" t="n">
-        <v>0</v>
-      </c>
-      <c r="S46" t="inlineStr"/>
-      <c r="T46" t="inlineStr">
+      <c r="S46" t="n">
+        <v>0</v>
+      </c>
+      <c r="T46" t="inlineStr"/>
+      <c r="U46" t="inlineStr">
         <is>
           <t>1. In a large pot, combine chicken, sliced onion, garlic, chicken broth, and spices. Bring to a boil; reduce heat and simmer for 30 minutes until chicken is tender.
 2. Remove the chicken; stir in barley and cook, covered, for an additional 20 minutes until barley is tender.
@@ -5023,8 +5253,8 @@
 5. Cook time: 50</t>
         </is>
       </c>
-      <c r="U46" t="inlineStr"/>
-      <c r="V46" t="inlineStr">
+      <c r="V46" t="inlineStr"/>
+      <c r="W46" t="inlineStr">
         <is>
           <t>['In a large pot, combine chicken, sliced onion, garlic, chicken broth, and spices. Bring to a boil; reduce heat and simmer for 30 minutes until chicken is tender.', 'Remove the chicken; stir in barley and cook, covered, for an additional 20 minutes until barley is tender.', 'Return the chicken to the pot; stir in lemon juice and adjust seasoning.', 'Garnish with fresh cilantro before serving.', 'Cook time: 50']</t>
         </is>
@@ -5043,15 +5273,20 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Oil Free Lamb Kofta with Tomato &amp; Bulgur</t>
+          <t>Oil Free Lamb Kofta With Tomato &amp; Bulgur</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
+          <t>3357</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
           <t>['1 lb lean ground lamb', '1 small onion, grated', '2 garlic cloves, minced', '1 tsp ground cumin', '1 tsp ground coriander', 'Salt and pepper, to taste', '1 cup bulgur wheat, soaked in water for 30 minutes and drained', '1 large tomato, diced', '1/4 cup chopped fresh mint', 'Juice of 1 lemon']</t>
         </is>
       </c>
-      <c r="E47" t="inlineStr">
+      <c r="F47" t="inlineStr">
         <is>
           <t>1. In a bowl, combine ground lamb, grated onion, garlic, cumin, coriander, salt, and pepper; mix thoroughly. Form into small kofta patties.
 2. Preheat a grill pan over medium-high heat and grill the kofta for 5–7 minutes until cooked through.
@@ -5060,59 +5295,59 @@
 5. Cook time: 10</t>
         </is>
       </c>
-      <c r="F47" t="inlineStr">
+      <c r="G47" t="inlineStr">
         <is>
           <t>{"calories": 520, "protein": "35 g", "carbs": "60 g", "fiber": "10 g", "fat": "10 g"}</t>
         </is>
       </c>
-      <c r="G47" t="n">
+      <c r="H47" t="n">
         <v>4</v>
       </c>
-      <c r="H47" t="n">
+      <c r="I47" t="n">
         <v>30</v>
       </c>
-      <c r="I47" t="inlineStr">
-        <is>
-          <t>['weight-loss', 'plant-based', 'whole-foods', 'oil-free', 'lunches-and-dinners', 'soups', 'salads', 'wraps', 'sandwiches', 'rice', 'stews', 'stir-fry', 'seafood', 'ethnic', 'arabic', 'desserts']</t>
-        </is>
-      </c>
       <c r="J47" t="inlineStr">
         <is>
+          <t>['animal-protein', 'arabic', 'ethnic', 'lunches-and-dinners', 'oil-free', 'weight-loss']</t>
+        </is>
+      </c>
+      <c r="K47" t="inlineStr">
+        <is>
           <t>oil_free</t>
         </is>
       </c>
-      <c r="K47" t="inlineStr">
+      <c r="L47" t="inlineStr">
         <is>
           <t>plant_based</t>
         </is>
       </c>
-      <c r="L47" t="inlineStr">
+      <c r="M47" t="inlineStr">
         <is>
           <t>Savory</t>
         </is>
       </c>
-      <c r="M47" t="inlineStr">
+      <c r="N47" t="inlineStr">
         <is>
           <t>weight_loss</t>
         </is>
       </c>
-      <c r="N47" t="b">
-        <v>0</v>
-      </c>
       <c r="O47" t="b">
         <v>0</v>
       </c>
-      <c r="P47" t="inlineStr"/>
-      <c r="Q47" t="inlineStr">
+      <c r="P47" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q47" t="inlineStr"/>
+      <c r="R47" t="inlineStr">
         <is>
           <t>hot</t>
         </is>
       </c>
-      <c r="R47" t="n">
-        <v>0</v>
-      </c>
-      <c r="S47" t="inlineStr"/>
-      <c r="T47" t="inlineStr">
+      <c r="S47" t="n">
+        <v>0</v>
+      </c>
+      <c r="T47" t="inlineStr"/>
+      <c r="U47" t="inlineStr">
         <is>
           <t>1. In a bowl, combine ground lamb, grated onion, garlic, cumin, coriander, salt, and pepper; mix thoroughly. Form into small kofta patties.
 2. Preheat a grill pan over medium-high heat and grill the kofta for 5–7 minutes until cooked through.
@@ -5121,8 +5356,8 @@
 5. Cook time: 10</t>
         </is>
       </c>
-      <c r="U47" t="inlineStr"/>
-      <c r="V47" t="inlineStr">
+      <c r="V47" t="inlineStr"/>
+      <c r="W47" t="inlineStr">
         <is>
           <t>['In a bowl, combine ground lamb, grated onion, garlic, cumin, coriander, salt, and pepper; mix thoroughly. Form into small kofta patties.', 'Preheat a grill pan over medium-high heat and grill the kofta for 5–7 minutes until cooked through.', 'In a separate bowl, mix soaked bulgur with diced tomato, chopped mint, and lemon juice.', 'Serve the grilled lamb kofta over a bed of bulgur-tomato mixture.', 'Cook time: 10']</t>
         </is>
@@ -5146,10 +5381,15 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
+          <t>3358</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
           <t>['8 oz chicken breast, cut into strips', '8 oz lean beef sirloin, thinly sliced', '8 oz lamb cubes (lean), cut into 1 inch pieces', '1 tbsp ground sumac', '1 tbsp ground cumin', 'Juice of 1 lemon', 'Salt and pepper, to taste', '1 red onion, cut into wedges', '1 cup cherry tomatoes', 'Fresh parsley, chopped (for garnish)']</t>
         </is>
       </c>
-      <c r="E48" t="inlineStr">
+      <c r="F48" t="inlineStr">
         <is>
           <t>1. In separate bowls, season each meat type with lemon juice, salt, pepper, and appropriate spices (e.g., sumac for beef, cumin for lamb, and a mild blend for chicken).
 2. Thread the meats onto skewers along with red onion wedges and cherry tomatoes.
@@ -5158,59 +5398,59 @@
 5. Cook time: 12</t>
         </is>
       </c>
-      <c r="F48" t="inlineStr">
+      <c r="G48" t="inlineStr">
         <is>
           <t>{"calories": 550, "protein": "40 g", "carbs": "55 g", "fiber": "8 g", "fat": "14 g"}</t>
         </is>
       </c>
-      <c r="G48" t="n">
+      <c r="H48" t="n">
         <v>4</v>
       </c>
-      <c r="H48" t="n">
+      <c r="I48" t="n">
         <v>25</v>
       </c>
-      <c r="I48" t="inlineStr">
-        <is>
-          <t>['weight-loss', 'plant-based', 'whole-foods', 'oil-free', 'lunches-and-dinners', 'soups', 'salads', 'wraps', 'sandwiches', 'rice', 'stews', 'stir-fry', 'seafood', 'ethnic', 'arabic', 'desserts']</t>
-        </is>
-      </c>
       <c r="J48" t="inlineStr">
         <is>
+          <t>['animal-protein', 'arabic', 'ethnic', 'lunches-and-dinners', 'oil-free', 'weight-loss']</t>
+        </is>
+      </c>
+      <c r="K48" t="inlineStr">
+        <is>
           <t>oil_free</t>
         </is>
       </c>
-      <c r="K48" t="inlineStr">
+      <c r="L48" t="inlineStr">
         <is>
           <t>plant_based</t>
         </is>
       </c>
-      <c r="L48" t="inlineStr">
+      <c r="M48" t="inlineStr">
         <is>
           <t>Savory</t>
         </is>
       </c>
-      <c r="M48" t="inlineStr">
+      <c r="N48" t="inlineStr">
         <is>
           <t>weight_loss</t>
         </is>
       </c>
-      <c r="N48" t="b">
-        <v>0</v>
-      </c>
       <c r="O48" t="b">
         <v>0</v>
       </c>
-      <c r="P48" t="inlineStr"/>
-      <c r="Q48" t="inlineStr">
+      <c r="P48" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q48" t="inlineStr"/>
+      <c r="R48" t="inlineStr">
         <is>
           <t>hot</t>
         </is>
       </c>
-      <c r="R48" t="n">
-        <v>0</v>
-      </c>
-      <c r="S48" t="inlineStr"/>
-      <c r="T48" t="inlineStr">
+      <c r="S48" t="n">
+        <v>0</v>
+      </c>
+      <c r="T48" t="inlineStr"/>
+      <c r="U48" t="inlineStr">
         <is>
           <t>1. In separate bowls, season each meat type with lemon juice, salt, pepper, and appropriate spices (e.g., sumac for beef, cumin for lamb, and a mild blend for chicken).
 2. Thread the meats onto skewers along with red onion wedges and cherry tomatoes.
@@ -5219,8 +5459,8 @@
 5. Cook time: 12</t>
         </is>
       </c>
-      <c r="U48" t="inlineStr"/>
-      <c r="V48" t="inlineStr">
+      <c r="V48" t="inlineStr"/>
+      <c r="W48" t="inlineStr">
         <is>
           <t>['In separate bowls, season each meat type with lemon juice, salt, pepper, and appropriate spices (e.g., sumac for beef, cumin for lamb, and a mild blend for chicken).', 'Thread the meats onto skewers along with red onion wedges and cherry tomatoes.', 'Preheat a grill or grill pan over medium-high heat; grill skewers for 10–12 minutes, turning to ensure even cooking.', 'Remove from grill, sprinkle with chopped parsley, and serve with lemon wedges on the side.', 'Cook time: 12']</t>
         </is>
@@ -5239,15 +5479,20 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Oil Free Arabic Spiced Eggplant with Ground Beef</t>
+          <t>Oil Free Arabic Spiced Eggplant With Ground Beef</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
+          <t>3359</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
           <t>['2 medium eggplants, cut into 1 inch cubes', '1 lb lean ground beef', '1 large tomato, diced', '1 small onion, finely chopped', '2 garlic cloves, minced', '1 tsp ground cumin', '½ tsp ground coriander', '½ tsp ground cinnamon', 'Salt and pepper, to taste', '1 cup cooked brown rice', 'Fresh cilantro, chopped (for garnish)', 'Juice of 1 lemon']</t>
         </is>
       </c>
-      <c r="E49" t="inlineStr">
+      <c r="F49" t="inlineStr">
         <is>
           <t>1. Preheat oven to 375°F (190°C).
 2. In a large bowl, toss eggplant cubes with a splash of water, salt, and pepper; spread them on a baking sheet and roast for 25 minutes until tender and lightly browned.
@@ -5257,59 +5502,59 @@
 6. Cook time: 35</t>
         </is>
       </c>
-      <c r="F49" t="inlineStr">
+      <c r="G49" t="inlineStr">
         <is>
           <t>{"calories": 540, "protein": "38 g", "carbs": "60 g", "fiber": "8 g", "fat": "10 g"}</t>
         </is>
       </c>
-      <c r="G49" t="n">
+      <c r="H49" t="n">
         <v>4</v>
       </c>
-      <c r="H49" t="n">
+      <c r="I49" t="n">
         <v>30</v>
       </c>
-      <c r="I49" t="inlineStr">
-        <is>
-          <t>['weight-loss', 'plant-based', 'whole-foods', 'oil-free', 'lunches-and-dinners', 'soups', 'salads', 'wraps', 'sandwiches', 'rice', 'stews', 'stir-fry', 'seafood', 'ethnic', 'arabic', 'desserts']</t>
-        </is>
-      </c>
       <c r="J49" t="inlineStr">
         <is>
+          <t>['animal-protein', 'arabic', 'ethnic', 'lunches-and-dinners', 'oil-free', 'weight-loss']</t>
+        </is>
+      </c>
+      <c r="K49" t="inlineStr">
+        <is>
           <t>oil_free</t>
         </is>
       </c>
-      <c r="K49" t="inlineStr">
+      <c r="L49" t="inlineStr">
         <is>
           <t>plant_based</t>
         </is>
       </c>
-      <c r="L49" t="inlineStr">
-        <is>
-          <t>Savory</t>
-        </is>
-      </c>
       <c r="M49" t="inlineStr">
         <is>
+          <t>Spicy</t>
+        </is>
+      </c>
+      <c r="N49" t="inlineStr">
+        <is>
           <t>weight_loss</t>
         </is>
       </c>
-      <c r="N49" t="b">
-        <v>0</v>
-      </c>
       <c r="O49" t="b">
         <v>0</v>
       </c>
-      <c r="P49" t="inlineStr"/>
-      <c r="Q49" t="inlineStr">
+      <c r="P49" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q49" t="inlineStr"/>
+      <c r="R49" t="inlineStr">
         <is>
           <t>hot</t>
         </is>
       </c>
-      <c r="R49" t="n">
-        <v>0</v>
-      </c>
-      <c r="S49" t="inlineStr"/>
-      <c r="T49" t="inlineStr">
+      <c r="S49" t="n">
+        <v>0</v>
+      </c>
+      <c r="T49" t="inlineStr"/>
+      <c r="U49" t="inlineStr">
         <is>
           <t>1. Preheat oven to 375°F (190°C).
 2. In a large bowl, toss eggplant cubes with a splash of water, salt, and pepper; spread them on a baking sheet and roast for 25 minutes until tender and lightly browned.
@@ -5319,8 +5564,8 @@
 6. Cook time: 35</t>
         </is>
       </c>
-      <c r="U49" t="inlineStr"/>
-      <c r="V49" t="inlineStr">
+      <c r="V49" t="inlineStr"/>
+      <c r="W49" t="inlineStr">
         <is>
           <t>['Preheat oven to 375°F (190°C).', 'In a large bowl, toss eggplant cubes with a splash of water, salt, and pepper; spread them on a baking sheet and roast for 25 minutes until tender and lightly browned.', 'In a nonstick skillet (using a splash of water), sauté onion and garlic until softened. Add ground beef, tomato, cumin, coriander, cinnamon, salt, and pepper; cook until beef is browned and well combined with vegetables.', 'Stir in the roasted eggplant and cooked brown rice; mix thoroughly.', 'Finish with a squeeze of lemon juice and garnish with fresh cilantro before serving.', 'Cook time: 35']</t>
         </is>
@@ -5339,15 +5584,20 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Oil Free Baked Kofta with Tomato- Pomegranate Glaze</t>
+          <t>Oil Free Baked Kofta With Tomato- Pomegranate Glaze</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
+          <t>3360</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
           <t>['1 lb lean ground beef or lamb', '1 small onion, grated', '2 garlic cloves, minced', '1 tsp ground cumin', '1 tsp ground coriander', '½ tsp ground allspice', 'Salt and pepper, to taste', '2 cups crushed tomatoes (no oil added)', '2 tbsp pomegranate molasses', '1 tsp dried oregano', '1/4 cup water', 'Fresh parsley, chopped (for garnish)']</t>
         </is>
       </c>
-      <c r="E50" t="inlineStr">
+      <c r="F50" t="inlineStr">
         <is>
           <t>1. In a bowl, mix the ground meat with grated onion, garlic, cumin, coriander, allspice, salt, and pepper. Form small oval patties (kofta).
 2. Arrange the kofta in a baking dish. In a separate bowl, combine crushed tomatoes, pomegranate molasses, oregano, and water; pour over the meat.
@@ -5356,59 +5606,59 @@
 5. Cook time: 30</t>
         </is>
       </c>
-      <c r="F50" t="inlineStr">
+      <c r="G50" t="inlineStr">
         <is>
           <t>{"calories": 480, "protein": "30 g", "carbs": "50 g", "fiber": "7 g", "fat": "8 g"}</t>
         </is>
       </c>
-      <c r="G50" t="n">
+      <c r="H50" t="n">
         <v>4</v>
       </c>
-      <c r="H50" t="n">
+      <c r="I50" t="n">
         <v>25</v>
       </c>
-      <c r="I50" t="inlineStr">
-        <is>
-          <t>['weight-loss', 'plant-based', 'whole-foods', 'oil-free', 'lunches-and-dinners', 'soups', 'salads', 'wraps', 'sandwiches', 'rice', 'stews', 'stir-fry', 'seafood', 'ethnic', 'arabic', 'desserts']</t>
-        </is>
-      </c>
       <c r="J50" t="inlineStr">
         <is>
+          <t>['animal-protein', 'arabic', 'ethnic', 'lunches-and-dinners', 'oil-free', 'weight-loss']</t>
+        </is>
+      </c>
+      <c r="K50" t="inlineStr">
+        <is>
           <t>oil_free</t>
         </is>
       </c>
-      <c r="K50" t="inlineStr">
+      <c r="L50" t="inlineStr">
         <is>
           <t>plant_based</t>
         </is>
       </c>
-      <c r="L50" t="inlineStr">
+      <c r="M50" t="inlineStr">
         <is>
           <t>Savory</t>
         </is>
       </c>
-      <c r="M50" t="inlineStr">
+      <c r="N50" t="inlineStr">
         <is>
           <t>weight_loss</t>
         </is>
       </c>
-      <c r="N50" t="b">
-        <v>0</v>
-      </c>
       <c r="O50" t="b">
         <v>0</v>
       </c>
-      <c r="P50" t="inlineStr"/>
-      <c r="Q50" t="inlineStr">
+      <c r="P50" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q50" t="inlineStr"/>
+      <c r="R50" t="inlineStr">
         <is>
           <t>hot</t>
         </is>
       </c>
-      <c r="R50" t="n">
-        <v>0</v>
-      </c>
-      <c r="S50" t="inlineStr"/>
-      <c r="T50" t="inlineStr">
+      <c r="S50" t="n">
+        <v>0</v>
+      </c>
+      <c r="T50" t="inlineStr"/>
+      <c r="U50" t="inlineStr">
         <is>
           <t>1. In a bowl, mix the ground meat with grated onion, garlic, cumin, coriander, allspice, salt, and pepper. Form small oval patties (kofta).
 2. Arrange the kofta in a baking dish. In a separate bowl, combine crushed tomatoes, pomegranate molasses, oregano, and water; pour over the meat.
@@ -5417,8 +5667,8 @@
 5. Cook time: 30</t>
         </is>
       </c>
-      <c r="U50" t="inlineStr"/>
-      <c r="V50" t="inlineStr">
+      <c r="V50" t="inlineStr"/>
+      <c r="W50" t="inlineStr">
         <is>
           <t>['In a bowl, mix the ground meat with grated onion, garlic, cumin, coriander, allspice, salt, and pepper. Form small oval patties (kofta).', 'Arrange the kofta in a baking dish. In a separate bowl, combine crushed tomatoes, pomegranate molasses, oregano, and water; pour over the meat.', 'Cover and bake at 375°F (190°C) for 30 minutes until the meat is cooked through and flavors meld.', 'Garnish with fresh parsley before serving.', 'Cook time: 30']</t>
         </is>
@@ -5437,15 +5687,20 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Oil Free Spiced Lamb with Freekeh Pilaf</t>
+          <t>Oil Free Spiced Lamb With Freekeh Pilaf</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
+          <t>3361</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
           <t>['1 lb lean lamb stew meat, cut into 1 inch cubes', '1 cup freekeh, rinsed', '4 cups low sodium lamb or vegetable broth', '1 large onion, chopped', '2 garlic cloves, minced', '1 tsp ground cumin', '1 tsp ground cinnamon', 'Salt and pepper, to taste', 'Fresh cilantro, chopped (for garnish)', 'Juice of 1 lemon']</t>
         </is>
       </c>
-      <c r="E51" t="inlineStr">
+      <c r="F51" t="inlineStr">
         <is>
           <t>1. In a heavy pot, combine lamb cubes, chopped onion, garlic, cumin, cinnamon, salt, and pepper. Sauté using a small amount of water until the onion softens.
 2. Add freekeh and broth; bring to a boil, then reduce heat and simmer for 1–1½ hours until lamb is tender and freekeh is cooked through.
@@ -5453,59 +5708,59 @@
 4. Cook time: 1</t>
         </is>
       </c>
-      <c r="F51" t="inlineStr">
+      <c r="G51" t="inlineStr">
         <is>
           <t>{"calories": 520, "protein": "38 g", "carbs": "60 g", "fiber": "8 g", "fat": "10 g"}</t>
         </is>
       </c>
-      <c r="G51" t="n">
+      <c r="H51" t="n">
         <v>4</v>
       </c>
-      <c r="H51" t="n">
+      <c r="I51" t="n">
         <v>25</v>
       </c>
-      <c r="I51" t="inlineStr">
-        <is>
-          <t>['weight-loss', 'plant-based', 'whole-foods', 'oil-free', 'lunches-and-dinners', 'soups', 'salads', 'wraps', 'sandwiches', 'rice', 'stews', 'stir-fry', 'seafood', 'ethnic', 'arabic', 'desserts']</t>
-        </is>
-      </c>
       <c r="J51" t="inlineStr">
         <is>
+          <t>['animal-protein', 'arabic', 'ethnic', 'lunches-and-dinners', 'oil-free', 'rice', 'weight-loss']</t>
+        </is>
+      </c>
+      <c r="K51" t="inlineStr">
+        <is>
           <t>oil_free</t>
         </is>
       </c>
-      <c r="K51" t="inlineStr">
+      <c r="L51" t="inlineStr">
         <is>
           <t>plant_based</t>
         </is>
       </c>
-      <c r="L51" t="inlineStr">
-        <is>
-          <t>Savory</t>
-        </is>
-      </c>
       <c r="M51" t="inlineStr">
         <is>
+          <t>Spicy</t>
+        </is>
+      </c>
+      <c r="N51" t="inlineStr">
+        <is>
           <t>weight_loss</t>
         </is>
       </c>
-      <c r="N51" t="b">
-        <v>0</v>
-      </c>
       <c r="O51" t="b">
         <v>0</v>
       </c>
-      <c r="P51" t="inlineStr"/>
-      <c r="Q51" t="inlineStr">
+      <c r="P51" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q51" t="inlineStr"/>
+      <c r="R51" t="inlineStr">
         <is>
           <t>hot</t>
         </is>
       </c>
-      <c r="R51" t="n">
-        <v>0</v>
-      </c>
-      <c r="S51" t="inlineStr"/>
-      <c r="T51" t="inlineStr">
+      <c r="S51" t="n">
+        <v>0</v>
+      </c>
+      <c r="T51" t="inlineStr"/>
+      <c r="U51" t="inlineStr">
         <is>
           <t>1. In a heavy pot, combine lamb cubes, chopped onion, garlic, cumin, cinnamon, salt, and pepper. Sauté using a small amount of water until the onion softens.
 2. Add freekeh and broth; bring to a boil, then reduce heat and simmer for 1–1½ hours until lamb is tender and freekeh is cooked through.
@@ -5513,8 +5768,8 @@
 4. Cook time: 1</t>
         </is>
       </c>
-      <c r="U51" t="inlineStr"/>
-      <c r="V51" t="inlineStr">
+      <c r="V51" t="inlineStr"/>
+      <c r="W51" t="inlineStr">
         <is>
           <t>['In a heavy pot, combine lamb cubes, chopped onion, garlic, cumin, cinnamon, salt, and pepper. Sauté using a small amount of water until the onion softens.', 'Add freekeh and broth; bring to a boil, then reduce heat and simmer for 1–1½ hours until lamb is tender and freekeh is cooked through.', 'Stir in lemon juice, adjust seasonings, and garnish with fresh cilantro before serving.', 'Cook time: 1']</t>
         </is>
@@ -5538,10 +5793,15 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
+          <t>3362</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
           <t>['2 cups whole wheat flour', '1 tsp active dry yeast', '¾ cup warm water', '¼ tsp salt', '½ cup chopped pitted dates', '½ cup chopped fresh parsley', '2 garlic cloves, minced', 'Juice of 1 lemon', '1 tsp ground cumin', '1 tbsp low sodium tomato paste', 'Extra flour for dusting']</t>
         </is>
       </c>
-      <c r="E52" t="inlineStr">
+      <c r="F52" t="inlineStr">
         <is>
           <t>1. In a bowl, combine flour, yeast, salt, and warm water; knead until a smooth dough forms. Cover and let rise for 1 hour.
 2. In another bowl, mix chopped dates, parsley, garlic, lemon juice, cumin, and tomato paste.
@@ -5553,59 +5813,59 @@
 8. Cook time: 25</t>
         </is>
       </c>
-      <c r="F52" t="inlineStr">
+      <c r="G52" t="inlineStr">
         <is>
           <t>{"calories": 500, "protein": "12 g", "carbs": "70 g", "fiber": "8 g", "fat": "5 g"}</t>
         </is>
       </c>
-      <c r="G52" t="n">
+      <c r="H52" t="n">
         <v>4</v>
       </c>
-      <c r="H52" t="n">
+      <c r="I52" t="n">
         <v>30</v>
       </c>
-      <c r="I52" t="inlineStr">
-        <is>
-          <t>['weight-loss', 'plant-based', 'whole-foods', 'oil-free', 'lunches-and-dinners', 'soups', 'salads', 'wraps', 'sandwiches', 'rice', 'stews', 'stir-fry', 'seafood', 'ethnic', 'arabic', 'desserts']</t>
-        </is>
-      </c>
       <c r="J52" t="inlineStr">
         <is>
+          <t>['appetizers', 'arabic', 'ethnic', 'oil-free', 'weight-loss']</t>
+        </is>
+      </c>
+      <c r="K52" t="inlineStr">
+        <is>
           <t>oil_free</t>
         </is>
       </c>
-      <c r="K52" t="inlineStr">
+      <c r="L52" t="inlineStr">
         <is>
           <t>plant_based</t>
         </is>
       </c>
-      <c r="L52" t="inlineStr">
+      <c r="M52" t="inlineStr">
         <is>
           <t>Savory</t>
         </is>
       </c>
-      <c r="M52" t="inlineStr">
+      <c r="N52" t="inlineStr">
         <is>
           <t>weight_loss</t>
         </is>
       </c>
-      <c r="N52" t="b">
-        <v>0</v>
-      </c>
       <c r="O52" t="b">
         <v>0</v>
       </c>
-      <c r="P52" t="inlineStr"/>
-      <c r="Q52" t="inlineStr">
+      <c r="P52" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q52" t="inlineStr"/>
+      <c r="R52" t="inlineStr">
         <is>
           <t>hot</t>
         </is>
       </c>
-      <c r="R52" t="n">
-        <v>0</v>
-      </c>
-      <c r="S52" t="inlineStr"/>
-      <c r="T52" t="inlineStr">
+      <c r="S52" t="n">
+        <v>0</v>
+      </c>
+      <c r="T52" t="inlineStr"/>
+      <c r="U52" t="inlineStr">
         <is>
           <t>1. In a bowl, combine flour, yeast, salt, and warm water; knead until a smooth dough forms. Cover and let rise for 1 hour.
 2. In another bowl, mix chopped dates, parsley, garlic, lemon juice, cumin, and tomato paste.
@@ -5617,8 +5877,8 @@
 8. Cook time: 25</t>
         </is>
       </c>
-      <c r="U52" t="inlineStr"/>
-      <c r="V52" t="inlineStr">
+      <c r="V52" t="inlineStr"/>
+      <c r="W52" t="inlineStr">
         <is>
           <t>['In a bowl, combine flour, yeast, salt, and warm water; knead until a smooth dough forms. Cover and let rise for 1 hour.', 'In another bowl, mix chopped dates, parsley, garlic, lemon juice, cumin, and tomato paste.', 'Preheat the oven to 400°F (200°C). Divide dough into 4 equal portions; roll each portion into a thin circle on a floured surface.', 'Spread the herb-date mixture evenly over each circle.', 'Roll up the dough tightly (like a log), then coil it into a spiral on a baking sheet lined with parchment. Gently flatten into a round.', 'Bake for 20–25 minutes until golden and cooked through.', 'Slice and serve warm.', 'Cook time: 25']</t>
         </is>
@@ -5637,15 +5897,20 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Oil Free Eggplant &amp; Tomato Casserole with Bulgur</t>
+          <t>Oil Free Eggplant &amp; Tomato Casserole With Bulgur</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
+          <t>3363</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
           <t>['2 medium eggplants, sliced into ½ inch rounds', '2 large tomatoes, sliced', '1 cup cooked bulgur wheat', '1 small onion, thinly sliced', '2 garlic cloves, minced', '1 tsp dried oregano', 'Salt and pepper, to taste', '1 cup low sodium vegetable broth', 'Fresh basil, chopped (for garnish)']</t>
         </is>
       </c>
-      <c r="E53" t="inlineStr">
+      <c r="F53" t="inlineStr">
         <is>
           <t>1. Preheat oven to 375°F (190°C).
 2. Arrange eggplant and tomato slices alternately in a baking dish.
@@ -5656,59 +5921,59 @@
 7. Cook time: 35</t>
         </is>
       </c>
-      <c r="F53" t="inlineStr">
+      <c r="G53" t="inlineStr">
         <is>
           <t>{"calories": 480, "protein": "12 g", "carbs": "65 g", "fiber": "9 g", "fat": "3 g"}</t>
         </is>
       </c>
-      <c r="G53" t="n">
+      <c r="H53" t="n">
         <v>4</v>
       </c>
-      <c r="H53" t="n">
+      <c r="I53" t="n">
         <v>25</v>
       </c>
-      <c r="I53" t="inlineStr">
-        <is>
-          <t>['weight-loss', 'plant-based', 'whole-foods', 'oil-free', 'lunches-and-dinners', 'soups', 'salads', 'wraps', 'sandwiches', 'rice', 'stews', 'stir-fry', 'seafood', 'ethnic', 'arabic', 'desserts']</t>
-        </is>
-      </c>
       <c r="J53" t="inlineStr">
         <is>
+          <t>['arabic', 'ethnic', 'lunches-and-dinners', 'oil-free', 'vegetarian', 'weight-loss']</t>
+        </is>
+      </c>
+      <c r="K53" t="inlineStr">
+        <is>
           <t>oil_free</t>
         </is>
       </c>
-      <c r="K53" t="inlineStr">
-        <is>
-          <t>plant_based</t>
-        </is>
-      </c>
       <c r="L53" t="inlineStr">
         <is>
+          <t>Vegetarian</t>
+        </is>
+      </c>
+      <c r="M53" t="inlineStr">
+        <is>
           <t>Savory</t>
         </is>
       </c>
-      <c r="M53" t="inlineStr">
+      <c r="N53" t="inlineStr">
         <is>
           <t>weight_loss</t>
         </is>
       </c>
-      <c r="N53" t="b">
-        <v>0</v>
-      </c>
       <c r="O53" t="b">
         <v>0</v>
       </c>
-      <c r="P53" t="inlineStr"/>
-      <c r="Q53" t="inlineStr">
+      <c r="P53" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q53" t="inlineStr"/>
+      <c r="R53" t="inlineStr">
         <is>
           <t>hot</t>
         </is>
       </c>
-      <c r="R53" t="n">
-        <v>0</v>
-      </c>
-      <c r="S53" t="inlineStr"/>
-      <c r="T53" t="inlineStr">
+      <c r="S53" t="n">
+        <v>0</v>
+      </c>
+      <c r="T53" t="inlineStr"/>
+      <c r="U53" t="inlineStr">
         <is>
           <t>1. Preheat oven to 375°F (190°C).
 2. Arrange eggplant and tomato slices alternately in a baking dish.
@@ -5719,8 +5984,8 @@
 7. Cook time: 35</t>
         </is>
       </c>
-      <c r="U53" t="inlineStr"/>
-      <c r="V53" t="inlineStr">
+      <c r="V53" t="inlineStr"/>
+      <c r="W53" t="inlineStr">
         <is>
           <t>['Preheat oven to 375°F (190°C).', 'Arrange eggplant and tomato slices alternately in a baking dish.', 'In a skillet, sauté onion and garlic (using a splash of water) until soft; stir in cooked bulgur and oregano, then season with salt and pepper.', 'Spoon the bulgur mixture evenly over the layered vegetables.', 'Pour vegetable broth over the casserole, cover with foil, and bake for 35 minutes until the vegetables are tender.', 'Garnish with fresh basil before serving.', 'Cook time: 35']</t>
         </is>
@@ -5739,15 +6004,20 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Oil Free Grilled Chicken Kebabs with Couscous</t>
+          <t>Oil Free Grilled Chicken Kebabs With Couscous</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
+          <t>3364</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
           <t>['1 lb boneless, skin less chicken breast, cut into 1 inch cubes', '1 tsp ground sumac', '1 tsp ground cumin', 'Juice of 1 lemon', 'Salt and pepper, to taste', '10 wooden skewers (soaked in water for 30 minutes)', '2 cups cooked couscous', '1/4 cup chopped fresh mint', '1/4 cup chopped fresh parsley']</t>
         </is>
       </c>
-      <c r="E54" t="inlineStr">
+      <c r="F54" t="inlineStr">
         <is>
           <t>1. In a bowl, marinate chicken cubes with lemon juice, sumac, cumin, salt, and pepper for 20 minutes.
 2. Thread the chicken onto skewers. Preheat a grill or grill pan over medium-high heat; grill the kebabs for 8–10 minutes until chicken is cooked through.
@@ -5756,59 +6026,59 @@
 5. Cook time: 20</t>
         </is>
       </c>
-      <c r="F54" t="inlineStr">
+      <c r="G54" t="inlineStr">
         <is>
           <t>{"calories": 480, "protein": "38 g", "carbs": "55 g", "fiber": "7 g", "fat": "8 g"}</t>
         </is>
       </c>
-      <c r="G54" t="n">
+      <c r="H54" t="n">
         <v>4</v>
       </c>
-      <c r="H54" t="n">
+      <c r="I54" t="n">
         <v>20</v>
       </c>
-      <c r="I54" t="inlineStr">
-        <is>
-          <t>['weight-loss', 'plant-based', 'whole-foods', 'oil-free', 'lunches-and-dinners', 'soups', 'salads', 'wraps', 'sandwiches', 'rice', 'stews', 'stir-fry', 'seafood', 'ethnic', 'arabic', 'desserts']</t>
-        </is>
-      </c>
       <c r="J54" t="inlineStr">
         <is>
+          <t>['animal-protein', 'arabic', 'ethnic', 'lunches-and-dinners', 'oil-free', 'weight-loss']</t>
+        </is>
+      </c>
+      <c r="K54" t="inlineStr">
+        <is>
           <t>oil_free</t>
         </is>
       </c>
-      <c r="K54" t="inlineStr">
+      <c r="L54" t="inlineStr">
         <is>
           <t>plant_based</t>
         </is>
       </c>
-      <c r="L54" t="inlineStr">
+      <c r="M54" t="inlineStr">
         <is>
           <t>Savory</t>
         </is>
       </c>
-      <c r="M54" t="inlineStr">
+      <c r="N54" t="inlineStr">
         <is>
           <t>weight_loss</t>
         </is>
       </c>
-      <c r="N54" t="b">
-        <v>0</v>
-      </c>
       <c r="O54" t="b">
         <v>0</v>
       </c>
-      <c r="P54" t="inlineStr"/>
-      <c r="Q54" t="inlineStr">
+      <c r="P54" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q54" t="inlineStr"/>
+      <c r="R54" t="inlineStr">
         <is>
           <t>hot</t>
         </is>
       </c>
-      <c r="R54" t="n">
-        <v>0</v>
-      </c>
-      <c r="S54" t="inlineStr"/>
-      <c r="T54" t="inlineStr">
+      <c r="S54" t="n">
+        <v>0</v>
+      </c>
+      <c r="T54" t="inlineStr"/>
+      <c r="U54" t="inlineStr">
         <is>
           <t>1. In a bowl, marinate chicken cubes with lemon juice, sumac, cumin, salt, and pepper for 20 minutes.
 2. Thread the chicken onto skewers. Preheat a grill or grill pan over medium-high heat; grill the kebabs for 8–10 minutes until chicken is cooked through.
@@ -5817,8 +6087,8 @@
 5. Cook time: 20</t>
         </is>
       </c>
-      <c r="U54" t="inlineStr"/>
-      <c r="V54" t="inlineStr">
+      <c r="V54" t="inlineStr"/>
+      <c r="W54" t="inlineStr">
         <is>
           <t>['In a bowl, marinate chicken cubes with lemon juice, sumac, cumin, salt, and pepper for 20 minutes.', 'Thread the chicken onto skewers. Preheat a grill or grill pan over medium-high heat; grill the kebabs for 8–10 minutes until chicken is cooked through.', 'Toss cooked couscous with chopped mint and parsley.', 'Serve the grilled chicken kebabs over a bed of herbed couscous.', 'Cook time: 20']</t>
         </is>
@@ -5842,10 +6112,15 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
+          <t>3365</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
           <t>['1 lb lean lamb stew meat, cut into 1 inch cubes', '2 cups basmati rice, rinsed', '4 cups low sodium lamb or vegetable broth', '1 large onion, chopped', '2 garlic cloves, minced', '1 tsp ground cinnamon', '1 tsp ground cumin', '1/2 tsp ground coriander', 'Salt and pepper, to taste', '½ cup raisins', 'Fresh cilantro, chopped (for garnish)']</t>
         </is>
       </c>
-      <c r="E55" t="inlineStr">
+      <c r="F55" t="inlineStr">
         <is>
           <t>1. In a heavy pot, sauté lamb, onion, and garlic (using a splash of water) until the onion softens.
 2. Add basmati rice, cinnamon, cumin, coriander, salt, and pepper; stir well.
@@ -5854,59 +6129,59 @@
 5. Cook time: 30</t>
         </is>
       </c>
-      <c r="F55" t="inlineStr">
+      <c r="G55" t="inlineStr">
         <is>
           <t>{"calories": 540, "protein": "38 g", "carbs": "60 g", "fiber": "8 g", "fat": "10 g"}</t>
         </is>
       </c>
-      <c r="G55" t="n">
+      <c r="H55" t="n">
         <v>4</v>
       </c>
-      <c r="H55" t="n">
+      <c r="I55" t="n">
         <v>25</v>
       </c>
-      <c r="I55" t="inlineStr">
-        <is>
-          <t>['weight-loss', 'plant-based', 'whole-foods', 'oil-free', 'lunches-and-dinners', 'soups', 'salads', 'wraps', 'sandwiches', 'rice', 'stews', 'stir-fry', 'seafood', 'ethnic', 'arabic', 'desserts']</t>
-        </is>
-      </c>
       <c r="J55" t="inlineStr">
         <is>
+          <t>['animal-protein', 'arabic', 'ethnic', 'lunches-and-dinners', 'oil-free', 'rice', 'weight-loss']</t>
+        </is>
+      </c>
+      <c r="K55" t="inlineStr">
+        <is>
           <t>oil_free</t>
         </is>
       </c>
-      <c r="K55" t="inlineStr">
+      <c r="L55" t="inlineStr">
         <is>
           <t>plant_based</t>
         </is>
       </c>
-      <c r="L55" t="inlineStr">
+      <c r="M55" t="inlineStr">
         <is>
           <t>Savory</t>
         </is>
       </c>
-      <c r="M55" t="inlineStr">
+      <c r="N55" t="inlineStr">
         <is>
           <t>weight_loss</t>
         </is>
       </c>
-      <c r="N55" t="b">
-        <v>0</v>
-      </c>
       <c r="O55" t="b">
         <v>0</v>
       </c>
-      <c r="P55" t="inlineStr"/>
-      <c r="Q55" t="inlineStr">
+      <c r="P55" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q55" t="inlineStr"/>
+      <c r="R55" t="inlineStr">
         <is>
           <t>hot</t>
         </is>
       </c>
-      <c r="R55" t="n">
-        <v>0</v>
-      </c>
-      <c r="S55" t="inlineStr"/>
-      <c r="T55" t="inlineStr">
+      <c r="S55" t="n">
+        <v>0</v>
+      </c>
+      <c r="T55" t="inlineStr"/>
+      <c r="U55" t="inlineStr">
         <is>
           <t>1. In a heavy pot, sauté lamb, onion, and garlic (using a splash of water) until the onion softens.
 2. Add basmati rice, cinnamon, cumin, coriander, salt, and pepper; stir well.
@@ -5915,8 +6190,8 @@
 5. Cook time: 30</t>
         </is>
       </c>
-      <c r="U55" t="inlineStr"/>
-      <c r="V55" t="inlineStr">
+      <c r="V55" t="inlineStr"/>
+      <c r="W55" t="inlineStr">
         <is>
           <t>['In a heavy pot, sauté lamb, onion, and garlic (using a splash of water) until the onion softens.', 'Add basmati rice, cinnamon, cumin, coriander, salt, and pepper; stir well.', 'Pour in the broth and add raisins; bring to a boil, then reduce heat, cover, and simmer for 25–30 minutes until the rice is tender and the lamb is cooked.', 'Garnish with chopped cilantro before serving.', 'Cook time: 30']</t>
         </is>
@@ -5935,15 +6210,20 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Oil Free Baked Falafel with Whole Wheat Pita</t>
+          <t>Oil Free Baked Falafel With Whole Wheat Pita</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
+          <t>3366</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
           <t>['1 can (15 oz) chickpeas, drained and rinsed', '1 small onion, roughly chopped', '3 garlic cloves', '1/4 cup fresh parsley', '1/4 cup fresh cilantro', '2 tsp ground cumin', '1 tsp ground coriander', '1/2 tsp baking soda', 'Salt and pepper, to taste', '2 tbsp lemon juice', '2–3 tbsp water (as needed)', '4 whole wheat pita breads', 'Sliced cucumbers and tomatoes, for serving', 'Fat free tahini sauce (optional)']</t>
         </is>
       </c>
-      <c r="E56" t="inlineStr">
+      <c r="F56" t="inlineStr">
         <is>
           <t>1. In a food processor, combine chickpeas, onion, garlic, parsley, cilantro, cumin, coriander, baking soda, lemon juice, salt, and pepper. Process until the mixture is coarse but well blended; add water as needed.
 2. Form the mixture into small patties.
@@ -5952,59 +6232,59 @@
 5. Cook time: 25</t>
         </is>
       </c>
-      <c r="F56" t="inlineStr">
+      <c r="G56" t="inlineStr">
         <is>
           <t>{"calories": 420, "protein": "16 g", "carbs": "60 g", "fiber": "12 g", "fat": "10 g"}</t>
         </is>
       </c>
-      <c r="G56" t="n">
+      <c r="H56" t="n">
         <v>4</v>
       </c>
-      <c r="H56" t="n">
+      <c r="I56" t="n">
         <v>20</v>
       </c>
-      <c r="I56" t="inlineStr">
-        <is>
-          <t>['weight-loss', 'plant-based', 'whole-foods', 'oil-free', 'lunches-and-dinners', 'soups', 'salads', 'wraps', 'sandwiches', 'rice', 'stews', 'stir-fry', 'seafood', 'ethnic', 'arabic', 'desserts']</t>
-        </is>
-      </c>
       <c r="J56" t="inlineStr">
         <is>
+          <t>['arabic', 'ethnic', 'lunches-and-dinners', 'oil-free', 'vegetarian', 'weight-loss']</t>
+        </is>
+      </c>
+      <c r="K56" t="inlineStr">
+        <is>
           <t>oil_free</t>
         </is>
       </c>
-      <c r="K56" t="inlineStr">
-        <is>
-          <t>plant_based</t>
-        </is>
-      </c>
       <c r="L56" t="inlineStr">
         <is>
+          <t>Vegetarian</t>
+        </is>
+      </c>
+      <c r="M56" t="inlineStr">
+        <is>
           <t>Savory</t>
         </is>
       </c>
-      <c r="M56" t="inlineStr">
+      <c r="N56" t="inlineStr">
         <is>
           <t>weight_loss</t>
         </is>
       </c>
-      <c r="N56" t="b">
-        <v>0</v>
-      </c>
       <c r="O56" t="b">
         <v>0</v>
       </c>
-      <c r="P56" t="inlineStr"/>
-      <c r="Q56" t="inlineStr">
+      <c r="P56" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q56" t="inlineStr"/>
+      <c r="R56" t="inlineStr">
         <is>
           <t>hot</t>
         </is>
       </c>
-      <c r="R56" t="n">
-        <v>0</v>
-      </c>
-      <c r="S56" t="inlineStr"/>
-      <c r="T56" t="inlineStr">
+      <c r="S56" t="n">
+        <v>0</v>
+      </c>
+      <c r="T56" t="inlineStr"/>
+      <c r="U56" t="inlineStr">
         <is>
           <t>1. In a food processor, combine chickpeas, onion, garlic, parsley, cilantro, cumin, coriander, baking soda, lemon juice, salt, and pepper. Process until the mixture is coarse but well blended; add water as needed.
 2. Form the mixture into small patties.
@@ -6013,8 +6293,8 @@
 5. Cook time: 25</t>
         </is>
       </c>
-      <c r="U56" t="inlineStr"/>
-      <c r="V56" t="inlineStr">
+      <c r="V56" t="inlineStr"/>
+      <c r="W56" t="inlineStr">
         <is>
           <t>['In a food processor, combine chickpeas, onion, garlic, parsley, cilantro, cumin, coriander, baking soda, lemon juice, salt, and pepper. Process until the mixture is coarse but well blended; add water as needed.', 'Form the mixture into small patties.', 'Arrange patties on a parchment lined baking sheet and bake in a preheated 400°F (200°C) oven for 20–25 minutes until golden and firm.', 'Serve falafel patties inside whole wheat pita with sliced cucumbers, tomatoes, and a drizzle of fat free tahini sauce if desired.', 'Cook time: 25']</t>
         </is>
@@ -6038,10 +6318,15 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
+          <t>3367</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
           <t>['1 cup semolina', '½ cup whole wheat flour', '1 tsp baking powder', '¼ tsp salt', '1 cup unsweetened applesauce', '⅓ cup honey or maple syrup', '1 tsp ground cinnamon', '½ cup chopped dates', '½ cup chopped walnuts (optional)', '1 tsp vanilla extract']</t>
         </is>
       </c>
-      <c r="E57" t="inlineStr">
+      <c r="F57" t="inlineStr">
         <is>
           <t>1. Preheat oven to 350°F (175°C). Grease a loaf pan lightly using water or a nonstick spray.
 2. In a bowl, whisk together semolina, whole wheat flour, baking powder, salt, and cinnamon.
@@ -6054,59 +6339,59 @@
 9. Cook time: 50</t>
         </is>
       </c>
-      <c r="F57" t="inlineStr">
+      <c r="G57" t="inlineStr">
         <is>
           <t>{"calories": 180, "protein": "5 g", "carbs": "32 g", "fiber": "4 g", "fat": "3 g"}</t>
         </is>
       </c>
-      <c r="G57" t="n">
+      <c r="H57" t="n">
         <v>10</v>
       </c>
-      <c r="H57" t="n">
+      <c r="I57" t="n">
         <v>20</v>
       </c>
-      <c r="I57" t="inlineStr">
-        <is>
-          <t>['weight-loss', 'plant-based', 'whole-foods', 'oil-free', 'lunches-and-dinners', 'soups', 'salads', 'wraps', 'sandwiches', 'rice', 'stews', 'stir-fry', 'seafood', 'ethnic', 'arabic', 'desserts']</t>
-        </is>
-      </c>
       <c r="J57" t="inlineStr">
         <is>
+          <t>['arabic', 'desserts', 'ethnic', 'oil-free', 'weight-loss']</t>
+        </is>
+      </c>
+      <c r="K57" t="inlineStr">
+        <is>
           <t>oil_free</t>
         </is>
       </c>
-      <c r="K57" t="inlineStr">
+      <c r="L57" t="inlineStr">
         <is>
           <t>plant_based</t>
         </is>
       </c>
-      <c r="L57" t="inlineStr">
+      <c r="M57" t="inlineStr">
         <is>
           <t>Savory</t>
         </is>
       </c>
-      <c r="M57" t="inlineStr">
+      <c r="N57" t="inlineStr">
         <is>
           <t>weight_loss</t>
         </is>
       </c>
-      <c r="N57" t="b">
-        <v>0</v>
-      </c>
       <c r="O57" t="b">
         <v>0</v>
       </c>
-      <c r="P57" t="inlineStr"/>
-      <c r="Q57" t="inlineStr">
+      <c r="P57" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q57" t="inlineStr"/>
+      <c r="R57" t="inlineStr">
         <is>
           <t>hot</t>
         </is>
       </c>
-      <c r="R57" t="n">
-        <v>0</v>
-      </c>
-      <c r="S57" t="inlineStr"/>
-      <c r="T57" t="inlineStr">
+      <c r="S57" t="n">
+        <v>0</v>
+      </c>
+      <c r="T57" t="inlineStr"/>
+      <c r="U57" t="inlineStr">
         <is>
           <t>1. Preheat oven to 350°F (175°C). Grease a loaf pan lightly using water or a nonstick spray.
 2. In a bowl, whisk together semolina, whole wheat flour, baking powder, salt, and cinnamon.
@@ -6119,8 +6404,8 @@
 9. Cook time: 50</t>
         </is>
       </c>
-      <c r="U57" t="inlineStr"/>
-      <c r="V57" t="inlineStr">
+      <c r="V57" t="inlineStr"/>
+      <c r="W57" t="inlineStr">
         <is>
           <t>['Preheat oven to 350°F (175°C). Grease a loaf pan lightly using water or a nonstick spray.', 'In a bowl, whisk together semolina, whole wheat flour, baking powder, salt, and cinnamon.', 'In another bowl, mix unsweetened applesauce, honey (or maple syrup), and vanilla extract until smooth.', 'Combine the wet and dry ingredients; fold in chopped dates and walnuts if using.', 'Pour the batter into the prepared loaf pan and smooth the top.', 'Bake for 45–50 minutes until a toothpick inserted in the center comes out clean.', 'Let cool in the pan for 10 minutes before transferring to a wire rack.', 'Slice and serve.', 'Cook time: 50']</t>
         </is>
@@ -6144,10 +6429,15 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
+          <t>3368</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
           <t>['2 cups whole wheat flour', '1 tsp active dry yeast', '½ tsp salt', '1 tsp honey (optional, for activation)', '1 cup warm water (approximately, adjust as needed)']</t>
         </is>
       </c>
-      <c r="E58" t="inlineStr">
+      <c r="F58" t="inlineStr">
         <is>
           <t>1. In a small bowl, dissolve the yeast (and honey, if using) in about ¼ cup of warm water; let it sit for 5–10 minutes until frothy.
 2. In a large bowl, combine the flour and salt. Gradually add the yeast mixture along with the remaining warm water, mixing until a soft, sticky dough forms.
@@ -6160,59 +6450,59 @@
 9. Cook time: 19</t>
         </is>
       </c>
-      <c r="F58" t="inlineStr">
+      <c r="G58" t="inlineStr">
         <is>
           <t>{"calories": 130, "protein": "5 g", "carbs": "25 g", "fiber": "3 g", "fat": "1 g"}</t>
         </is>
       </c>
-      <c r="G58" t="n">
+      <c r="H58" t="n">
         <v>8</v>
       </c>
-      <c r="H58" t="n">
+      <c r="I58" t="n">
         <v>15</v>
       </c>
-      <c r="I58" t="inlineStr">
-        <is>
-          <t>['weight-loss', 'plant-based', 'whole-foods', 'oil-free', 'lunches-and-dinners', 'soups', 'salads', 'wraps', 'sandwiches', 'rice', 'stews', 'stir-fry', 'seafood', 'ethnic', 'arabic', 'desserts']</t>
-        </is>
-      </c>
       <c r="J58" t="inlineStr">
         <is>
+          <t>['appetizers', 'arabic', 'ethnic', 'oil-free', 'vegetarian', 'weight-loss']</t>
+        </is>
+      </c>
+      <c r="K58" t="inlineStr">
+        <is>
           <t>oil_free</t>
         </is>
       </c>
-      <c r="K58" t="inlineStr">
-        <is>
-          <t>plant_based</t>
-        </is>
-      </c>
       <c r="L58" t="inlineStr">
         <is>
+          <t>Vegetarian</t>
+        </is>
+      </c>
+      <c r="M58" t="inlineStr">
+        <is>
           <t>Savory</t>
         </is>
       </c>
-      <c r="M58" t="inlineStr">
+      <c r="N58" t="inlineStr">
         <is>
           <t>weight_loss</t>
         </is>
       </c>
-      <c r="N58" t="b">
-        <v>0</v>
-      </c>
       <c r="O58" t="b">
         <v>0</v>
       </c>
-      <c r="P58" t="inlineStr"/>
-      <c r="Q58" t="inlineStr">
+      <c r="P58" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q58" t="inlineStr"/>
+      <c r="R58" t="inlineStr">
         <is>
           <t>hot</t>
         </is>
       </c>
-      <c r="R58" t="n">
-        <v>0</v>
-      </c>
-      <c r="S58" t="inlineStr"/>
-      <c r="T58" t="inlineStr">
+      <c r="S58" t="n">
+        <v>0</v>
+      </c>
+      <c r="T58" t="inlineStr"/>
+      <c r="U58" t="inlineStr">
         <is>
           <t>1. In a small bowl, dissolve the yeast (and honey, if using) in about ¼ cup of warm water; let it sit for 5–10 minutes until frothy.
 2. In a large bowl, combine the flour and salt. Gradually add the yeast mixture along with the remaining warm water, mixing until a soft, sticky dough forms.
@@ -6225,8 +6515,8 @@
 9. Cook time: 19</t>
         </is>
       </c>
-      <c r="U58" t="inlineStr"/>
-      <c r="V58" t="inlineStr">
+      <c r="V58" t="inlineStr"/>
+      <c r="W58" t="inlineStr">
         <is>
           <t>['In a small bowl, dissolve the yeast (and honey, if using) in about ¼ cup of warm water; let it sit for 5–10 minutes until frothy.', 'In a large bowl, combine the flour and salt. Gradually add the yeast mixture along with the remaining warm water, mixing until a soft, sticky dough forms.', 'Turn the dough onto a lightly floured surface and knead for 5–7 minutes until smooth and elastic.', 'Place the dough in a lightly covered bowl and let it rise in a warm place for about 1 hour, or until doubled in size.', 'Punch down the dough, divide it into 8 equal portions, and shape each into a smooth ball.', 'Roll each ball into a thin circle (about ¼ inch thick). Preheat an oven with a baking stone to 475°F (245°C) or heat a heavy skillet over high heat.', 'Bake each pita (or cook on the skillet) for 2–3 minutes until the dough puffs up and lightly browns in spots.', 'Remove and cover with a clean cloth to keep soft. Serve warm.', 'Cook time: 19']</t>
         </is>
@@ -6250,10 +6540,15 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
+          <t>3369</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
           <t>['For the Dough:', '2 cups whole wheat flour', '1 tsp active dry yeast', '½ tsp salt', '¾ cup warm water', 'For the Filling:', '2 cups fresh spinach, chopped', '1 small onion, finely chopped', '½ cup diced tomato', '½ tsp sumac', 'Salt and pepper, to taste', 'Juice of 1 lemon']</t>
         </is>
       </c>
-      <c r="E59" t="inlineStr">
+      <c r="F59" t="inlineStr">
         <is>
           <t>1. Combine flour, yeast, salt, and warm water in a bowl; knead until smooth. Cover and let rise for 1 hour.
 2. In a separate bowl, mix spinach, onion, tomato, sumac, salt, pepper, and lemon juice until well combined.
@@ -6265,59 +6560,59 @@
 8. Cook time: 20</t>
         </is>
       </c>
-      <c r="F59" t="inlineStr">
+      <c r="G59" t="inlineStr">
         <is>
           <t>{"calories": 220, "protein": "8 g", "carbs": "40 g", "fiber": "6 g", "fat": "3 g"}</t>
         </is>
       </c>
-      <c r="G59" t="n">
+      <c r="H59" t="n">
         <v>4</v>
       </c>
-      <c r="H59" t="n">
+      <c r="I59" t="n">
         <v>25</v>
       </c>
-      <c r="I59" t="inlineStr">
-        <is>
-          <t>['weight-loss', 'plant-based', 'whole-foods', 'oil-free', 'lunches-and-dinners', 'soups', 'salads', 'wraps', 'sandwiches', 'rice', 'stews', 'stir-fry', 'seafood', 'ethnic', 'arabic', 'desserts']</t>
-        </is>
-      </c>
       <c r="J59" t="inlineStr">
         <is>
+          <t>['appetizers', 'arabic', 'ethnic', 'oil-free', 'vegetarian', 'weight-loss']</t>
+        </is>
+      </c>
+      <c r="K59" t="inlineStr">
+        <is>
           <t>oil_free</t>
         </is>
       </c>
-      <c r="K59" t="inlineStr">
-        <is>
-          <t>plant_based</t>
-        </is>
-      </c>
       <c r="L59" t="inlineStr">
         <is>
+          <t>Vegetarian</t>
+        </is>
+      </c>
+      <c r="M59" t="inlineStr">
+        <is>
           <t>Savory</t>
         </is>
       </c>
-      <c r="M59" t="inlineStr">
+      <c r="N59" t="inlineStr">
         <is>
           <t>weight_loss</t>
         </is>
       </c>
-      <c r="N59" t="b">
-        <v>0</v>
-      </c>
       <c r="O59" t="b">
         <v>0</v>
       </c>
-      <c r="P59" t="inlineStr"/>
-      <c r="Q59" t="inlineStr">
+      <c r="P59" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q59" t="inlineStr"/>
+      <c r="R59" t="inlineStr">
         <is>
           <t>hot</t>
         </is>
       </c>
-      <c r="R59" t="n">
-        <v>0</v>
-      </c>
-      <c r="S59" t="inlineStr"/>
-      <c r="T59" t="inlineStr">
+      <c r="S59" t="n">
+        <v>0</v>
+      </c>
+      <c r="T59" t="inlineStr"/>
+      <c r="U59" t="inlineStr">
         <is>
           <t>1. Combine flour, yeast, salt, and warm water in a bowl; knead until smooth. Cover and let rise for 1 hour.
 2. In a separate bowl, mix spinach, onion, tomato, sumac, salt, pepper, and lemon juice until well combined.
@@ -6329,8 +6624,8 @@
 8. Cook time: 20</t>
         </is>
       </c>
-      <c r="U59" t="inlineStr"/>
-      <c r="V59" t="inlineStr">
+      <c r="V59" t="inlineStr"/>
+      <c r="W59" t="inlineStr">
         <is>
           <t>['Combine flour, yeast, salt, and warm water in a bowl; knead until smooth. Cover and let rise for 1 hour.', 'In a separate bowl, mix spinach, onion, tomato, sumac, salt, pepper, and lemon juice until well combined.', 'Divide the dough into small balls, roll each into a thin circle, and place 1–2 tablespoons of filling in the center.', 'Fold the edges over the filling to form a triangle or envelope shape, pressing to seal.', 'Preheat the oven to 375°F (190°C) and place fatayer on a parchment lined baking sheet.', 'Bake for 20 minutes until the dough is cooked and slightly golden.', 'Serve warm.', 'Cook time: 20']</t>
         </is>
@@ -6354,10 +6649,15 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
+          <t>3370</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
           <t>['2 cups whole wheat flour', '½ cup fine semolina', '1 tsp active dry yeast', '½ tsp salt', '1 cup warm water']</t>
         </is>
       </c>
-      <c r="E60" t="inlineStr">
+      <c r="F60" t="inlineStr">
         <is>
           <t>1. In a bowl, combine whole wheat flour, semolina, yeast, salt, and warm water; mix until a soft dough forms.
 2. Knead on a lightly floured surface for 5–7 minutes until smooth; cover and let rise for 1 hour.
@@ -6368,59 +6668,59 @@
 7. Cook time: 10</t>
         </is>
       </c>
-      <c r="F60" t="inlineStr">
+      <c r="G60" t="inlineStr">
         <is>
           <t>{"calories": 120, "protein": "5 g", "carbs": "24 g", "fiber": "3 g", "fat": "1 g"}</t>
         </is>
       </c>
-      <c r="G60" t="n">
+      <c r="H60" t="n">
         <v>8</v>
       </c>
-      <c r="H60" t="n">
+      <c r="I60" t="n">
         <v>15</v>
       </c>
-      <c r="I60" t="inlineStr">
-        <is>
-          <t>['weight-loss', 'plant-based', 'whole-foods', 'oil-free', 'lunches-and-dinners', 'soups', 'salads', 'wraps', 'sandwiches', 'rice', 'stews', 'stir-fry', 'seafood', 'ethnic', 'arabic', 'desserts']</t>
-        </is>
-      </c>
       <c r="J60" t="inlineStr">
         <is>
+          <t>['appetizers', 'arabic', 'ethnic', 'oil-free', 'vegetarian', 'weight-loss']</t>
+        </is>
+      </c>
+      <c r="K60" t="inlineStr">
+        <is>
           <t>oil_free</t>
         </is>
       </c>
-      <c r="K60" t="inlineStr">
-        <is>
-          <t>plant_based</t>
-        </is>
-      </c>
       <c r="L60" t="inlineStr">
         <is>
+          <t>Vegetarian</t>
+        </is>
+      </c>
+      <c r="M60" t="inlineStr">
+        <is>
           <t>Savory</t>
         </is>
       </c>
-      <c r="M60" t="inlineStr">
+      <c r="N60" t="inlineStr">
         <is>
           <t>weight_loss</t>
         </is>
       </c>
-      <c r="N60" t="b">
-        <v>0</v>
-      </c>
       <c r="O60" t="b">
         <v>0</v>
       </c>
-      <c r="P60" t="inlineStr"/>
-      <c r="Q60" t="inlineStr">
+      <c r="P60" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q60" t="inlineStr"/>
+      <c r="R60" t="inlineStr">
         <is>
           <t>hot</t>
         </is>
       </c>
-      <c r="R60" t="n">
-        <v>0</v>
-      </c>
-      <c r="S60" t="inlineStr"/>
-      <c r="T60" t="inlineStr">
+      <c r="S60" t="n">
+        <v>0</v>
+      </c>
+      <c r="T60" t="inlineStr"/>
+      <c r="U60" t="inlineStr">
         <is>
           <t>1. In a bowl, combine whole wheat flour, semolina, yeast, salt, and warm water; mix until a soft dough forms.
 2. Knead on a lightly floured surface for 5–7 minutes until smooth; cover and let rise for 1 hour.
@@ -6431,8 +6731,8 @@
 7. Cook time: 10</t>
         </is>
       </c>
-      <c r="U60" t="inlineStr"/>
-      <c r="V60" t="inlineStr">
+      <c r="V60" t="inlineStr"/>
+      <c r="W60" t="inlineStr">
         <is>
           <t>['In a bowl, combine whole wheat flour, semolina, yeast, salt, and warm water; mix until a soft dough forms.', 'Knead on a lightly floured surface for 5–7 minutes until smooth; cover and let rise for 1 hour.', 'Divide the dough into small balls and roll each ball out as thinly as possible into a circle.', 'Preheat a large griddle or nonstick skillet over high heat.', 'Cook each flatbread for 1–2 minutes on each side until bubbles form and the surface is lightly golden.', 'Serve warm.', 'Cook time: 10']</t>
         </is>
@@ -6456,10 +6756,15 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
+          <t>3371</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
           <t>['1 cup semolina', '½ cup whole wheat flour', '1 tsp baking powder', '¼ tsp salt', '1 cup unsweetened applesauce', '⅓ cup honey or maple syrup', '1 tsp ground cinnamon', '½ cup shredded coconut (optional)', '½ cup chopped almonds (optional)', '1/2 cup water (adjust as needed)', 'For the Syrup:', '¼ cup water', '2 tbsp honey', 'Juice of 1 lemon']</t>
         </is>
       </c>
-      <c r="E61" t="inlineStr">
+      <c r="F61" t="inlineStr">
         <is>
           <t>1. Preheat oven to 350°F (175°C). Grease a loaf pan with water or nonstick spray.
 2. In a bowl, whisk together semolina, flour, baking powder, salt, and cinnamon; stir in coconut and almonds if using.
@@ -6471,59 +6776,59 @@
 8. Cook time: 45</t>
         </is>
       </c>
-      <c r="F61" t="inlineStr">
+      <c r="G61" t="inlineStr">
         <is>
           <t>{"calories": 180, "protein": "5 g", "carbs": "32 g", "fiber": "4 g", "fat": "3 g"}</t>
         </is>
       </c>
-      <c r="G61" t="n">
+      <c r="H61" t="n">
         <v>10</v>
       </c>
-      <c r="H61" t="n">
+      <c r="I61" t="n">
         <v>20</v>
       </c>
-      <c r="I61" t="inlineStr">
-        <is>
-          <t>['weight-loss', 'plant-based', 'whole-foods', 'oil-free', 'lunches-and-dinners', 'soups', 'salads', 'wraps', 'sandwiches', 'rice', 'stews', 'stir-fry', 'seafood', 'ethnic', 'arabic', 'desserts']</t>
-        </is>
-      </c>
       <c r="J61" t="inlineStr">
         <is>
+          <t>['arabic', 'desserts', 'ethnic', 'oil-free', 'vegetarian', 'weight-loss']</t>
+        </is>
+      </c>
+      <c r="K61" t="inlineStr">
+        <is>
           <t>oil_free</t>
         </is>
       </c>
-      <c r="K61" t="inlineStr">
-        <is>
-          <t>plant_based</t>
-        </is>
-      </c>
       <c r="L61" t="inlineStr">
         <is>
+          <t>Vegetarian</t>
+        </is>
+      </c>
+      <c r="M61" t="inlineStr">
+        <is>
           <t>Savory</t>
         </is>
       </c>
-      <c r="M61" t="inlineStr">
+      <c r="N61" t="inlineStr">
         <is>
           <t>weight_loss</t>
         </is>
       </c>
-      <c r="N61" t="b">
-        <v>0</v>
-      </c>
       <c r="O61" t="b">
         <v>0</v>
       </c>
-      <c r="P61" t="inlineStr"/>
-      <c r="Q61" t="inlineStr">
+      <c r="P61" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q61" t="inlineStr"/>
+      <c r="R61" t="inlineStr">
         <is>
           <t>hot</t>
         </is>
       </c>
-      <c r="R61" t="n">
-        <v>0</v>
-      </c>
-      <c r="S61" t="inlineStr"/>
-      <c r="T61" t="inlineStr">
+      <c r="S61" t="n">
+        <v>0</v>
+      </c>
+      <c r="T61" t="inlineStr"/>
+      <c r="U61" t="inlineStr">
         <is>
           <t>1. Preheat oven to 350°F (175°C). Grease a loaf pan with water or nonstick spray.
 2. In a bowl, whisk together semolina, flour, baking powder, salt, and cinnamon; stir in coconut and almonds if using.
@@ -6535,8 +6840,8 @@
 8. Cook time: 45</t>
         </is>
       </c>
-      <c r="U61" t="inlineStr"/>
-      <c r="V61" t="inlineStr">
+      <c r="V61" t="inlineStr"/>
+      <c r="W61" t="inlineStr">
         <is>
           <t>['Preheat oven to 350°F (175°C). Grease a loaf pan with water or nonstick spray.', 'In a bowl, whisk together semolina, flour, baking powder, salt, and cinnamon; stir in coconut and almonds if using.', 'In another bowl, mix applesauce, honey, vanilla extract (if using), and water until smooth.', 'Combine the wet and dry ingredients until just blended; pour into the prepared pan.', 'Bake for 45 minutes until a toothpick inserted in the center comes out clean.', 'Meanwhile, prepare the syrup by simmering water, honey, and lemon juice for 5 minutes.', 'Remove the cake from the oven, pour the syrup over it, and let cool before slicing.', 'Cook time: 45']</t>
         </is>
@@ -6560,10 +6865,15 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
+          <t>3372</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
           <t>['For the Pancakes:', '1 cup all-purpose flour (or a mix with whole wheat flour)', '½ cup fine semolina', '1 tsp active dry yeast', '½ tsp salt', '1 cup warm water (adjust as needed)', 'For the Filling:', '1 cup chopped walnuts', '½ cup chopped dates', '½ tsp ground cinnamon', '2 tbsp honey or maple syrup']</t>
         </is>
       </c>
-      <c r="E62" t="inlineStr">
+      <c r="F62" t="inlineStr">
         <is>
           <t>1. In a bowl, combine flour, semolina, yeast, salt, and warm water; whisk until smooth and let rest for 1 hour.
 2. Heat a nonstick skillet over medium heat. Drop about 2–3 tablespoons of batter to form small, thick pancakes. Cook until bubbles form on the surface; do not flip (the pancakes should remain soft on one side).
@@ -6573,59 +6883,59 @@
 6. Cook time: 15</t>
         </is>
       </c>
-      <c r="F62" t="inlineStr">
+      <c r="G62" t="inlineStr">
         <is>
           <t>{"calories": 120, "protein": "3 g", "carbs": "20 g", "fiber": "3 g", "fat": "2 g"}</t>
         </is>
       </c>
-      <c r="G62" t="n">
+      <c r="H62" t="n">
         <v>10</v>
       </c>
-      <c r="H62" t="n">
+      <c r="I62" t="n">
         <v>30</v>
       </c>
-      <c r="I62" t="inlineStr">
-        <is>
-          <t>['weight-loss', 'plant-based', 'whole-foods', 'oil-free', 'lunches-and-dinners', 'soups', 'salads', 'wraps', 'sandwiches', 'rice', 'stews', 'stir-fry', 'seafood', 'ethnic', 'arabic', 'desserts']</t>
-        </is>
-      </c>
       <c r="J62" t="inlineStr">
         <is>
+          <t>['appetizers', 'arabic', 'ethnic', 'oil-free', 'vegetarian', 'weight-loss']</t>
+        </is>
+      </c>
+      <c r="K62" t="inlineStr">
+        <is>
           <t>oil_free</t>
         </is>
       </c>
-      <c r="K62" t="inlineStr">
-        <is>
-          <t>plant_based</t>
-        </is>
-      </c>
       <c r="L62" t="inlineStr">
         <is>
+          <t>Vegetarian</t>
+        </is>
+      </c>
+      <c r="M62" t="inlineStr">
+        <is>
           <t>Savory</t>
         </is>
       </c>
-      <c r="M62" t="inlineStr">
+      <c r="N62" t="inlineStr">
         <is>
           <t>weight_loss</t>
         </is>
       </c>
-      <c r="N62" t="b">
-        <v>0</v>
-      </c>
       <c r="O62" t="b">
         <v>0</v>
       </c>
-      <c r="P62" t="inlineStr"/>
-      <c r="Q62" t="inlineStr">
+      <c r="P62" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q62" t="inlineStr"/>
+      <c r="R62" t="inlineStr">
         <is>
           <t>hot</t>
         </is>
       </c>
-      <c r="R62" t="n">
-        <v>0</v>
-      </c>
-      <c r="S62" t="inlineStr"/>
-      <c r="T62" t="inlineStr">
+      <c r="S62" t="n">
+        <v>0</v>
+      </c>
+      <c r="T62" t="inlineStr"/>
+      <c r="U62" t="inlineStr">
         <is>
           <t>1. In a bowl, combine flour, semolina, yeast, salt, and warm water; whisk until smooth and let rest for 1 hour.
 2. Heat a nonstick skillet over medium heat. Drop about 2–3 tablespoons of batter to form small, thick pancakes. Cook until bubbles form on the surface; do not flip (the pancakes should remain soft on one side).
@@ -6635,8 +6945,8 @@
 6. Cook time: 15</t>
         </is>
       </c>
-      <c r="U62" t="inlineStr"/>
-      <c r="V62" t="inlineStr">
+      <c r="V62" t="inlineStr"/>
+      <c r="W62" t="inlineStr">
         <is>
           <t>['In a bowl, combine flour, semolina, yeast, salt, and warm water; whisk until smooth and let rest for 1 hour.', 'Heat a nonstick skillet over medium heat. Drop about 2–3 tablespoons of batter to form small, thick pancakes. Cook until bubbles form on the surface; do not flip (the pancakes should remain soft on one side).', 'For the filling, mix walnuts, dates, cinnamon, and honey until well combined.', 'Once the pancakes are cooked, fold them in half and stuff with the filling.', 'Serve immediately as a sweet treat.', 'Cook time: 15']</t>
         </is>
@@ -6660,10 +6970,15 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
+          <t>3373</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
           <t>['1 cup fine semolina', '½ cup low fat ricotta cheese', '½ cup low fat milk', '⅓ cup honey or maple syrup', '1 tsp rose water (optional)', '½ tsp ground cardamom', '¼ cup chopped pistachios (for garnish)']</t>
         </is>
       </c>
-      <c r="E63" t="inlineStr">
+      <c r="F63" t="inlineStr">
         <is>
           <t>1. Preheat oven to 375°F (190°C).
 2. In a bowl, combine semolina, ricotta, milk, honey, rose water (if using), and cardamom until smooth.
@@ -6673,59 +6988,59 @@
 6. Cook time: 30</t>
         </is>
       </c>
-      <c r="F63" t="inlineStr">
+      <c r="G63" t="inlineStr">
         <is>
           <t>{"calories": 350, "protein": "12 g", "carbs": "50 g", "fiber": "3 g", "fat": "6 g"}</t>
         </is>
       </c>
-      <c r="G63" t="n">
+      <c r="H63" t="n">
         <v>4</v>
       </c>
-      <c r="H63" t="n">
+      <c r="I63" t="n">
         <v>20</v>
       </c>
-      <c r="I63" t="inlineStr">
-        <is>
-          <t>['weight-loss', 'plant-based', 'whole-foods', 'oil-free', 'lunches-and-dinners', 'soups', 'salads', 'wraps', 'sandwiches', 'rice', 'stews', 'stir-fry', 'seafood', 'ethnic', 'arabic', 'desserts']</t>
-        </is>
-      </c>
       <c r="J63" t="inlineStr">
         <is>
+          <t>['arabic', 'desserts', 'ethnic', 'oil-free', 'vegetarian', 'weight-loss']</t>
+        </is>
+      </c>
+      <c r="K63" t="inlineStr">
+        <is>
           <t>oil_free</t>
         </is>
       </c>
-      <c r="K63" t="inlineStr">
-        <is>
-          <t>plant_based</t>
-        </is>
-      </c>
       <c r="L63" t="inlineStr">
         <is>
+          <t>Vegetarian</t>
+        </is>
+      </c>
+      <c r="M63" t="inlineStr">
+        <is>
           <t>Savory</t>
         </is>
       </c>
-      <c r="M63" t="inlineStr">
+      <c r="N63" t="inlineStr">
         <is>
           <t>weight_loss</t>
         </is>
       </c>
-      <c r="N63" t="b">
-        <v>0</v>
-      </c>
       <c r="O63" t="b">
         <v>0</v>
       </c>
-      <c r="P63" t="inlineStr"/>
-      <c r="Q63" t="inlineStr">
+      <c r="P63" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q63" t="inlineStr"/>
+      <c r="R63" t="inlineStr">
         <is>
           <t>hot</t>
         </is>
       </c>
-      <c r="R63" t="n">
-        <v>0</v>
-      </c>
-      <c r="S63" t="inlineStr"/>
-      <c r="T63" t="inlineStr">
+      <c r="S63" t="n">
+        <v>0</v>
+      </c>
+      <c r="T63" t="inlineStr"/>
+      <c r="U63" t="inlineStr">
         <is>
           <t>1. Preheat oven to 375°F (190°C).
 2. In a bowl, combine semolina, ricotta, milk, honey, rose water (if using), and cardamom until smooth.
@@ -6735,8 +7050,8 @@
 6. Cook time: 30</t>
         </is>
       </c>
-      <c r="U63" t="inlineStr"/>
-      <c r="V63" t="inlineStr">
+      <c r="V63" t="inlineStr"/>
+      <c r="W63" t="inlineStr">
         <is>
           <t>['Preheat oven to 375°F (190°C).', 'In a bowl, combine semolina, ricotta, milk, honey, rose water (if using), and cardamom until smooth.', 'Pour the mixture into a water brushed baking dish.', 'Bake for 25–30 minutes until set and lightly golden on top.', 'Sprinkle with chopped pistachios and serve warm.', 'Cook time: 30']</t>
         </is>
@@ -6755,15 +7070,20 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Oil Free Ma’amoul (Date-Filled Cookies)</t>
+          <t>Oil Free Ma’Amoul (Date-Filled Cookies)</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
+          <t>3374</t>
+        </is>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
           <t>['For the Dough:', '2 cups whole wheat flour', '½ cup semolina', '½ tsp baking soda', '½ tsp salt', '½ cup unsweetened applesauce', '2–3 tbsp water (as needed)', '1 tsp ground cinnamon', 'For the Filling:', '1 cup pitted dates, finely chopped', '½ tsp ground cinnamon', '2 tbsp orange juice']</t>
         </is>
       </c>
-      <c r="E64" t="inlineStr">
+      <c r="F64" t="inlineStr">
         <is>
           <t>1. In a bowl, whisk together flour, semolina, baking soda, salt, and cinnamon. Add applesauce and water to form a firm dough. Let rest for 30 minutes.
 2. In another bowl, combine chopped dates, cinnamon, and orange juice to form the filling.
@@ -6773,59 +7093,59 @@
 6. Cook time: 20</t>
         </is>
       </c>
-      <c r="F64" t="inlineStr">
+      <c r="G64" t="inlineStr">
         <is>
           <t>{"calories": 120, "protein": "3 g", "carbs": "20 g", "fiber": "3 g", "fat": "2 g"}</t>
         </is>
       </c>
-      <c r="G64" t="n">
+      <c r="H64" t="n">
         <v>24</v>
       </c>
-      <c r="H64" t="n">
+      <c r="I64" t="n">
         <v>30</v>
       </c>
-      <c r="I64" t="inlineStr">
-        <is>
-          <t>['weight-loss', 'plant-based', 'whole-foods', 'oil-free', 'lunches-and-dinners', 'soups', 'salads', 'wraps', 'sandwiches', 'rice', 'stews', 'stir-fry', 'seafood', 'ethnic', 'arabic', 'desserts']</t>
-        </is>
-      </c>
       <c r="J64" t="inlineStr">
         <is>
+          <t>['arabic', 'desserts', 'ethnic', 'oil-free', 'vegetarian', 'weight-loss']</t>
+        </is>
+      </c>
+      <c r="K64" t="inlineStr">
+        <is>
           <t>oil_free</t>
         </is>
       </c>
-      <c r="K64" t="inlineStr">
-        <is>
-          <t>plant_based</t>
-        </is>
-      </c>
       <c r="L64" t="inlineStr">
         <is>
+          <t>Vegetarian</t>
+        </is>
+      </c>
+      <c r="M64" t="inlineStr">
+        <is>
           <t>Savory</t>
         </is>
       </c>
-      <c r="M64" t="inlineStr">
+      <c r="N64" t="inlineStr">
         <is>
           <t>weight_loss</t>
         </is>
       </c>
-      <c r="N64" t="b">
-        <v>0</v>
-      </c>
       <c r="O64" t="b">
         <v>0</v>
       </c>
-      <c r="P64" t="inlineStr"/>
-      <c r="Q64" t="inlineStr">
+      <c r="P64" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q64" t="inlineStr"/>
+      <c r="R64" t="inlineStr">
         <is>
           <t>hot</t>
         </is>
       </c>
-      <c r="R64" t="n">
-        <v>0</v>
-      </c>
-      <c r="S64" t="inlineStr"/>
-      <c r="T64" t="inlineStr">
+      <c r="S64" t="n">
+        <v>0</v>
+      </c>
+      <c r="T64" t="inlineStr"/>
+      <c r="U64" t="inlineStr">
         <is>
           <t>1. In a bowl, whisk together flour, semolina, baking soda, salt, and cinnamon. Add applesauce and water to form a firm dough. Let rest for 30 minutes.
 2. In another bowl, combine chopped dates, cinnamon, and orange juice to form the filling.
@@ -6835,8 +7155,8 @@
 6. Cook time: 20</t>
         </is>
       </c>
-      <c r="U64" t="inlineStr"/>
-      <c r="V64" t="inlineStr">
+      <c r="V64" t="inlineStr"/>
+      <c r="W64" t="inlineStr">
         <is>
           <t>['In a bowl, whisk together flour, semolina, baking soda, salt, and cinnamon. Add applesauce and water to form a firm dough. Let rest for 30 minutes.', 'In another bowl, combine chopped dates, cinnamon, and orange juice to form the filling.', 'Take small portions of dough, flatten into a disc, place about 1 teaspoon of filling in the center, and fold to seal, forming a ball.', 'Place on a parchment lined baking sheet and bake at 350°F (175°C) for 20 minutes until lightly golden.', 'Allow to cool and serve.', 'Cook time: 20']</t>
         </is>
@@ -6860,10 +7180,15 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
+          <t>3375</t>
+        </is>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
           <t>['½ cup short-grain rice, rinsed', '4 cups low fat milk (or almond milk)', '¼ cup honey or sugar', '1 tsp vanilla extract', '½ tsp ground cardamom', '¼ cup chopped pistachios (for garnish)']</t>
         </is>
       </c>
-      <c r="E65" t="inlineStr">
+      <c r="F65" t="inlineStr">
         <is>
           <t>1. In a pot, combine rice and milk; bring to a simmer over medium heat.
 2. Cook on low heat for about 45 minutes, stirring occasionally until the rice is very soft and the pudding thickens.
@@ -6872,59 +7197,59 @@
 5. Cook time: 45</t>
         </is>
       </c>
-      <c r="F65" t="inlineStr">
+      <c r="G65" t="inlineStr">
         <is>
           <t>{"calories": 240, "protein": "10 g", "carbs": "40 g", "fiber": "6 g", "fat": "3 g"}</t>
         </is>
       </c>
-      <c r="G65" t="n">
+      <c r="H65" t="n">
         <v>4</v>
       </c>
-      <c r="H65" t="n">
+      <c r="I65" t="n">
         <v>10</v>
       </c>
-      <c r="I65" t="inlineStr">
-        <is>
-          <t>['weight-loss', 'plant-based', 'whole-foods', 'oil-free', 'lunches-and-dinners', 'soups', 'salads', 'wraps', 'sandwiches', 'rice', 'stews', 'stir-fry', 'seafood', 'ethnic', 'arabic', 'desserts']</t>
-        </is>
-      </c>
       <c r="J65" t="inlineStr">
         <is>
+          <t>['arabic', 'desserts', 'ethnic', 'oil-free', 'vegetarian', 'weight-loss']</t>
+        </is>
+      </c>
+      <c r="K65" t="inlineStr">
+        <is>
           <t>oil_free</t>
         </is>
       </c>
-      <c r="K65" t="inlineStr">
-        <is>
-          <t>plant_based</t>
-        </is>
-      </c>
       <c r="L65" t="inlineStr">
         <is>
+          <t>Vegetarian</t>
+        </is>
+      </c>
+      <c r="M65" t="inlineStr">
+        <is>
           <t>Savory</t>
         </is>
       </c>
-      <c r="M65" t="inlineStr">
+      <c r="N65" t="inlineStr">
         <is>
           <t>weight_loss</t>
         </is>
       </c>
-      <c r="N65" t="b">
-        <v>0</v>
-      </c>
       <c r="O65" t="b">
         <v>0</v>
       </c>
-      <c r="P65" t="inlineStr"/>
-      <c r="Q65" t="inlineStr">
+      <c r="P65" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q65" t="inlineStr"/>
+      <c r="R65" t="inlineStr">
         <is>
           <t>hot</t>
         </is>
       </c>
-      <c r="R65" t="n">
-        <v>0</v>
-      </c>
-      <c r="S65" t="inlineStr"/>
-      <c r="T65" t="inlineStr">
+      <c r="S65" t="n">
+        <v>0</v>
+      </c>
+      <c r="T65" t="inlineStr"/>
+      <c r="U65" t="inlineStr">
         <is>
           <t>1. In a pot, combine rice and milk; bring to a simmer over medium heat.
 2. Cook on low heat for about 45 minutes, stirring occasionally until the rice is very soft and the pudding thickens.
@@ -6933,8 +7258,8 @@
 5. Cook time: 45</t>
         </is>
       </c>
-      <c r="U65" t="inlineStr"/>
-      <c r="V65" t="inlineStr">
+      <c r="V65" t="inlineStr"/>
+      <c r="W65" t="inlineStr">
         <is>
           <t>['In a pot, combine rice and milk; bring to a simmer over medium heat.', 'Cook on low heat for about 45 minutes, stirring occasionally until the rice is very soft and the pudding thickens.', 'Stir in honey (or sugar), vanilla, and cardamom.', 'Remove from heat and let cool slightly before serving warm or chilled, garnished with chopped pistachios.', 'Cook time: 45']</t>
         </is>
@@ -6953,15 +7278,20 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Oil Free Arabic Date Rolls (Tamr bi Laban)</t>
+          <t>Oil Free Arabic Date Rolls (Tamr Bi Laban)</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
+          <t>3376</t>
+        </is>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
           <t>['1 cup pitted dates, mashed', '½ cup low fat milk (or water)', '½ tsp ground cinnamon', '¼ cup chopped walnuts', '¼ cup chopped almonds', '¼ cup shredded unsweetened coconut (optional)']</t>
         </is>
       </c>
-      <c r="E66" t="inlineStr">
+      <c r="F66" t="inlineStr">
         <is>
           <t>1. In a bowl, combine mashed dates with milk, ground cinnamon, walnuts, almonds, and shredded coconut until well mixed.
 2. Spread the mixture evenly on a clean surface and roll tightly into a log shape.
@@ -6970,59 +7300,59 @@
 5. Cook time: 1</t>
         </is>
       </c>
-      <c r="F66" t="inlineStr">
+      <c r="G66" t="inlineStr">
         <is>
           <t>{"calories": 230, "protein": "8 g", "carbs": "45 g", "fiber": "7 g", "fat": "5 g"}</t>
         </is>
       </c>
-      <c r="G66" t="n">
+      <c r="H66" t="n">
         <v>6</v>
       </c>
-      <c r="H66" t="n">
+      <c r="I66" t="n">
         <v>15</v>
       </c>
-      <c r="I66" t="inlineStr">
-        <is>
-          <t>['weight-loss', 'plant-based', 'whole-foods', 'oil-free', 'lunches-and-dinners', 'soups', 'salads', 'wraps', 'sandwiches', 'rice', 'stews', 'stir-fry', 'seafood', 'ethnic', 'arabic', 'desserts']</t>
-        </is>
-      </c>
       <c r="J66" t="inlineStr">
         <is>
+          <t>['arabic', 'desserts', 'ethnic', 'oil-free', 'vegetarian', 'weight-loss']</t>
+        </is>
+      </c>
+      <c r="K66" t="inlineStr">
+        <is>
           <t>oil_free</t>
         </is>
       </c>
-      <c r="K66" t="inlineStr">
-        <is>
-          <t>plant_based</t>
-        </is>
-      </c>
       <c r="L66" t="inlineStr">
         <is>
+          <t>Vegetarian</t>
+        </is>
+      </c>
+      <c r="M66" t="inlineStr">
+        <is>
           <t>Savory</t>
         </is>
       </c>
-      <c r="M66" t="inlineStr">
+      <c r="N66" t="inlineStr">
         <is>
           <t>weight_loss</t>
         </is>
       </c>
-      <c r="N66" t="b">
-        <v>0</v>
-      </c>
       <c r="O66" t="b">
         <v>0</v>
       </c>
-      <c r="P66" t="inlineStr"/>
-      <c r="Q66" t="inlineStr">
+      <c r="P66" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q66" t="inlineStr"/>
+      <c r="R66" t="inlineStr">
         <is>
           <t>hot</t>
         </is>
       </c>
-      <c r="R66" t="n">
-        <v>0</v>
-      </c>
-      <c r="S66" t="inlineStr"/>
-      <c r="T66" t="inlineStr">
+      <c r="S66" t="n">
+        <v>0</v>
+      </c>
+      <c r="T66" t="inlineStr"/>
+      <c r="U66" t="inlineStr">
         <is>
           <t>1. In a bowl, combine mashed dates with milk, ground cinnamon, walnuts, almonds, and shredded coconut until well mixed.
 2. Spread the mixture evenly on a clean surface and roll tightly into a log shape.
@@ -7031,8 +7361,8 @@
 5. Cook time: 1</t>
         </is>
       </c>
-      <c r="U66" t="inlineStr"/>
-      <c r="V66" t="inlineStr">
+      <c r="V66" t="inlineStr"/>
+      <c r="W66" t="inlineStr">
         <is>
           <t>['In a bowl, combine mashed dates with milk, ground cinnamon, walnuts, almonds, and shredded coconut until well mixed.', 'Spread the mixture evenly on a clean surface and roll tightly into a log shape.', 'Refrigerate for 1 hour to firm up.', 'Slice into 1 inch thick rolls and serve chilled.', 'Cook time: 1']</t>
         </is>
@@ -7056,10 +7386,15 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
+          <t>3377</t>
+        </is>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
           <t>['1 cup whole wheat flatbread, torn into bite sized pieces', '½ cup puffed rice or barley (optional for extra texture)', '4 cups low fat milk (or unsweetened almond milk)', '¼ cup honey or maple syrup', '1 tsp ground cinnamon', '¼ cup raisins', '¼ cup chopped almonds (optional)', '1 tsp vanilla extract', '1/4 cup chopped pistachios (for garnish)']</t>
         </is>
       </c>
-      <c r="E67" t="inlineStr">
+      <c r="F67" t="inlineStr">
         <is>
           <t>1. Preheat your oven to 350°F (175°C). Arrange the torn flatbread (and puffed rice, if using) evenly in a lightly water brushed baking dish.
 2. In a saucepan, combine the milk, honey, cinnamon, and vanilla extract. Warm gently (do not boil) until the honey dissolves.
@@ -7069,59 +7404,59 @@
 6. Cook time: 35</t>
         </is>
       </c>
-      <c r="F67" t="inlineStr">
+      <c r="G67" t="inlineStr">
         <is>
           <t>{"calories": 350, "protein": "12 g", "carbs": "60 g", "fiber": "5 g", "fat": "4 g"}</t>
         </is>
       </c>
-      <c r="G67" t="n">
+      <c r="H67" t="n">
         <v>6</v>
       </c>
-      <c r="H67" t="n">
+      <c r="I67" t="n">
         <v>15</v>
       </c>
-      <c r="I67" t="inlineStr">
-        <is>
-          <t>['weight-loss', 'plant-based', 'whole-foods', 'oil-free', 'lunches-and-dinners', 'soups', 'salads', 'wraps', 'sandwiches', 'rice', 'stews', 'stir-fry', 'seafood', 'ethnic', 'arabic', 'desserts']</t>
-        </is>
-      </c>
       <c r="J67" t="inlineStr">
         <is>
+          <t>['arabic', 'desserts', 'ethnic', 'oil-free', 'vegetarian', 'weight-loss']</t>
+        </is>
+      </c>
+      <c r="K67" t="inlineStr">
+        <is>
           <t>oil_free</t>
         </is>
       </c>
-      <c r="K67" t="inlineStr">
-        <is>
-          <t>plant_based</t>
-        </is>
-      </c>
       <c r="L67" t="inlineStr">
         <is>
+          <t>Vegetarian</t>
+        </is>
+      </c>
+      <c r="M67" t="inlineStr">
+        <is>
           <t>Savory</t>
         </is>
       </c>
-      <c r="M67" t="inlineStr">
+      <c r="N67" t="inlineStr">
         <is>
           <t>weight_loss</t>
         </is>
       </c>
-      <c r="N67" t="b">
-        <v>0</v>
-      </c>
       <c r="O67" t="b">
         <v>0</v>
       </c>
-      <c r="P67" t="inlineStr"/>
-      <c r="Q67" t="inlineStr">
+      <c r="P67" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q67" t="inlineStr"/>
+      <c r="R67" t="inlineStr">
         <is>
           <t>hot</t>
         </is>
       </c>
-      <c r="R67" t="n">
-        <v>0</v>
-      </c>
-      <c r="S67" t="inlineStr"/>
-      <c r="T67" t="inlineStr">
+      <c r="S67" t="n">
+        <v>0</v>
+      </c>
+      <c r="T67" t="inlineStr"/>
+      <c r="U67" t="inlineStr">
         <is>
           <t>1. Preheat your oven to 350°F (175°C). Arrange the torn flatbread (and puffed rice, if using) evenly in a lightly water brushed baking dish.
 2. In a saucepan, combine the milk, honey, cinnamon, and vanilla extract. Warm gently (do not boil) until the honey dissolves.
@@ -7131,8 +7466,8 @@
 6. Cook time: 35</t>
         </is>
       </c>
-      <c r="U67" t="inlineStr"/>
-      <c r="V67" t="inlineStr">
+      <c r="V67" t="inlineStr"/>
+      <c r="W67" t="inlineStr">
         <is>
           <t>['Preheat your oven to 350°F (175°C). Arrange the torn flatbread (and puffed rice, if using) evenly in a lightly water brushed baking dish.', 'In a saucepan, combine the milk, honey, cinnamon, and vanilla extract. Warm gently (do not boil) until the honey dissolves.', 'Stir in the raisins and chopped almonds, then pour the milk mixture over the bread pieces, ensuring everything is well soaked.', 'Bake uncovered for 30–35 minutes until the pudding is set and the top is lightly golden.', 'Remove from the oven, sprinkle with chopped pistachios, and serve warm or chilled.', 'Cook time: 35']</t>
         </is>
@@ -7151,15 +7486,20 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Oil Free Qatayef  with Walnut Filling</t>
+          <t>Oil Free Qatayef  With Walnut Filling</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
+          <t>3378</t>
+        </is>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
           <t>['For the Pancakes:', '1 cup all-purpose flour (or whole wheat flour)', '1 cup water', '1 tsp active dry yeast', '1 tbsp sugar', '¼ tsp salt For the Filling:', '½ cup walnuts, finely chopped', '¼ cup pitted dates, chopped', '½ tsp ground cinnamon', '1 tbsp orange juice', 'Pinch of salt']</t>
         </is>
       </c>
-      <c r="E68" t="inlineStr">
+      <c r="F68" t="inlineStr">
         <is>
           <t>1. In a bowl, whisk together flour, water, yeast, sugar, and salt until smooth. Cover and let rest for 1 hour until bubbly.
 2. Heat a nonstick skillet over medium heat. Drop about 2–3 tablespoons of batter to form small, thick pancakes (do not flip; cook until bubbles form on top).
@@ -7169,59 +7509,59 @@
 6. Cook time: 15</t>
         </is>
       </c>
-      <c r="F68" t="inlineStr">
+      <c r="G68" t="inlineStr">
         <is>
           <t>{"calories": 120, "protein": "3 g", "carbs": "20 g", "fiber": "3 g", "fat": "2 g"}</t>
         </is>
       </c>
-      <c r="G68" t="n">
+      <c r="H68" t="n">
         <v>10</v>
       </c>
-      <c r="H68" t="n">
+      <c r="I68" t="n">
         <v>20</v>
       </c>
-      <c r="I68" t="inlineStr">
-        <is>
-          <t>['weight-loss', 'plant-based', 'whole-foods', 'oil-free', 'lunches-and-dinners', 'soups', 'salads', 'wraps', 'sandwiches', 'rice', 'stews', 'stir-fry', 'seafood', 'ethnic', 'arabic', 'desserts']</t>
-        </is>
-      </c>
       <c r="J68" t="inlineStr">
         <is>
+          <t>['arabic', 'desserts', 'ethnic', 'oil-free', 'vegetarian', 'weight-loss']</t>
+        </is>
+      </c>
+      <c r="K68" t="inlineStr">
+        <is>
           <t>oil_free</t>
         </is>
       </c>
-      <c r="K68" t="inlineStr">
-        <is>
-          <t>plant_based</t>
-        </is>
-      </c>
       <c r="L68" t="inlineStr">
         <is>
+          <t>Vegetarian</t>
+        </is>
+      </c>
+      <c r="M68" t="inlineStr">
+        <is>
           <t>Savory</t>
         </is>
       </c>
-      <c r="M68" t="inlineStr">
+      <c r="N68" t="inlineStr">
         <is>
           <t>weight_loss</t>
         </is>
       </c>
-      <c r="N68" t="b">
-        <v>0</v>
-      </c>
       <c r="O68" t="b">
         <v>0</v>
       </c>
-      <c r="P68" t="inlineStr"/>
-      <c r="Q68" t="inlineStr">
+      <c r="P68" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q68" t="inlineStr"/>
+      <c r="R68" t="inlineStr">
         <is>
           <t>hot</t>
         </is>
       </c>
-      <c r="R68" t="n">
-        <v>0</v>
-      </c>
-      <c r="S68" t="inlineStr"/>
-      <c r="T68" t="inlineStr">
+      <c r="S68" t="n">
+        <v>0</v>
+      </c>
+      <c r="T68" t="inlineStr"/>
+      <c r="U68" t="inlineStr">
         <is>
           <t>1. In a bowl, whisk together flour, water, yeast, sugar, and salt until smooth. Cover and let rest for 1 hour until bubbly.
 2. Heat a nonstick skillet over medium heat. Drop about 2–3 tablespoons of batter to form small, thick pancakes (do not flip; cook until bubbles form on top).
@@ -7231,8 +7571,8 @@
 6. Cook time: 15</t>
         </is>
       </c>
-      <c r="U68" t="inlineStr"/>
-      <c r="V68" t="inlineStr">
+      <c r="V68" t="inlineStr"/>
+      <c r="W68" t="inlineStr">
         <is>
           <t>['In a bowl, whisk together flour, water, yeast, sugar, and salt until smooth. Cover and let rest for 1 hour until bubbly.', 'Heat a nonstick skillet over medium heat. Drop about 2–3 tablespoons of batter to form small, thick pancakes (do not flip; cook until bubbles form on top).', 'In a separate bowl, combine walnuts, dates, cinnamon, orange juice, and a pinch of salt to form the filling.', 'Once pancakes are done, let them cool slightly, then fold each in half or roll them and place about 1 teaspoon of filling inside each.', 'Serve immediately as a sweet treat.', 'Cook time: 15']</t>
         </is>
@@ -7251,15 +7591,20 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Oil Free Rice Pudding with Saffron &amp; Pistachios</t>
+          <t>Oil Free Rice Pudding With Saffron &amp; Pistachios</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
+          <t>3379</t>
+        </is>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
           <t>['½ cup short grain rice, rinsed', '4 cups low fat milk (or almond milk)', '¼ cup sugar or honey', 'A pinch of saffron threads', '1 tsp vanilla extract', '½ cup chopped pistachios (for garnish)', '½ tsp ground cardamom']</t>
         </is>
       </c>
-      <c r="E69" t="inlineStr">
+      <c r="F69" t="inlineStr">
         <is>
           <t>1. In a heavy pot, combine rice and milk; bring to a simmer over medium heat.
 2. Add sugar, saffron, vanilla, and cardamom; cook on low heat for about 45 minutes, stirring occasionally until the rice is very soft and the pudding has thickened.
@@ -7268,59 +7613,59 @@
 5. Cook time: 45</t>
         </is>
       </c>
-      <c r="F69" t="inlineStr">
+      <c r="G69" t="inlineStr">
         <is>
           <t>{"calories": 240, "protein": "10 g", "carbs": "40 g", "fiber": "6 g", "fat": "3 g"}</t>
         </is>
       </c>
-      <c r="G69" t="n">
+      <c r="H69" t="n">
         <v>4</v>
       </c>
-      <c r="H69" t="n">
+      <c r="I69" t="n">
         <v>10</v>
       </c>
-      <c r="I69" t="inlineStr">
-        <is>
-          <t>['weight-loss', 'plant-based', 'whole-foods', 'oil-free', 'lunches-and-dinners', 'soups', 'salads', 'wraps', 'sandwiches', 'rice', 'stews', 'stir-fry', 'seafood', 'ethnic', 'arabic', 'desserts']</t>
-        </is>
-      </c>
       <c r="J69" t="inlineStr">
         <is>
+          <t>['arabic', 'desserts', 'ethnic', 'oil-free', 'vegetarian', 'weight-loss']</t>
+        </is>
+      </c>
+      <c r="K69" t="inlineStr">
+        <is>
           <t>oil_free</t>
         </is>
       </c>
-      <c r="K69" t="inlineStr">
-        <is>
-          <t>plant_based</t>
-        </is>
-      </c>
       <c r="L69" t="inlineStr">
         <is>
+          <t>Vegetarian</t>
+        </is>
+      </c>
+      <c r="M69" t="inlineStr">
+        <is>
           <t>Savory</t>
         </is>
       </c>
-      <c r="M69" t="inlineStr">
+      <c r="N69" t="inlineStr">
         <is>
           <t>weight_loss</t>
         </is>
       </c>
-      <c r="N69" t="b">
-        <v>0</v>
-      </c>
       <c r="O69" t="b">
         <v>0</v>
       </c>
-      <c r="P69" t="inlineStr"/>
-      <c r="Q69" t="inlineStr">
+      <c r="P69" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q69" t="inlineStr"/>
+      <c r="R69" t="inlineStr">
         <is>
           <t>hot</t>
         </is>
       </c>
-      <c r="R69" t="n">
-        <v>0</v>
-      </c>
-      <c r="S69" t="inlineStr"/>
-      <c r="T69" t="inlineStr">
+      <c r="S69" t="n">
+        <v>0</v>
+      </c>
+      <c r="T69" t="inlineStr"/>
+      <c r="U69" t="inlineStr">
         <is>
           <t>1. In a heavy pot, combine rice and milk; bring to a simmer over medium heat.
 2. Add sugar, saffron, vanilla, and cardamom; cook on low heat for about 45 minutes, stirring occasionally until the rice is very soft and the pudding has thickened.
@@ -7329,8 +7674,8 @@
 5. Cook time: 45</t>
         </is>
       </c>
-      <c r="U69" t="inlineStr"/>
-      <c r="V69" t="inlineStr">
+      <c r="V69" t="inlineStr"/>
+      <c r="W69" t="inlineStr">
         <is>
           <t>['In a heavy pot, combine rice and milk; bring to a simmer over medium heat.', 'Add sugar, saffron, vanilla, and cardamom; cook on low heat for about 45 minutes, stirring occasionally until the rice is very soft and the pudding has thickened.', 'Remove from heat and let cool slightly.', 'Spoon into serving bowls and garnish with chopped pistachios. Serve warm or chilled.', 'Cook time: 45']</t>
         </is>
@@ -7354,10 +7699,15 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
+          <t>3380</t>
+        </is>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
           <t>['1 cup whole wheat flour', '½ cup fine semolina', '1 tsp active dry yeast', '¼ tsp salt', '¾ cup warm water (adjust as needed)', '1 cup finely chopped walnuts or pistachios', '2 tbsp honey or maple syrup', '1 tsp ground cinnamon', '1 tbsp orange juice']</t>
         </is>
       </c>
-      <c r="E70" t="inlineStr">
+      <c r="F70" t="inlineStr">
         <is>
           <t>1. In a bowl, combine flour, semolina, yeast, salt, and warm water to form a smooth dough; cover and let rise for 1 hour.
 2. In another bowl, mix chopped nuts with honey, cinnamon, and orange juice to create the filling.
@@ -7368,59 +7718,59 @@
 7. Cook time: 25</t>
         </is>
       </c>
-      <c r="F70" t="inlineStr">
+      <c r="G70" t="inlineStr">
         <is>
           <t>{"calories": 300, "protein": "8 g", "carbs": "45 g", "fiber": "5 g", "fat": "8 g"}</t>
         </is>
       </c>
-      <c r="G70" t="n">
+      <c r="H70" t="n">
         <v>4</v>
       </c>
-      <c r="H70" t="n">
+      <c r="I70" t="n">
         <v>30</v>
       </c>
-      <c r="I70" t="inlineStr">
-        <is>
-          <t>['weight-loss', 'plant-based', 'whole-foods', 'oil-free', 'lunches-and-dinners', 'soups', 'salads', 'wraps', 'sandwiches', 'rice', 'stews', 'stir-fry', 'seafood', 'ethnic', 'arabic', 'desserts']</t>
-        </is>
-      </c>
       <c r="J70" t="inlineStr">
         <is>
+          <t>['arabic', 'desserts', 'ethnic', 'oil-free', 'vegetarian', 'weight-loss']</t>
+        </is>
+      </c>
+      <c r="K70" t="inlineStr">
+        <is>
           <t>oil_free</t>
         </is>
       </c>
-      <c r="K70" t="inlineStr">
-        <is>
-          <t>plant_based</t>
-        </is>
-      </c>
       <c r="L70" t="inlineStr">
         <is>
+          <t>Vegetarian</t>
+        </is>
+      </c>
+      <c r="M70" t="inlineStr">
+        <is>
           <t>Savory</t>
         </is>
       </c>
-      <c r="M70" t="inlineStr">
+      <c r="N70" t="inlineStr">
         <is>
           <t>weight_loss</t>
         </is>
       </c>
-      <c r="N70" t="b">
-        <v>0</v>
-      </c>
       <c r="O70" t="b">
         <v>0</v>
       </c>
-      <c r="P70" t="inlineStr"/>
-      <c r="Q70" t="inlineStr">
+      <c r="P70" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q70" t="inlineStr"/>
+      <c r="R70" t="inlineStr">
         <is>
           <t>hot</t>
         </is>
       </c>
-      <c r="R70" t="n">
-        <v>0</v>
-      </c>
-      <c r="S70" t="inlineStr"/>
-      <c r="T70" t="inlineStr">
+      <c r="S70" t="n">
+        <v>0</v>
+      </c>
+      <c r="T70" t="inlineStr"/>
+      <c r="U70" t="inlineStr">
         <is>
           <t>1. In a bowl, combine flour, semolina, yeast, salt, and warm water to form a smooth dough; cover and let rise for 1 hour.
 2. In another bowl, mix chopped nuts with honey, cinnamon, and orange juice to create the filling.
@@ -7431,8 +7781,8 @@
 7. Cook time: 25</t>
         </is>
       </c>
-      <c r="U70" t="inlineStr"/>
-      <c r="V70" t="inlineStr">
+      <c r="V70" t="inlineStr"/>
+      <c r="W70" t="inlineStr">
         <is>
           <t>['In a bowl, combine flour, semolina, yeast, salt, and warm water to form a smooth dough; cover and let rise for 1 hour.', 'In another bowl, mix chopped nuts with honey, cinnamon, and orange juice to create the filling.', 'Preheat your oven to 375°F (190°C). Divide the dough into 8 equal pieces; roll each piece into a thin rectangle on a lightly floured surface.', 'Spread a thin layer of the nut mixture along the long side of each rectangle. Roll tightly into a log, then coil the log into a spiral on a parchment lined baking sheet.', 'Bake for 20–25 minutes until golden and crisp.', 'Let cool before serving.', 'Cook time: 25']</t>
         </is>
@@ -7451,15 +7801,20 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Oil Free Ma’amoul with Pistachio Filling</t>
+          <t>Oil Free Ma’Amoul With Pistachio Filling</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
+          <t>3381</t>
+        </is>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
           <t>['For the Dough:', '2 cups whole wheat flour', '½ cup semolina', '½ tsp baking soda', '½ tsp salt', '½ cup unsweetened applesauce', '2–3 tbsp water (as needed)', '1 tsp ground cinnamon', 'For the Filling:', '1 cup pitted dates, finely chopped', '½ cup pistachios, chopped', '1 tsp ground cardamom', '1 tbsp orange juice']</t>
         </is>
       </c>
-      <c r="E71" t="inlineStr">
+      <c r="F71" t="inlineStr">
         <is>
           <t>1. In a bowl, whisk together whole wheat flour, semolina, baking soda, salt, and cinnamon. Stir in applesauce and water to form a firm dough; cover and let rest for 30 minutes.
 2. In another bowl, mix dates, chopped pistachios, cardamom, and orange juice to create the filling.
@@ -7469,59 +7824,59 @@
 6. Cook time: 25</t>
         </is>
       </c>
-      <c r="F71" t="inlineStr">
+      <c r="G71" t="inlineStr">
         <is>
           <t>{"calories": 120, "protein": "3 g", "carbs": "20 g", "fiber": "3 g", "fat": "2 g"}</t>
         </is>
       </c>
-      <c r="G71" t="n">
+      <c r="H71" t="n">
         <v>24</v>
       </c>
-      <c r="H71" t="n">
+      <c r="I71" t="n">
         <v>30</v>
       </c>
-      <c r="I71" t="inlineStr">
-        <is>
-          <t>['weight-loss', 'plant-based', 'whole-foods', 'oil-free', 'lunches-and-dinners', 'soups', 'salads', 'wraps', 'sandwiches', 'rice', 'stews', 'stir-fry', 'seafood', 'ethnic', 'arabic', 'desserts']</t>
-        </is>
-      </c>
       <c r="J71" t="inlineStr">
         <is>
+          <t>['arabic', 'desserts', 'ethnic', 'oil-free', 'vegetarian', 'weight-loss']</t>
+        </is>
+      </c>
+      <c r="K71" t="inlineStr">
+        <is>
           <t>oil_free</t>
         </is>
       </c>
-      <c r="K71" t="inlineStr">
-        <is>
-          <t>plant_based</t>
-        </is>
-      </c>
       <c r="L71" t="inlineStr">
         <is>
+          <t>Vegetarian</t>
+        </is>
+      </c>
+      <c r="M71" t="inlineStr">
+        <is>
           <t>Savory</t>
         </is>
       </c>
-      <c r="M71" t="inlineStr">
+      <c r="N71" t="inlineStr">
         <is>
           <t>weight_loss</t>
         </is>
       </c>
-      <c r="N71" t="b">
-        <v>0</v>
-      </c>
       <c r="O71" t="b">
         <v>0</v>
       </c>
-      <c r="P71" t="inlineStr"/>
-      <c r="Q71" t="inlineStr">
+      <c r="P71" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q71" t="inlineStr"/>
+      <c r="R71" t="inlineStr">
         <is>
           <t>hot</t>
         </is>
       </c>
-      <c r="R71" t="n">
-        <v>0</v>
-      </c>
-      <c r="S71" t="inlineStr"/>
-      <c r="T71" t="inlineStr">
+      <c r="S71" t="n">
+        <v>0</v>
+      </c>
+      <c r="T71" t="inlineStr"/>
+      <c r="U71" t="inlineStr">
         <is>
           <t>1. In a bowl, whisk together whole wheat flour, semolina, baking soda, salt, and cinnamon. Stir in applesauce and water to form a firm dough; cover and let rest for 30 minutes.
 2. In another bowl, mix dates, chopped pistachios, cardamom, and orange juice to create the filling.
@@ -7531,8 +7886,8 @@
 6. Cook time: 25</t>
         </is>
       </c>
-      <c r="U71" t="inlineStr"/>
-      <c r="V71" t="inlineStr">
+      <c r="V71" t="inlineStr"/>
+      <c r="W71" t="inlineStr">
         <is>
           <t>['In a bowl, whisk together whole wheat flour, semolina, baking soda, salt, and cinnamon. Stir in applesauce and water to form a firm dough; cover and let rest for 30 minutes.', 'In another bowl, mix dates, chopped pistachios, cardamom, and orange juice to create the filling.', 'Take small portions of dough, flatten into discs, and place about 1 teaspoon of filling in the center; fold and seal the dough to enclose the filling, shaping into small balls.', 'Place on a parchment lined baking sheet and bake at 350°F (175°C) for 20–25 minutes until lightly golden.', 'Allow to cool before serving.', 'Cook time: 25']</t>
         </is>
@@ -7556,10 +7911,15 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
+          <t>3382</t>
+        </is>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
           <t>['1 cup chickpea flour (besan)', '2 cups low fat milk (or almond milk)', '1/3 cup sugar or honey', '1 tsp vanilla extract', '1/2 tsp ground cardamom', '1/4 cup water', '1/4 cup chopped pistachios (for garnish)']</t>
         </is>
       </c>
-      <c r="E72" t="inlineStr">
+      <c r="F72" t="inlineStr">
         <is>
           <t>1. In a nonstick pan, whisk together chickpea flour and water to form a smooth paste.
 2. Slowly add milk while stirring continuously to avoid lumps.
@@ -7569,59 +7929,59 @@
 6. Cook time: 20</t>
         </is>
       </c>
-      <c r="F72" t="inlineStr">
+      <c r="G72" t="inlineStr">
         <is>
           <t>{"calories": 160, "protein": "5 g", "carbs": "30 g", "fiber": "4 g", "fat": "3 g"}</t>
         </is>
       </c>
-      <c r="G72" t="n">
+      <c r="H72" t="n">
         <v>10</v>
       </c>
-      <c r="H72" t="n">
+      <c r="I72" t="n">
         <v>15</v>
       </c>
-      <c r="I72" t="inlineStr">
-        <is>
-          <t>['weight-loss', 'plant-based', 'whole-foods', 'oil-free', 'lunches-and-dinners', 'soups', 'salads', 'wraps', 'sandwiches', 'rice', 'stews', 'stir-fry', 'seafood', 'ethnic', 'arabic', 'desserts']</t>
-        </is>
-      </c>
       <c r="J72" t="inlineStr">
         <is>
+          <t>['arabic', 'desserts', 'ethnic', 'oil-free', 'vegetarian', 'weight-loss']</t>
+        </is>
+      </c>
+      <c r="K72" t="inlineStr">
+        <is>
           <t>oil_free</t>
         </is>
       </c>
-      <c r="K72" t="inlineStr">
-        <is>
-          <t>plant_based</t>
-        </is>
-      </c>
       <c r="L72" t="inlineStr">
         <is>
+          <t>Vegetarian</t>
+        </is>
+      </c>
+      <c r="M72" t="inlineStr">
+        <is>
           <t>Savory</t>
         </is>
       </c>
-      <c r="M72" t="inlineStr">
+      <c r="N72" t="inlineStr">
         <is>
           <t>weight_loss</t>
         </is>
       </c>
-      <c r="N72" t="b">
-        <v>0</v>
-      </c>
       <c r="O72" t="b">
         <v>0</v>
       </c>
-      <c r="P72" t="inlineStr"/>
-      <c r="Q72" t="inlineStr">
+      <c r="P72" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q72" t="inlineStr"/>
+      <c r="R72" t="inlineStr">
         <is>
           <t>hot</t>
         </is>
       </c>
-      <c r="R72" t="n">
-        <v>0</v>
-      </c>
-      <c r="S72" t="inlineStr"/>
-      <c r="T72" t="inlineStr">
+      <c r="S72" t="n">
+        <v>0</v>
+      </c>
+      <c r="T72" t="inlineStr"/>
+      <c r="U72" t="inlineStr">
         <is>
           <t>1. In a nonstick pan, whisk together chickpea flour and water to form a smooth paste.
 2. Slowly add milk while stirring continuously to avoid lumps.
@@ -7631,8 +7991,8 @@
 6. Cook time: 20</t>
         </is>
       </c>
-      <c r="U72" t="inlineStr"/>
-      <c r="V72" t="inlineStr">
+      <c r="V72" t="inlineStr"/>
+      <c r="W72" t="inlineStr">
         <is>
           <t>['In a nonstick pan, whisk together chickpea flour and water to form a smooth paste.', 'Slowly add milk while stirring continuously to avoid lumps.', 'Add sugar, vanilla extract, and cardamom; cook over low heat, stirring constantly for about 15–20 minutes until the mixture thickens and pulls away from the sides of the pan.', 'Pour the mixture into a greased (use nonstick spray or water) dish and let it cool completely.', 'Garnish with chopped pistachios and cut into squares before serving.', 'Cook time: 20']</t>
         </is>
@@ -7656,10 +8016,15 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
+          <t>3383</t>
+        </is>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
           <t>['2 cups almond flour', '1/2 cup whole wheat flour', '1/3 cup powdered sugar', '1/4 tsp salt', '1/2 cup unsweetened applesauce', '1 tsp vanilla extract', '1/4 cup almond milk (if needed for consistency)', '1/4 cup sliced almonds (for topping)']</t>
         </is>
       </c>
-      <c r="E73" t="inlineStr">
+      <c r="F73" t="inlineStr">
         <is>
           <t>1. Preheat oven to 350°F (175°C).
 2. In a bowl, mix almond flour, whole wheat flour, powdered sugar, and salt.
@@ -7671,59 +8036,59 @@
 8. Cook time: 15</t>
         </is>
       </c>
-      <c r="F73" t="inlineStr">
+      <c r="G73" t="inlineStr">
         <is>
           <t>{"calories": 90, "protein": "3 g", "carbs": "12 g", "fiber": "2 g", "fat": "4 g"}</t>
         </is>
       </c>
-      <c r="G73" t="n">
+      <c r="H73" t="n">
         <v>24</v>
       </c>
-      <c r="H73" t="n">
+      <c r="I73" t="n">
         <v>20</v>
       </c>
-      <c r="I73" t="inlineStr">
-        <is>
-          <t>['weight-loss', 'plant-based', 'whole-foods', 'oil-free', 'lunches-and-dinners', 'soups', 'salads', 'wraps', 'sandwiches', 'rice', 'stews', 'stir-fry', 'seafood', 'ethnic', 'arabic', 'desserts']</t>
-        </is>
-      </c>
       <c r="J73" t="inlineStr">
         <is>
+          <t>['arabic', 'desserts', 'ethnic', 'oil-free', 'vegetarian', 'weight-loss']</t>
+        </is>
+      </c>
+      <c r="K73" t="inlineStr">
+        <is>
           <t>oil_free</t>
         </is>
       </c>
-      <c r="K73" t="inlineStr">
-        <is>
-          <t>plant_based</t>
-        </is>
-      </c>
       <c r="L73" t="inlineStr">
         <is>
+          <t>Vegetarian</t>
+        </is>
+      </c>
+      <c r="M73" t="inlineStr">
+        <is>
           <t>Savory</t>
         </is>
       </c>
-      <c r="M73" t="inlineStr">
+      <c r="N73" t="inlineStr">
         <is>
           <t>weight_loss</t>
         </is>
       </c>
-      <c r="N73" t="b">
-        <v>0</v>
-      </c>
       <c r="O73" t="b">
         <v>0</v>
       </c>
-      <c r="P73" t="inlineStr"/>
-      <c r="Q73" t="inlineStr">
+      <c r="P73" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q73" t="inlineStr"/>
+      <c r="R73" t="inlineStr">
         <is>
           <t>hot</t>
         </is>
       </c>
-      <c r="R73" t="n">
-        <v>0</v>
-      </c>
-      <c r="S73" t="inlineStr"/>
-      <c r="T73" t="inlineStr">
+      <c r="S73" t="n">
+        <v>0</v>
+      </c>
+      <c r="T73" t="inlineStr"/>
+      <c r="U73" t="inlineStr">
         <is>
           <t>1. Preheat oven to 350°F (175°C).
 2. In a bowl, mix almond flour, whole wheat flour, powdered sugar, and salt.
@@ -7735,8 +8100,8 @@
 8. Cook time: 15</t>
         </is>
       </c>
-      <c r="U73" t="inlineStr"/>
-      <c r="V73" t="inlineStr">
+      <c r="V73" t="inlineStr"/>
+      <c r="W73" t="inlineStr">
         <is>
           <t>['Preheat oven to 350°F (175°C).', 'In a bowl, mix almond flour, whole wheat flour, powdered sugar, and salt.', 'Add applesauce and vanilla extract; mix until a soft dough forms. If the dough is too dry, add almond milk a tablespoon at a time.', 'Shape the dough into small round cookies and place them on a parchment lined baking sheet.', 'Gently press a few sliced almonds onto the top of each cookie.', 'Bake for 12–15 minutes until the edges are just set.', 'Allow to cool on a wire rack before serving.', 'Cook time: 15']</t>
         </is>
@@ -7760,10 +8125,15 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
+          <t>3384</t>
+        </is>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
           <t>['4 cups grated carrots', '3 cups low fat milk (or almond milk)', '1/3 cup sugar or honey', '1 tsp ground cardamom', '½ cup chopped raisins', '1/4 cup chopped almonds (optional)', '1 tsp vanilla extract']</t>
         </is>
       </c>
-      <c r="E74" t="inlineStr">
+      <c r="F74" t="inlineStr">
         <is>
           <t>1. In a large, heavy saucepan, combine grated carrots and milk; bring to a simmer over medium heat.
 2. Cook, stirring frequently, for about 45 minutes until the carrots are very soft and the mixture thickens.
@@ -7773,59 +8143,59 @@
 6. Cook time: 55</t>
         </is>
       </c>
-      <c r="F74" t="inlineStr">
+      <c r="G74" t="inlineStr">
         <is>
           <t>{"calories": 280, "protein": "8 g", "carbs": "50 g", "fiber": "6 g", "fat": "4 g"}</t>
         </is>
       </c>
-      <c r="G74" t="n">
+      <c r="H74" t="n">
         <v>4</v>
       </c>
-      <c r="H74" t="n">
+      <c r="I74" t="n">
         <v>15</v>
       </c>
-      <c r="I74" t="inlineStr">
-        <is>
-          <t>['weight-loss', 'plant-based', 'whole-foods', 'oil-free', 'lunches-and-dinners', 'soups', 'salads', 'wraps', 'sandwiches', 'rice', 'stews', 'stir-fry', 'seafood', 'ethnic', 'arabic', 'desserts']</t>
-        </is>
-      </c>
       <c r="J74" t="inlineStr">
         <is>
+          <t>['arabic', 'desserts', 'ethnic', 'oil-free', 'vegetarian', 'weight-loss']</t>
+        </is>
+      </c>
+      <c r="K74" t="inlineStr">
+        <is>
           <t>oil_free</t>
         </is>
       </c>
-      <c r="K74" t="inlineStr">
-        <is>
-          <t>plant_based</t>
-        </is>
-      </c>
       <c r="L74" t="inlineStr">
         <is>
+          <t>Vegetarian</t>
+        </is>
+      </c>
+      <c r="M74" t="inlineStr">
+        <is>
           <t>Savory</t>
         </is>
       </c>
-      <c r="M74" t="inlineStr">
+      <c r="N74" t="inlineStr">
         <is>
           <t>weight_loss</t>
         </is>
       </c>
-      <c r="N74" t="b">
-        <v>0</v>
-      </c>
       <c r="O74" t="b">
         <v>0</v>
       </c>
-      <c r="P74" t="inlineStr"/>
-      <c r="Q74" t="inlineStr">
+      <c r="P74" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q74" t="inlineStr"/>
+      <c r="R74" t="inlineStr">
         <is>
           <t>hot</t>
         </is>
       </c>
-      <c r="R74" t="n">
-        <v>0</v>
-      </c>
-      <c r="S74" t="inlineStr"/>
-      <c r="T74" t="inlineStr">
+      <c r="S74" t="n">
+        <v>0</v>
+      </c>
+      <c r="T74" t="inlineStr"/>
+      <c r="U74" t="inlineStr">
         <is>
           <t>1. In a large, heavy saucepan, combine grated carrots and milk; bring to a simmer over medium heat.
 2. Cook, stirring frequently, for about 45 minutes until the carrots are very soft and the mixture thickens.
@@ -7835,8 +8205,8 @@
 6. Cook time: 55</t>
         </is>
       </c>
-      <c r="U74" t="inlineStr"/>
-      <c r="V74" t="inlineStr">
+      <c r="V74" t="inlineStr"/>
+      <c r="W74" t="inlineStr">
         <is>
           <t>['In a large, heavy saucepan, combine grated carrots and milk; bring to a simmer over medium heat.', 'Cook, stirring frequently, for about 45 minutes until the carrots are very soft and the mixture thickens.', 'Stir in sugar, cardamom, raisins, and vanilla extract; continue to simmer for 10 more minutes until the halwa reaches a pudding-like consistency.', 'If desired, stir in chopped almonds.', 'Serve warm or chilled.', 'Cook time: 55']</t>
         </is>
@@ -7860,10 +8230,15 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
+          <t>3385</t>
+        </is>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
           <t>['4 cups low fat milk (or almond milk)', '1/3 cup sugar or honey', '3 tbsp cornstarch', '1 tsp rose water', '1 tsp vanilla extract', '1/4 tsp ground cardamom', 'Fresh rose petals or chopped pistachios (for garnish)']</t>
         </is>
       </c>
-      <c r="E75" t="inlineStr">
+      <c r="F75" t="inlineStr">
         <is>
           <t>1. In a saucepan, whisk together cornstarch and sugar (or honey) with ½ cup of milk until smooth.
 2. Gradually add the remaining milk while stirring constantly.
@@ -7874,59 +8249,59 @@
 7. Cook time: 10</t>
         </is>
       </c>
-      <c r="F75" t="inlineStr">
+      <c r="G75" t="inlineStr">
         <is>
           <t>{"calories": 240, "protein": "10 g", "carbs": "40 g", "fiber": "6 g", "fat": "3 g"}</t>
         </is>
       </c>
-      <c r="G75" t="n">
+      <c r="H75" t="n">
         <v>4</v>
       </c>
-      <c r="H75" t="n">
+      <c r="I75" t="n">
         <v>10</v>
       </c>
-      <c r="I75" t="inlineStr">
-        <is>
-          <t>['weight-loss', 'plant-based', 'whole-foods', 'oil-free', 'lunches-and-dinners', 'soups', 'salads', 'wraps', 'sandwiches', 'rice', 'stews', 'stir-fry', 'seafood', 'ethnic', 'arabic', 'desserts']</t>
-        </is>
-      </c>
       <c r="J75" t="inlineStr">
         <is>
+          <t>['arabic', 'desserts', 'ethnic', 'oil-free', 'vegetarian', 'weight-loss']</t>
+        </is>
+      </c>
+      <c r="K75" t="inlineStr">
+        <is>
           <t>oil_free</t>
         </is>
       </c>
-      <c r="K75" t="inlineStr">
-        <is>
-          <t>plant_based</t>
-        </is>
-      </c>
       <c r="L75" t="inlineStr">
         <is>
+          <t>Vegetarian</t>
+        </is>
+      </c>
+      <c r="M75" t="inlineStr">
+        <is>
           <t>Savory</t>
         </is>
       </c>
-      <c r="M75" t="inlineStr">
+      <c r="N75" t="inlineStr">
         <is>
           <t>weight_loss</t>
         </is>
       </c>
-      <c r="N75" t="b">
-        <v>0</v>
-      </c>
       <c r="O75" t="b">
         <v>0</v>
       </c>
-      <c r="P75" t="inlineStr"/>
-      <c r="Q75" t="inlineStr">
+      <c r="P75" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q75" t="inlineStr"/>
+      <c r="R75" t="inlineStr">
         <is>
           <t>hot</t>
         </is>
       </c>
-      <c r="R75" t="n">
-        <v>0</v>
-      </c>
-      <c r="S75" t="inlineStr"/>
-      <c r="T75" t="inlineStr">
+      <c r="S75" t="n">
+        <v>0</v>
+      </c>
+      <c r="T75" t="inlineStr"/>
+      <c r="U75" t="inlineStr">
         <is>
           <t>1. In a saucepan, whisk together cornstarch and sugar (or honey) with ½ cup of milk until smooth.
 2. Gradually add the remaining milk while stirring constantly.
@@ -7937,8 +8312,8 @@
 7. Cook time: 10</t>
         </is>
       </c>
-      <c r="U75" t="inlineStr"/>
-      <c r="V75" t="inlineStr">
+      <c r="V75" t="inlineStr"/>
+      <c r="W75" t="inlineStr">
         <is>
           <t>['In a saucepan, whisk together cornstarch and sugar (or honey) with ½ cup of milk until smooth.', 'Gradually add the remaining milk while stirring constantly.', 'Bring the mixture to a gentle simmer over medium heat; stir continuously until the pudding thickens (about 10–12 minutes).', 'Remove from heat and stir in rose water, vanilla extract, and cardamom.', 'Pour into serving bowls, allow to cool, and chill in the refrigerator for at least 2 hours.', 'Garnish with fresh rose petals or chopped pistachios before serving.', 'Cook time: 10']</t>
         </is>
@@ -7962,10 +8337,15 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
+          <t>3386</t>
+        </is>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
           <t>['2 cups glutinous rice flour', '1 ½ cups water', '1/4 cup sugar or honey', '1/4 tsp salt', '1 tsp orange blossom water', '1/2 cup chopped dried apricots', '1/4 cup chopped pistachios (for garnish)']</t>
         </is>
       </c>
-      <c r="E76" t="inlineStr">
+      <c r="F76" t="inlineStr">
         <is>
           <t>1. In a bowl, mix glutinous rice flour, water, sugar, salt, and orange blossom water until smooth.
 2. Stir in chopped dried apricots.
@@ -7976,59 +8356,59 @@
 7. Cook time: 40</t>
         </is>
       </c>
-      <c r="F76" t="inlineStr">
+      <c r="G76" t="inlineStr">
         <is>
           <t>{"calories": 250, "protein": "5 g", "carbs": "55 g", "fiber": "4 g", "fat": "2 g"}</t>
         </is>
       </c>
-      <c r="G76" t="n">
+      <c r="H76" t="n">
         <v>6</v>
       </c>
-      <c r="H76" t="n">
+      <c r="I76" t="n">
         <v>15</v>
       </c>
-      <c r="I76" t="inlineStr">
-        <is>
-          <t>['weight-loss', 'plant-based', 'whole-foods', 'oil-free', 'lunches-and-dinners', 'soups', 'salads', 'wraps', 'sandwiches', 'rice', 'stews', 'stir-fry', 'seafood', 'ethnic', 'arabic', 'desserts']</t>
-        </is>
-      </c>
       <c r="J76" t="inlineStr">
         <is>
+          <t>['arabic', 'desserts', 'ethnic', 'oil-free', 'vegetarian', 'weight-loss']</t>
+        </is>
+      </c>
+      <c r="K76" t="inlineStr">
+        <is>
           <t>oil_free</t>
         </is>
       </c>
-      <c r="K76" t="inlineStr">
-        <is>
-          <t>plant_based</t>
-        </is>
-      </c>
       <c r="L76" t="inlineStr">
         <is>
+          <t>Vegetarian</t>
+        </is>
+      </c>
+      <c r="M76" t="inlineStr">
+        <is>
           <t>Savory</t>
         </is>
       </c>
-      <c r="M76" t="inlineStr">
+      <c r="N76" t="inlineStr">
         <is>
           <t>weight_loss</t>
         </is>
       </c>
-      <c r="N76" t="b">
-        <v>0</v>
-      </c>
       <c r="O76" t="b">
         <v>0</v>
       </c>
-      <c r="P76" t="inlineStr"/>
-      <c r="Q76" t="inlineStr">
+      <c r="P76" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q76" t="inlineStr"/>
+      <c r="R76" t="inlineStr">
         <is>
           <t>hot</t>
         </is>
       </c>
-      <c r="R76" t="n">
-        <v>0</v>
-      </c>
-      <c r="S76" t="inlineStr"/>
-      <c r="T76" t="inlineStr">
+      <c r="S76" t="n">
+        <v>0</v>
+      </c>
+      <c r="T76" t="inlineStr"/>
+      <c r="U76" t="inlineStr">
         <is>
           <t>1. In a bowl, mix glutinous rice flour, water, sugar, salt, and orange blossom water until smooth.
 2. Stir in chopped dried apricots.
@@ -8039,8 +8419,8 @@
 7. Cook time: 40</t>
         </is>
       </c>
-      <c r="U76" t="inlineStr"/>
-      <c r="V76" t="inlineStr">
+      <c r="V76" t="inlineStr"/>
+      <c r="W76" t="inlineStr">
         <is>
           <t>['In a bowl, mix glutinous rice flour, water, sugar, salt, and orange blossom water until smooth.', 'Stir in chopped dried apricots.', 'Pour the batter into a water brushed 8x8 inch pan and smooth the top.', 'Steam the mixture over boiling water for 40 minutes until the rice cake is set.', 'Remove, let cool completely, then cut into slices.', 'Garnish each slice with chopped pistachios before serving.', 'Cook time: 40']</t>
         </is>
@@ -8059,15 +8439,20 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Oil Free Beef  Kebabs with Sumac &amp; Onions</t>
+          <t>Oil Free Beef  Kebabs With Sumac &amp; Onions</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
+          <t>3387</t>
+        </is>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
           <t>['1 lb lean beef sirloin, cut into 1 inch cubes', '1 tsp ground sumac', '4 garlic cloves, minced', '1 large red onion, cut into wedges', 'Juice of 1 lemon', 'Salt and pepper, to taste', '2 cups water (for marinating)', 'Lemon wedges and chopped parsley (for garnish)']</t>
         </is>
       </c>
-      <c r="E77" t="inlineStr">
+      <c r="F77" t="inlineStr">
         <is>
           <t>1. In a bowl, combine beef cubes with minced garlic, lemon juice, sumac, salt, and pepper. Add 2 cups water and let marinate in the refrigerator for 30 minutes.
 2. Thread the beef and a wedge of red onion alternately onto soaked wooden skewers.
@@ -8076,59 +8461,59 @@
 5. Cook time: 10</t>
         </is>
       </c>
-      <c r="F77" t="inlineStr">
+      <c r="G77" t="inlineStr">
         <is>
           <t>{"calories": 450, "protein": "38 g", "carbs": "30 g", "fiber": "5 g", "fat": "8 g"}</t>
         </is>
       </c>
-      <c r="G77" t="n">
+      <c r="H77" t="n">
         <v>4</v>
       </c>
-      <c r="H77" t="n">
+      <c r="I77" t="n">
         <v>20</v>
       </c>
-      <c r="I77" t="inlineStr">
-        <is>
-          <t>['weight-loss', 'plant-based', 'whole-foods', 'oil-free', 'lunches-and-dinners', 'soups', 'salads', 'wraps', 'sandwiches', 'rice', 'stews', 'stir-fry', 'seafood', 'ethnic', 'arabic', 'desserts']</t>
-        </is>
-      </c>
       <c r="J77" t="inlineStr">
         <is>
+          <t>['animal-protein', 'arabic', 'ethnic', 'lunches-and-dinners', 'oil-free', 'weight-loss']</t>
+        </is>
+      </c>
+      <c r="K77" t="inlineStr">
+        <is>
           <t>oil_free</t>
         </is>
       </c>
-      <c r="K77" t="inlineStr">
+      <c r="L77" t="inlineStr">
         <is>
           <t>plant_based</t>
         </is>
       </c>
-      <c r="L77" t="inlineStr">
+      <c r="M77" t="inlineStr">
         <is>
           <t>Savory</t>
         </is>
       </c>
-      <c r="M77" t="inlineStr">
+      <c r="N77" t="inlineStr">
         <is>
           <t>weight_loss</t>
         </is>
       </c>
-      <c r="N77" t="b">
-        <v>0</v>
-      </c>
       <c r="O77" t="b">
         <v>0</v>
       </c>
-      <c r="P77" t="inlineStr"/>
-      <c r="Q77" t="inlineStr">
+      <c r="P77" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q77" t="inlineStr"/>
+      <c r="R77" t="inlineStr">
         <is>
           <t>hot</t>
         </is>
       </c>
-      <c r="R77" t="n">
-        <v>0</v>
-      </c>
-      <c r="S77" t="inlineStr"/>
-      <c r="T77" t="inlineStr">
+      <c r="S77" t="n">
+        <v>0</v>
+      </c>
+      <c r="T77" t="inlineStr"/>
+      <c r="U77" t="inlineStr">
         <is>
           <t>1. In a bowl, combine beef cubes with minced garlic, lemon juice, sumac, salt, and pepper. Add 2 cups water and let marinate in the refrigerator for 30 minutes.
 2. Thread the beef and a wedge of red onion alternately onto soaked wooden skewers.
@@ -8137,8 +8522,8 @@
 5. Cook time: 10</t>
         </is>
       </c>
-      <c r="U77" t="inlineStr"/>
-      <c r="V77" t="inlineStr">
+      <c r="V77" t="inlineStr"/>
+      <c r="W77" t="inlineStr">
         <is>
           <t>['In a bowl, combine beef cubes with minced garlic, lemon juice, sumac, salt, and pepper. Add 2\u202fcups water and let marinate in the refrigerator for 30 minutes.', 'Thread the beef and a wedge of red onion alternately onto soaked wooden skewers.', 'Preheat a grill pan over medium high heat. Grill the kebabs for about 8–10 minutes, turning frequently until the beef is just cooked through and onions are tender.', 'Garnish with lemon wedges and chopped parsley before serving.', 'Cook time: 10']</t>
         </is>
@@ -8162,10 +8547,15 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
+          <t>3388</t>
+        </is>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
           <t>['1 lb lean beef stew meat, cut into 1 inch cubes', '2 cups basmati rice, rinsed', '4 cups low sodium beef broth', '1 large onion, thinly sliced', '3 garlic cloves, minced', '1 tsp ground cumin', '1 tsp ground coriander', '½ tsp ground turmeric', '½ tsp ground cinnamon', 'Salt and pepper, to taste', '½ cup raisins', '1/4 cup chopped fresh mint', 'Juice of 1 lemon']</t>
         </is>
       </c>
-      <c r="E78" t="inlineStr">
+      <c r="F78" t="inlineStr">
         <is>
           <t>1. In a heavy pot, combine beef, onion, garlic, cumin, coriander, turmeric, cinnamon, salt, and pepper; sauté with a splash of water until the onion softens.
 2. Add raisins and beef broth; bring to a boil, then cover and simmer for 1–1½ hours until beef is tender.
@@ -8174,59 +8564,59 @@
 5. Cook time: 1</t>
         </is>
       </c>
-      <c r="F78" t="inlineStr">
+      <c r="G78" t="inlineStr">
         <is>
           <t>{"calories": 540, "protein": "38 g", "carbs": "60 g", "fiber": "8 g", "fat": "10 g"}</t>
         </is>
       </c>
-      <c r="G78" t="n">
+      <c r="H78" t="n">
         <v>4</v>
       </c>
-      <c r="H78" t="n">
+      <c r="I78" t="n">
         <v>25</v>
       </c>
-      <c r="I78" t="inlineStr">
-        <is>
-          <t>['weight-loss', 'plant-based', 'whole-foods', 'oil-free', 'lunches-and-dinners', 'soups', 'salads', 'wraps', 'sandwiches', 'rice', 'stews', 'stir-fry', 'seafood', 'ethnic', 'arabic', 'desserts']</t>
-        </is>
-      </c>
       <c r="J78" t="inlineStr">
         <is>
+          <t>['animal-protein', 'arabic', 'ethnic', 'lunches-and-dinners', 'oil-free', 'weight-loss']</t>
+        </is>
+      </c>
+      <c r="K78" t="inlineStr">
+        <is>
           <t>oil_free</t>
         </is>
       </c>
-      <c r="K78" t="inlineStr">
+      <c r="L78" t="inlineStr">
         <is>
           <t>plant_based</t>
         </is>
       </c>
-      <c r="L78" t="inlineStr">
+      <c r="M78" t="inlineStr">
         <is>
           <t>Savory</t>
         </is>
       </c>
-      <c r="M78" t="inlineStr">
+      <c r="N78" t="inlineStr">
         <is>
           <t>weight_loss</t>
         </is>
       </c>
-      <c r="N78" t="b">
-        <v>0</v>
-      </c>
       <c r="O78" t="b">
         <v>0</v>
       </c>
-      <c r="P78" t="inlineStr"/>
-      <c r="Q78" t="inlineStr">
+      <c r="P78" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q78" t="inlineStr"/>
+      <c r="R78" t="inlineStr">
         <is>
           <t>hot</t>
         </is>
       </c>
-      <c r="R78" t="n">
-        <v>0</v>
-      </c>
-      <c r="S78" t="inlineStr"/>
-      <c r="T78" t="inlineStr">
+      <c r="S78" t="n">
+        <v>0</v>
+      </c>
+      <c r="T78" t="inlineStr"/>
+      <c r="U78" t="inlineStr">
         <is>
           <t>1. In a heavy pot, combine beef, onion, garlic, cumin, coriander, turmeric, cinnamon, salt, and pepper; sauté with a splash of water until the onion softens.
 2. Add raisins and beef broth; bring to a boil, then cover and simmer for 1–1½ hours until beef is tender.
@@ -8235,8 +8625,8 @@
 5. Cook time: 1</t>
         </is>
       </c>
-      <c r="U78" t="inlineStr"/>
-      <c r="V78" t="inlineStr">
+      <c r="V78" t="inlineStr"/>
+      <c r="W78" t="inlineStr">
         <is>
           <t>['In a heavy pot, combine beef, onion, garlic, cumin, coriander, turmeric, cinnamon, salt, and pepper; sauté with a splash of water until the onion softens.', 'Add raisins and beef broth; bring to a boil, then cover and simmer for 1–1½ hours until beef is tender.', 'Stir in basmati rice, cover, and simmer for another 20 minutes until rice is cooked.', 'Mix in chopped mint and lemon juice, adjust seasoning, and serve hot.', 'Cook time: 1']</t>
         </is>
@@ -8255,15 +8645,20 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Oil Free Chicken Kebab with Freekeh</t>
+          <t>Oil Free Chicken Kebab With Freekeh</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
+          <t>3389</t>
+        </is>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
           <t>['1 lb chicken breast, cut into 1 inch cubes', '1 tsp ground sumac', '1 tsp ground cumin', 'Juice of 1 lemon', 'Salt and pepper, to taste', '10 wooden skewers (soaked in water for 30 minutes)', '2 cups freekeh, rinsed', '2 cups low sodium chicken broth', '1/4 cup chopped fresh parsley']</t>
         </is>
       </c>
-      <c r="E79" t="inlineStr">
+      <c r="F79" t="inlineStr">
         <is>
           <t>1. In a bowl, marinate chicken cubes with lemon juice, sumac, cumin, salt, and pepper for 20 minutes.
 2. Thread the marinated chicken onto skewers.
@@ -8274,59 +8669,59 @@
 7. Cook time: 25</t>
         </is>
       </c>
-      <c r="F79" t="inlineStr">
+      <c r="G79" t="inlineStr">
         <is>
           <t>{"calories": 480, "protein": "38 g", "carbs": "55 g", "fiber": "7 g", "fat": "8 g"}</t>
         </is>
       </c>
-      <c r="G79" t="n">
+      <c r="H79" t="n">
         <v>4</v>
       </c>
-      <c r="H79" t="n">
+      <c r="I79" t="n">
         <v>20</v>
       </c>
-      <c r="I79" t="inlineStr">
-        <is>
-          <t>['weight-loss', 'plant-based', 'whole-foods', 'oil-free', 'lunches-and-dinners', 'soups', 'salads', 'wraps', 'sandwiches', 'rice', 'stews', 'stir-fry', 'seafood', 'ethnic', 'arabic', 'desserts']</t>
-        </is>
-      </c>
       <c r="J79" t="inlineStr">
         <is>
+          <t>['animal-protein', 'arabic', 'ethnic', 'lunches-and-dinners', 'oil-free', 'weight-loss']</t>
+        </is>
+      </c>
+      <c r="K79" t="inlineStr">
+        <is>
           <t>oil_free</t>
         </is>
       </c>
-      <c r="K79" t="inlineStr">
+      <c r="L79" t="inlineStr">
         <is>
           <t>plant_based</t>
         </is>
       </c>
-      <c r="L79" t="inlineStr">
+      <c r="M79" t="inlineStr">
         <is>
           <t>Savory</t>
         </is>
       </c>
-      <c r="M79" t="inlineStr">
+      <c r="N79" t="inlineStr">
         <is>
           <t>weight_loss</t>
         </is>
       </c>
-      <c r="N79" t="b">
-        <v>0</v>
-      </c>
       <c r="O79" t="b">
         <v>0</v>
       </c>
-      <c r="P79" t="inlineStr"/>
-      <c r="Q79" t="inlineStr">
+      <c r="P79" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q79" t="inlineStr"/>
+      <c r="R79" t="inlineStr">
         <is>
           <t>hot</t>
         </is>
       </c>
-      <c r="R79" t="n">
-        <v>0</v>
-      </c>
-      <c r="S79" t="inlineStr"/>
-      <c r="T79" t="inlineStr">
+      <c r="S79" t="n">
+        <v>0</v>
+      </c>
+      <c r="T79" t="inlineStr"/>
+      <c r="U79" t="inlineStr">
         <is>
           <t>1. In a bowl, marinate chicken cubes with lemon juice, sumac, cumin, salt, and pepper for 20 minutes.
 2. Thread the marinated chicken onto skewers.
@@ -8337,8 +8732,8 @@
 7. Cook time: 25</t>
         </is>
       </c>
-      <c r="U79" t="inlineStr"/>
-      <c r="V79" t="inlineStr">
+      <c r="V79" t="inlineStr"/>
+      <c r="W79" t="inlineStr">
         <is>
           <t>['In a bowl, marinate chicken cubes with lemon juice, sumac, cumin, salt, and pepper for 20 minutes.', 'Thread the marinated chicken onto skewers.', 'Preheat a grill or grill pan over medium-high heat; grill the chicken kebabs for 8–10 minutes until cooked through.', 'Meanwhile, bring chicken broth to a boil; stir in freekeh, cover, and simmer for 15 minutes until tender.', 'Stir chopped parsley into the cooked freekeh.', 'Serve the grilled chicken kebabs over a bed of herbed freekeh.', 'Cook time: 25']</t>
         </is>
@@ -8362,10 +8757,15 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
+          <t>3390</t>
+        </is>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
           <t>['1 lb turkey breast, cut into chunks', '2 cups basmati rice, rinsed', '4 cups low sodium turkey or chicken broth', '1 large onion, sliced', '3 garlic cloves, minced', '1 tsp ground cumin', '1 tsp ground coriander', '½ tsp turmeric', '½ tsp cinnamon', 'Salt and pepper, to taste', 'Juice of 1 lemon', 'Fresh cilantro, chopped (for garnish)']</t>
         </is>
       </c>
-      <c r="E80" t="inlineStr">
+      <c r="F80" t="inlineStr">
         <is>
           <t>1. In a large pot, combine turkey chunks, onion, garlic, cumin, coriander, turmeric, cinnamon, salt, and pepper with the broth; bring to a boil and simmer for 30 minutes until turkey is tender.
 2. Stir in basmati rice; cover and simmer for another 20 minutes until the rice is cooked and has absorbed most of the liquid.
@@ -8374,59 +8774,59 @@
 5. Cook time: 50</t>
         </is>
       </c>
-      <c r="F80" t="inlineStr">
+      <c r="G80" t="inlineStr">
         <is>
           <t>{"calories": 520, "protein": "36 g", "carbs": "60 g", "fiber": "7 g", "fat": "8 g"}</t>
         </is>
       </c>
-      <c r="G80" t="n">
+      <c r="H80" t="n">
         <v>4</v>
       </c>
-      <c r="H80" t="n">
+      <c r="I80" t="n">
         <v>25</v>
       </c>
-      <c r="I80" t="inlineStr">
-        <is>
-          <t>['weight-loss', 'plant-based', 'whole-foods', 'oil-free', 'lunches-and-dinners', 'soups', 'salads', 'wraps', 'sandwiches', 'rice', 'stews', 'stir-fry', 'seafood', 'ethnic', 'arabic', 'desserts']</t>
-        </is>
-      </c>
       <c r="J80" t="inlineStr">
         <is>
+          <t>['animal-protein', 'arabic', 'ethnic', 'lunches-and-dinners', 'oil-free', 'weight-loss']</t>
+        </is>
+      </c>
+      <c r="K80" t="inlineStr">
+        <is>
           <t>oil_free</t>
         </is>
       </c>
-      <c r="K80" t="inlineStr">
+      <c r="L80" t="inlineStr">
         <is>
           <t>plant_based</t>
         </is>
       </c>
-      <c r="L80" t="inlineStr">
+      <c r="M80" t="inlineStr">
         <is>
           <t>Savory</t>
         </is>
       </c>
-      <c r="M80" t="inlineStr">
+      <c r="N80" t="inlineStr">
         <is>
           <t>weight_loss</t>
         </is>
       </c>
-      <c r="N80" t="b">
-        <v>0</v>
-      </c>
       <c r="O80" t="b">
         <v>0</v>
       </c>
-      <c r="P80" t="inlineStr"/>
-      <c r="Q80" t="inlineStr">
+      <c r="P80" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q80" t="inlineStr"/>
+      <c r="R80" t="inlineStr">
         <is>
           <t>hot</t>
         </is>
       </c>
-      <c r="R80" t="n">
-        <v>0</v>
-      </c>
-      <c r="S80" t="inlineStr"/>
-      <c r="T80" t="inlineStr">
+      <c r="S80" t="n">
+        <v>0</v>
+      </c>
+      <c r="T80" t="inlineStr"/>
+      <c r="U80" t="inlineStr">
         <is>
           <t>1. In a large pot, combine turkey chunks, onion, garlic, cumin, coriander, turmeric, cinnamon, salt, and pepper with the broth; bring to a boil and simmer for 30 minutes until turkey is tender.
 2. Stir in basmati rice; cover and simmer for another 20 minutes until the rice is cooked and has absorbed most of the liquid.
@@ -8435,8 +8835,8 @@
 5. Cook time: 50</t>
         </is>
       </c>
-      <c r="U80" t="inlineStr"/>
-      <c r="V80" t="inlineStr">
+      <c r="V80" t="inlineStr"/>
+      <c r="W80" t="inlineStr">
         <is>
           <t>['In a large pot, combine turkey chunks, onion, garlic, cumin, coriander, turmeric, cinnamon, salt, and pepper with the broth; bring to a boil and simmer for 30 minutes until turkey is tender.', 'Stir in basmati rice; cover and simmer for another 20 minutes until the rice is cooked and has absorbed most of the liquid.', 'Add lemon juice and adjust seasoning.', 'Garnish with fresh cilantro before serving.', 'Cook time: 50']</t>
         </is>
@@ -8460,10 +8860,15 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
+          <t>3391</t>
+        </is>
+      </c>
+      <c r="E81" t="inlineStr">
+        <is>
           <t>['8 oz chicken breast, thinly sliced', '8 oz lean beef sirloin, thinly sliced', '8 oz lamb cubes (lean), cut into 1 inch pieces', '1 tsp ground sumac', '1 tsp ground cumin', 'Juice of 1 lemon', 'Salt and pepper, to taste', '2 cups steamed white rice', '1 cup grilled vegetables (such as bell peppers and onions)', 'Fresh parsley, chopped (for garnish)']</t>
         </is>
       </c>
-      <c r="E81" t="inlineStr">
+      <c r="F81" t="inlineStr">
         <is>
           <t>1. In separate bowls, season each meat type with lemon juice, salt, pepper, and appropriate spices (e.g., sumac for beef, cumin for lamb, and a mild blend for chicken).
 2. Grill the meats on a preheated grill pan over medium- high heat: chicken slices for about 5 minutes, beef for 3–4 minutes, and lamb cubes for 8–10 minutes, until all are cooked to your preference.
@@ -8472,59 +8877,59 @@
 5. Cook time: 15</t>
         </is>
       </c>
-      <c r="F81" t="inlineStr">
+      <c r="G81" t="inlineStr">
         <is>
           <t>{"calories": 550, "protein": "40 g", "carbs": "55 g", "fiber": "8 g", "fat": "14 g"}</t>
         </is>
       </c>
-      <c r="G81" t="n">
+      <c r="H81" t="n">
         <v>4</v>
       </c>
-      <c r="H81" t="n">
+      <c r="I81" t="n">
         <v>25</v>
       </c>
-      <c r="I81" t="inlineStr">
-        <is>
-          <t>['weight-loss', 'plant-based', 'whole-foods', 'oil-free', 'lunches-and-dinners', 'soups', 'salads', 'wraps', 'sandwiches', 'rice', 'stews', 'stir-fry', 'seafood', 'ethnic', 'arabic', 'desserts']</t>
-        </is>
-      </c>
       <c r="J81" t="inlineStr">
         <is>
+          <t>['animal-protein', 'arabic', 'ethnic', 'lunches-and-dinners', 'oil-free', 'rice', 'weight-loss']</t>
+        </is>
+      </c>
+      <c r="K81" t="inlineStr">
+        <is>
           <t>oil_free</t>
         </is>
       </c>
-      <c r="K81" t="inlineStr">
+      <c r="L81" t="inlineStr">
         <is>
           <t>plant_based</t>
         </is>
       </c>
-      <c r="L81" t="inlineStr">
+      <c r="M81" t="inlineStr">
         <is>
           <t>Savory</t>
         </is>
       </c>
-      <c r="M81" t="inlineStr">
+      <c r="N81" t="inlineStr">
         <is>
           <t>weight_loss</t>
         </is>
       </c>
-      <c r="N81" t="b">
-        <v>0</v>
-      </c>
       <c r="O81" t="b">
         <v>0</v>
       </c>
-      <c r="P81" t="inlineStr"/>
-      <c r="Q81" t="inlineStr">
+      <c r="P81" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q81" t="inlineStr"/>
+      <c r="R81" t="inlineStr">
         <is>
           <t>hot</t>
         </is>
       </c>
-      <c r="R81" t="n">
-        <v>0</v>
-      </c>
-      <c r="S81" t="inlineStr"/>
-      <c r="T81" t="inlineStr">
+      <c r="S81" t="n">
+        <v>0</v>
+      </c>
+      <c r="T81" t="inlineStr"/>
+      <c r="U81" t="inlineStr">
         <is>
           <t>1. In separate bowls, season each meat type with lemon juice, salt, pepper, and appropriate spices (e.g., sumac for beef, cumin for lamb, and a mild blend for chicken).
 2. Grill the meats on a preheated grill pan over medium- high heat: chicken slices for about 5 minutes, beef for 3–4 minutes, and lamb cubes for 8–10 minutes, until all are cooked to your preference.
@@ -8533,8 +8938,8 @@
 5. Cook time: 15</t>
         </is>
       </c>
-      <c r="U81" t="inlineStr"/>
-      <c r="V81" t="inlineStr">
+      <c r="V81" t="inlineStr"/>
+      <c r="W81" t="inlineStr">
         <is>
           <t>['In separate bowls, season each meat type with lemon juice, salt, pepper, and appropriate spices (e.g., sumac for beef, cumin for lamb, and a mild blend for chicken).', 'Grill the meats on a preheated grill pan over medium- high heat: chicken slices for about 5 minutes, beef for 3–4 minutes, and lamb cubes for 8–10 minutes, until all are cooked to your preference.', 'In a large bowl, combine steamed white rice with grilled vegetables.', 'Arrange the grilled meats on top of the rice mixture, garnish with fresh parsley, and serve with additional lemon wedges on the side.', 'Cook time: 15']</t>
         </is>
